--- a/artfynd/A 38519-2025 artfynd.xlsx
+++ b/artfynd/A 38519-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128115307</v>
       </c>
       <c r="B2" t="n">
-        <v>91367</v>
+        <v>91368</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -869,45 +869,49 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>128115311</v>
+        <v>128115303</v>
       </c>
       <c r="B4" t="n">
-        <v>79029</v>
+        <v>98468</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Selsknösen, Vb</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>742052</v>
+        <v>742050</v>
       </c>
       <c r="R4" t="n">
-        <v>7112024</v>
+        <v>7111963</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -948,6 +952,7 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
+      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
@@ -966,10 +971,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128115303</v>
+        <v>128115305</v>
       </c>
       <c r="B5" t="n">
-        <v>98467</v>
+        <v>98468</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1005,10 +1010,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>742050</v>
+        <v>741970</v>
       </c>
       <c r="R5" t="n">
-        <v>7111963</v>
+        <v>7111969</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1068,49 +1073,45 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128115305</v>
+        <v>128115311</v>
       </c>
       <c r="B6" t="n">
-        <v>98467</v>
+        <v>79029</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
-      <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
-      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Selsknösen, Vb</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>741970</v>
+        <v>742052</v>
       </c>
       <c r="R6" t="n">
-        <v>7111969</v>
+        <v>7112024</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1151,7 +1152,6 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
-      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -1173,7 +1173,7 @@
         <v>128115285</v>
       </c>
       <c r="B7" t="n">
-        <v>91314</v>
+        <v>91315</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1267,32 +1267,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>128115289</v>
+        <v>128115299</v>
       </c>
       <c r="B8" t="n">
-        <v>91349</v>
+        <v>80168</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1202</v>
+        <v>6464</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1302,10 +1302,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>742020</v>
+        <v>742269</v>
       </c>
       <c r="R8" t="n">
-        <v>7111950</v>
+        <v>7112162</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1346,7 +1346,6 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
-      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
@@ -1365,32 +1364,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>128115299</v>
+        <v>128115289</v>
       </c>
       <c r="B9" t="n">
-        <v>80168</v>
+        <v>91350</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6464</v>
+        <v>1202</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1400,10 +1399,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>742269</v>
+        <v>742020</v>
       </c>
       <c r="R9" t="n">
-        <v>7112162</v>
+        <v>7111950</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1444,6 +1443,7 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
+      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
@@ -1879,7 +1879,7 @@
         <v>128115302</v>
       </c>
       <c r="B14" t="n">
-        <v>98467</v>
+        <v>98468</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1978,42 +1978,38 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>128115367</v>
+        <v>128115304</v>
       </c>
       <c r="B15" t="n">
-        <v>57672</v>
+        <v>98468</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr"/>
       <c r="K15" t="inlineStr"/>
       <c r="L15" t="inlineStr"/>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
       <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
@@ -2021,10 +2017,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>742063</v>
+        <v>741996</v>
       </c>
       <c r="R15" t="n">
-        <v>7111956</v>
+        <v>7111968</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2059,17 +2055,13 @@
           <t>2025-08-27</t>
         </is>
       </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
-        </is>
-      </c>
       <c r="AD15" t="b">
         <v>0</v>
       </c>
       <c r="AE15" t="b">
         <v>0</v>
       </c>
+      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
       </c>
@@ -2088,38 +2080,42 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>128115304</v>
+        <v>128115367</v>
       </c>
       <c r="B16" t="n">
-        <v>98467</v>
+        <v>57672</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="J16" t="inlineStr"/>
       <c r="K16" t="inlineStr"/>
       <c r="L16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
@@ -2127,10 +2123,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>741996</v>
+        <v>742063</v>
       </c>
       <c r="R16" t="n">
-        <v>7111968</v>
+        <v>7111956</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2165,13 +2161,17 @@
           <t>2025-08-27</t>
         </is>
       </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
+        </is>
+      </c>
       <c r="AD16" t="b">
         <v>0</v>
       </c>
       <c r="AE16" t="b">
         <v>0</v>
       </c>
-      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
@@ -2193,7 +2193,7 @@
         <v>128115314</v>
       </c>
       <c r="B17" t="n">
-        <v>98384</v>
+        <v>98385</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2287,10 +2287,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>128115287</v>
+        <v>128115298</v>
       </c>
       <c r="B18" t="n">
-        <v>91314</v>
+        <v>95700</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2298,21 +2298,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>5447</v>
+        <v>2809</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Mörk husmossa</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Hylocomiastrum umbratum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Hedw.) M.Fleisch.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2322,10 +2322,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>742039</v>
+        <v>742124</v>
       </c>
       <c r="R18" t="n">
-        <v>7111970</v>
+        <v>7112073</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2384,10 +2384,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>128115298</v>
+        <v>128115287</v>
       </c>
       <c r="B19" t="n">
-        <v>95699</v>
+        <v>91315</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2395,21 +2395,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>2809</v>
+        <v>5447</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Mörk husmossa</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Hylocomiastrum umbratum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Hedw.) M.Fleisch.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2419,10 +2419,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>742124</v>
+        <v>742039</v>
       </c>
       <c r="R19" t="n">
-        <v>7112073</v>
+        <v>7111970</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2484,7 +2484,7 @@
         <v>128115288</v>
       </c>
       <c r="B20" t="n">
-        <v>96814</v>
+        <v>96815</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2582,7 +2582,7 @@
         <v>128115286</v>
       </c>
       <c r="B21" t="n">
-        <v>91314</v>
+        <v>91315</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>

--- a/artfynd/A 38519-2025 artfynd.xlsx
+++ b/artfynd/A 38519-2025 artfynd.xlsx
@@ -869,49 +869,45 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>128115303</v>
+        <v>128115311</v>
       </c>
       <c r="B4" t="n">
-        <v>98468</v>
+        <v>79029</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
-      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Selsknösen, Vb</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>742050</v>
+        <v>742052</v>
       </c>
       <c r="R4" t="n">
-        <v>7111963</v>
+        <v>7112024</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -952,7 +948,6 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
-      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
@@ -971,7 +966,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128115305</v>
+        <v>128115303</v>
       </c>
       <c r="B5" t="n">
         <v>98468</v>
@@ -1010,10 +1005,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>741970</v>
+        <v>742050</v>
       </c>
       <c r="R5" t="n">
-        <v>7111969</v>
+        <v>7111963</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1073,45 +1068,49 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128115311</v>
+        <v>128115305</v>
       </c>
       <c r="B6" t="n">
-        <v>79029</v>
+        <v>98468</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Selsknösen, Vb</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>742052</v>
+        <v>741970</v>
       </c>
       <c r="R6" t="n">
-        <v>7112024</v>
+        <v>7111969</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1152,6 +1151,7 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
+      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 38519-2025 artfynd.xlsx
+++ b/artfynd/A 38519-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128115307</v>
       </c>
       <c r="B2" t="n">
-        <v>91368</v>
+        <v>91369</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -969,7 +969,7 @@
         <v>128115303</v>
       </c>
       <c r="B5" t="n">
-        <v>98468</v>
+        <v>98469</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1071,7 +1071,7 @@
         <v>128115305</v>
       </c>
       <c r="B6" t="n">
-        <v>98468</v>
+        <v>98469</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1173,7 +1173,7 @@
         <v>128115285</v>
       </c>
       <c r="B7" t="n">
-        <v>91315</v>
+        <v>91316</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1367,7 +1367,7 @@
         <v>128115289</v>
       </c>
       <c r="B9" t="n">
-        <v>91350</v>
+        <v>91351</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1879,7 +1879,7 @@
         <v>128115302</v>
       </c>
       <c r="B14" t="n">
-        <v>98468</v>
+        <v>98469</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1978,38 +1978,42 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>128115304</v>
+        <v>128115367</v>
       </c>
       <c r="B15" t="n">
-        <v>98468</v>
+        <v>57672</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
-      <c r="J15" t="inlineStr"/>
       <c r="K15" t="inlineStr"/>
       <c r="L15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
@@ -2017,10 +2021,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>741996</v>
+        <v>742063</v>
       </c>
       <c r="R15" t="n">
-        <v>7111968</v>
+        <v>7111956</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2055,13 +2059,17 @@
           <t>2025-08-27</t>
         </is>
       </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
+        </is>
+      </c>
       <c r="AD15" t="b">
         <v>0</v>
       </c>
       <c r="AE15" t="b">
         <v>0</v>
       </c>
-      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
       </c>
@@ -2080,42 +2088,38 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>128115367</v>
+        <v>128115304</v>
       </c>
       <c r="B16" t="n">
-        <v>57672</v>
+        <v>98469</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr"/>
       <c r="K16" t="inlineStr"/>
       <c r="L16" t="inlineStr"/>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
       <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
@@ -2123,10 +2127,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>742063</v>
+        <v>741996</v>
       </c>
       <c r="R16" t="n">
-        <v>7111956</v>
+        <v>7111968</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2161,17 +2165,13 @@
           <t>2025-08-27</t>
         </is>
       </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
-        </is>
-      </c>
       <c r="AD16" t="b">
         <v>0</v>
       </c>
       <c r="AE16" t="b">
         <v>0</v>
       </c>
+      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
@@ -2193,7 +2193,7 @@
         <v>128115314</v>
       </c>
       <c r="B17" t="n">
-        <v>98385</v>
+        <v>98386</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2287,10 +2287,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>128115298</v>
+        <v>128115287</v>
       </c>
       <c r="B18" t="n">
-        <v>95700</v>
+        <v>91316</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2298,21 +2298,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>2809</v>
+        <v>5447</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Mörk husmossa</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Hylocomiastrum umbratum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Hedw.) M.Fleisch.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2322,10 +2322,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>742124</v>
+        <v>742039</v>
       </c>
       <c r="R18" t="n">
-        <v>7112073</v>
+        <v>7111970</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2384,10 +2384,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>128115287</v>
+        <v>128115298</v>
       </c>
       <c r="B19" t="n">
-        <v>91315</v>
+        <v>95701</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2395,21 +2395,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>5447</v>
+        <v>2809</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Mörk husmossa</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Hylocomiastrum umbratum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Hedw.) M.Fleisch.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2419,10 +2419,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>742039</v>
+        <v>742124</v>
       </c>
       <c r="R19" t="n">
-        <v>7111970</v>
+        <v>7112073</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2484,7 +2484,7 @@
         <v>128115288</v>
       </c>
       <c r="B20" t="n">
-        <v>96815</v>
+        <v>96816</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2582,7 +2582,7 @@
         <v>128115286</v>
       </c>
       <c r="B21" t="n">
-        <v>91315</v>
+        <v>91316</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>

--- a/artfynd/A 38519-2025 artfynd.xlsx
+++ b/artfynd/A 38519-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128115307</v>
       </c>
       <c r="B2" t="n">
-        <v>91369</v>
+        <v>91370</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -969,7 +969,7 @@
         <v>128115303</v>
       </c>
       <c r="B5" t="n">
-        <v>98469</v>
+        <v>98470</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1071,7 +1071,7 @@
         <v>128115305</v>
       </c>
       <c r="B6" t="n">
-        <v>98469</v>
+        <v>98470</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1173,7 +1173,7 @@
         <v>128115285</v>
       </c>
       <c r="B7" t="n">
-        <v>91316</v>
+        <v>91317</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1367,7 +1367,7 @@
         <v>128115289</v>
       </c>
       <c r="B9" t="n">
-        <v>91351</v>
+        <v>91352</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1879,7 +1879,7 @@
         <v>128115302</v>
       </c>
       <c r="B14" t="n">
-        <v>98469</v>
+        <v>98470</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1978,42 +1978,38 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>128115367</v>
+        <v>128115304</v>
       </c>
       <c r="B15" t="n">
-        <v>57672</v>
+        <v>98470</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr"/>
       <c r="K15" t="inlineStr"/>
       <c r="L15" t="inlineStr"/>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
       <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
@@ -2021,10 +2017,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>742063</v>
+        <v>741996</v>
       </c>
       <c r="R15" t="n">
-        <v>7111956</v>
+        <v>7111968</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2059,17 +2055,13 @@
           <t>2025-08-27</t>
         </is>
       </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
-        </is>
-      </c>
       <c r="AD15" t="b">
         <v>0</v>
       </c>
       <c r="AE15" t="b">
         <v>0</v>
       </c>
+      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
       </c>
@@ -2088,38 +2080,42 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>128115304</v>
+        <v>128115367</v>
       </c>
       <c r="B16" t="n">
-        <v>98469</v>
+        <v>57672</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="J16" t="inlineStr"/>
       <c r="K16" t="inlineStr"/>
       <c r="L16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
@@ -2127,10 +2123,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>741996</v>
+        <v>742063</v>
       </c>
       <c r="R16" t="n">
-        <v>7111968</v>
+        <v>7111956</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2165,13 +2161,17 @@
           <t>2025-08-27</t>
         </is>
       </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
+        </is>
+      </c>
       <c r="AD16" t="b">
         <v>0</v>
       </c>
       <c r="AE16" t="b">
         <v>0</v>
       </c>
-      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
@@ -2193,7 +2193,7 @@
         <v>128115314</v>
       </c>
       <c r="B17" t="n">
-        <v>98386</v>
+        <v>98387</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2287,10 +2287,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>128115287</v>
+        <v>128115298</v>
       </c>
       <c r="B18" t="n">
-        <v>91316</v>
+        <v>95702</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2298,21 +2298,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>5447</v>
+        <v>2809</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Mörk husmossa</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Hylocomiastrum umbratum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Hedw.) M.Fleisch.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2322,10 +2322,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>742039</v>
+        <v>742124</v>
       </c>
       <c r="R18" t="n">
-        <v>7111970</v>
+        <v>7112073</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2384,10 +2384,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>128115298</v>
+        <v>128115287</v>
       </c>
       <c r="B19" t="n">
-        <v>95701</v>
+        <v>91317</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2395,21 +2395,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>2809</v>
+        <v>5447</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Mörk husmossa</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Hylocomiastrum umbratum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Hedw.) M.Fleisch.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2419,10 +2419,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>742124</v>
+        <v>742039</v>
       </c>
       <c r="R19" t="n">
-        <v>7112073</v>
+        <v>7111970</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2484,7 +2484,7 @@
         <v>128115288</v>
       </c>
       <c r="B20" t="n">
-        <v>96816</v>
+        <v>96817</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2582,7 +2582,7 @@
         <v>128115286</v>
       </c>
       <c r="B21" t="n">
-        <v>91316</v>
+        <v>91317</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>

--- a/artfynd/A 38519-2025 artfynd.xlsx
+++ b/artfynd/A 38519-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY23"/>
+  <dimension ref="A1:AY25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -869,45 +869,49 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>128115311</v>
+        <v>128115305</v>
       </c>
       <c r="B4" t="n">
-        <v>79029</v>
+        <v>98470</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Selsknösen, Vb</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>742052</v>
+        <v>741970</v>
       </c>
       <c r="R4" t="n">
-        <v>7112024</v>
+        <v>7111969</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -948,6 +952,7 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
+      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
@@ -1068,49 +1073,45 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128115305</v>
+        <v>128115311</v>
       </c>
       <c r="B6" t="n">
-        <v>98470</v>
+        <v>79029</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
-      <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
-      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Selsknösen, Vb</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>741970</v>
+        <v>742052</v>
       </c>
       <c r="R6" t="n">
-        <v>7111969</v>
+        <v>7112024</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1151,7 +1152,6 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
-      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -1267,32 +1267,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>128115299</v>
+        <v>128115289</v>
       </c>
       <c r="B8" t="n">
-        <v>80168</v>
+        <v>91352</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6464</v>
+        <v>1202</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1302,10 +1302,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>742269</v>
+        <v>742020</v>
       </c>
       <c r="R8" t="n">
-        <v>7112162</v>
+        <v>7111950</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1346,6 +1346,7 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
+      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
@@ -1364,32 +1365,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>128115289</v>
+        <v>128115299</v>
       </c>
       <c r="B9" t="n">
-        <v>91352</v>
+        <v>80168</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1202</v>
+        <v>6464</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1399,10 +1400,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>742020</v>
+        <v>742269</v>
       </c>
       <c r="R9" t="n">
-        <v>7111950</v>
+        <v>7112162</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1443,7 +1444,6 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
-      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
@@ -2384,32 +2384,32 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>128115287</v>
+        <v>128115288</v>
       </c>
       <c r="B19" t="n">
-        <v>91317</v>
+        <v>96817</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>5447</v>
+        <v>1841</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Vedflikmossa</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Lophozia guttulata</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Lindb. &amp; Arnell) A.Evans</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2419,10 +2419,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>742039</v>
+        <v>742438</v>
       </c>
       <c r="R19" t="n">
-        <v>7111970</v>
+        <v>7112145</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2463,6 +2463,7 @@
       <c r="AE19" t="b">
         <v>0</v>
       </c>
+      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
       </c>
@@ -2481,32 +2482,32 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>128115288</v>
+        <v>128115287</v>
       </c>
       <c r="B20" t="n">
-        <v>96817</v>
+        <v>91317</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>1841</v>
+        <v>5447</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Vedflikmossa</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Lophozia guttulata</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Lindb. &amp; Arnell) A.Evans</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2516,10 +2517,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>742438</v>
+        <v>742039</v>
       </c>
       <c r="R20" t="n">
-        <v>7112145</v>
+        <v>7111970</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2560,7 +2561,6 @@
       <c r="AE20" t="b">
         <v>0</v>
       </c>
-      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
       </c>
@@ -2868,6 +2868,201 @@
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>128314983</v>
+      </c>
+      <c r="B24" t="n">
+        <v>91710</v>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>2062</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Ulltickeporing</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Skeletocutis brevispora</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>Niemelä</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>Selsknösen, Vb</t>
+        </is>
+      </c>
+      <c r="Q24" t="n">
+        <v>742315</v>
+      </c>
+      <c r="R24" t="n">
+        <v>7112279</v>
+      </c>
+      <c r="S24" t="n">
+        <v>10</v>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>Umeå</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>Umeå socken</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>2025-08-27</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>2025-08-27</t>
+        </is>
+      </c>
+      <c r="AD24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF24" t="inlineStr"/>
+      <c r="AG24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT24" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>Elin Kannerby</t>
+        </is>
+      </c>
+      <c r="AX24" t="inlineStr">
+        <is>
+          <t>Elin Kannerby</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>128314982</v>
+      </c>
+      <c r="B25" t="n">
+        <v>91724</v>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>1505</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Kristallticka</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Skeletocutis stellae</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>(Pilát) Jean Keller</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>Selsknösen, Vb</t>
+        </is>
+      </c>
+      <c r="Q25" t="n">
+        <v>742153</v>
+      </c>
+      <c r="R25" t="n">
+        <v>7112076</v>
+      </c>
+      <c r="S25" t="n">
+        <v>10</v>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>Umeå</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>Umeå socken</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>2025-08-27</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>2025-08-27</t>
+        </is>
+      </c>
+      <c r="AD25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT25" t="inlineStr"/>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>Elin Kannerby</t>
+        </is>
+      </c>
+      <c r="AX25" t="inlineStr">
+        <is>
+          <t>Elin Kannerby</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 38519-2025 artfynd.xlsx
+++ b/artfynd/A 38519-2025 artfynd.xlsx
@@ -1978,38 +1978,42 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>128115304</v>
+        <v>128115367</v>
       </c>
       <c r="B15" t="n">
-        <v>98470</v>
+        <v>57672</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
-      <c r="J15" t="inlineStr"/>
       <c r="K15" t="inlineStr"/>
       <c r="L15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
@@ -2017,10 +2021,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>741996</v>
+        <v>742063</v>
       </c>
       <c r="R15" t="n">
-        <v>7111968</v>
+        <v>7111956</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2055,13 +2059,17 @@
           <t>2025-08-27</t>
         </is>
       </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
+        </is>
+      </c>
       <c r="AD15" t="b">
         <v>0</v>
       </c>
       <c r="AE15" t="b">
         <v>0</v>
       </c>
-      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
       </c>
@@ -2080,42 +2088,38 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>128115367</v>
+        <v>128115304</v>
       </c>
       <c r="B16" t="n">
-        <v>57672</v>
+        <v>98470</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr"/>
       <c r="K16" t="inlineStr"/>
       <c r="L16" t="inlineStr"/>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
       <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
@@ -2123,10 +2127,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>742063</v>
+        <v>741996</v>
       </c>
       <c r="R16" t="n">
-        <v>7111956</v>
+        <v>7111968</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2161,17 +2165,13 @@
           <t>2025-08-27</t>
         </is>
       </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
-        </is>
-      </c>
       <c r="AD16" t="b">
         <v>0</v>
       </c>
       <c r="AE16" t="b">
         <v>0</v>
       </c>
+      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 38519-2025 artfynd.xlsx
+++ b/artfynd/A 38519-2025 artfynd.xlsx
@@ -1678,45 +1678,49 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>128115294</v>
+        <v>128115293</v>
       </c>
       <c r="B12" t="n">
-        <v>80036</v>
+        <v>57669</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6456</v>
+        <v>100049</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr"/>
+      <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
           <t>Selsknösen, Vb</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>742181</v>
+        <v>742018</v>
       </c>
       <c r="R12" t="n">
-        <v>7112082</v>
+        <v>7112166</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1775,49 +1779,45 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>128115293</v>
+        <v>128115294</v>
       </c>
       <c r="B13" t="n">
-        <v>57669</v>
+        <v>80036</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100049</v>
+        <v>6456</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="K13" t="inlineStr"/>
-      <c r="L13" t="inlineStr"/>
-      <c r="M13" t="inlineStr"/>
-      <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>Selsknösen, Vb</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>742018</v>
+        <v>742181</v>
       </c>
       <c r="R13" t="n">
-        <v>7112166</v>
+        <v>7112082</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>

--- a/artfynd/A 38519-2025 artfynd.xlsx
+++ b/artfynd/A 38519-2025 artfynd.xlsx
@@ -869,49 +869,45 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>128115305</v>
+        <v>128115311</v>
       </c>
       <c r="B4" t="n">
-        <v>98470</v>
+        <v>79029</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
-      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Selsknösen, Vb</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>741970</v>
+        <v>742052</v>
       </c>
       <c r="R4" t="n">
-        <v>7111969</v>
+        <v>7112024</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -952,7 +948,6 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
-      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
@@ -1073,45 +1068,49 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128115311</v>
+        <v>128115305</v>
       </c>
       <c r="B6" t="n">
-        <v>79029</v>
+        <v>98470</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Selsknösen, Vb</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>742052</v>
+        <v>741970</v>
       </c>
       <c r="R6" t="n">
-        <v>7112024</v>
+        <v>7111969</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1152,6 +1151,7 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
+      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 38519-2025 artfynd.xlsx
+++ b/artfynd/A 38519-2025 artfynd.xlsx
@@ -1678,49 +1678,45 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>128115293</v>
+        <v>128115294</v>
       </c>
       <c r="B12" t="n">
-        <v>57669</v>
+        <v>80036</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100049</v>
+        <v>6456</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="K12" t="inlineStr"/>
-      <c r="L12" t="inlineStr"/>
-      <c r="M12" t="inlineStr"/>
-      <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
           <t>Selsknösen, Vb</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>742018</v>
+        <v>742181</v>
       </c>
       <c r="R12" t="n">
-        <v>7112166</v>
+        <v>7112082</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1779,45 +1775,49 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>128115294</v>
+        <v>128115293</v>
       </c>
       <c r="B13" t="n">
-        <v>80036</v>
+        <v>57669</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6456</v>
+        <v>100049</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr"/>
+      <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>Selsknösen, Vb</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>742181</v>
+        <v>742018</v>
       </c>
       <c r="R13" t="n">
-        <v>7112082</v>
+        <v>7112166</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1978,42 +1978,38 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>128115367</v>
+        <v>128115304</v>
       </c>
       <c r="B15" t="n">
-        <v>57672</v>
+        <v>98470</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr"/>
       <c r="K15" t="inlineStr"/>
       <c r="L15" t="inlineStr"/>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
       <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
@@ -2021,10 +2017,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>742063</v>
+        <v>741996</v>
       </c>
       <c r="R15" t="n">
-        <v>7111956</v>
+        <v>7111968</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2059,17 +2055,13 @@
           <t>2025-08-27</t>
         </is>
       </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
-        </is>
-      </c>
       <c r="AD15" t="b">
         <v>0</v>
       </c>
       <c r="AE15" t="b">
         <v>0</v>
       </c>
+      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
       </c>
@@ -2088,38 +2080,42 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>128115304</v>
+        <v>128115367</v>
       </c>
       <c r="B16" t="n">
-        <v>98470</v>
+        <v>57672</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="J16" t="inlineStr"/>
       <c r="K16" t="inlineStr"/>
       <c r="L16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
@@ -2127,10 +2123,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>741996</v>
+        <v>742063</v>
       </c>
       <c r="R16" t="n">
-        <v>7111968</v>
+        <v>7111956</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2165,13 +2161,17 @@
           <t>2025-08-27</t>
         </is>
       </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
+        </is>
+      </c>
       <c r="AD16" t="b">
         <v>0</v>
       </c>
       <c r="AE16" t="b">
         <v>0</v>
       </c>
-      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 38519-2025 artfynd.xlsx
+++ b/artfynd/A 38519-2025 artfynd.xlsx
@@ -869,45 +869,49 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>128115311</v>
+        <v>128115305</v>
       </c>
       <c r="B4" t="n">
-        <v>79029</v>
+        <v>98470</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Selsknösen, Vb</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>742052</v>
+        <v>741970</v>
       </c>
       <c r="R4" t="n">
-        <v>7112024</v>
+        <v>7111969</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -948,6 +952,7 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
+      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
@@ -966,49 +971,45 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128115303</v>
+        <v>128115311</v>
       </c>
       <c r="B5" t="n">
-        <v>98470</v>
+        <v>79029</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
-      <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
-      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Selsknösen, Vb</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>742050</v>
+        <v>742052</v>
       </c>
       <c r="R5" t="n">
-        <v>7111963</v>
+        <v>7112024</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1049,7 +1050,6 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
-      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1068,7 +1068,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128115305</v>
+        <v>128115303</v>
       </c>
       <c r="B6" t="n">
         <v>98470</v>
@@ -1107,10 +1107,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>741970</v>
+        <v>742050</v>
       </c>
       <c r="R6" t="n">
-        <v>7111969</v>
+        <v>7111963</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>

--- a/artfynd/A 38519-2025 artfynd.xlsx
+++ b/artfynd/A 38519-2025 artfynd.xlsx
@@ -1678,45 +1678,49 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>128115294</v>
+        <v>128115293</v>
       </c>
       <c r="B12" t="n">
-        <v>80036</v>
+        <v>57669</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6456</v>
+        <v>100049</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr"/>
+      <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
           <t>Selsknösen, Vb</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>742181</v>
+        <v>742018</v>
       </c>
       <c r="R12" t="n">
-        <v>7112082</v>
+        <v>7112166</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1775,49 +1779,45 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>128115293</v>
+        <v>128115294</v>
       </c>
       <c r="B13" t="n">
-        <v>57669</v>
+        <v>80036</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100049</v>
+        <v>6456</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="K13" t="inlineStr"/>
-      <c r="L13" t="inlineStr"/>
-      <c r="M13" t="inlineStr"/>
-      <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>Selsknösen, Vb</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>742018</v>
+        <v>742181</v>
       </c>
       <c r="R13" t="n">
-        <v>7112166</v>
+        <v>7112082</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1978,38 +1978,42 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>128115304</v>
+        <v>128115367</v>
       </c>
       <c r="B15" t="n">
-        <v>98470</v>
+        <v>57672</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
-      <c r="J15" t="inlineStr"/>
       <c r="K15" t="inlineStr"/>
       <c r="L15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
@@ -2017,10 +2021,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>741996</v>
+        <v>742063</v>
       </c>
       <c r="R15" t="n">
-        <v>7111968</v>
+        <v>7111956</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2055,13 +2059,17 @@
           <t>2025-08-27</t>
         </is>
       </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
+        </is>
+      </c>
       <c r="AD15" t="b">
         <v>0</v>
       </c>
       <c r="AE15" t="b">
         <v>0</v>
       </c>
-      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
       </c>
@@ -2080,42 +2088,38 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>128115367</v>
+        <v>128115304</v>
       </c>
       <c r="B16" t="n">
-        <v>57672</v>
+        <v>98470</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr"/>
       <c r="K16" t="inlineStr"/>
       <c r="L16" t="inlineStr"/>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
       <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
@@ -2123,10 +2127,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>742063</v>
+        <v>741996</v>
       </c>
       <c r="R16" t="n">
-        <v>7111956</v>
+        <v>7111968</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2161,17 +2165,13 @@
           <t>2025-08-27</t>
         </is>
       </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
-        </is>
-      </c>
       <c r="AD16" t="b">
         <v>0</v>
       </c>
       <c r="AE16" t="b">
         <v>0</v>
       </c>
+      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 38519-2025 artfynd.xlsx
+++ b/artfynd/A 38519-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128115307</v>
       </c>
       <c r="B2" t="n">
-        <v>91370</v>
+        <v>91378</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>128115310</v>
       </c>
       <c r="B3" t="n">
-        <v>79029</v>
+        <v>79032</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -869,10 +869,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>128115305</v>
+        <v>128115303</v>
       </c>
       <c r="B4" t="n">
-        <v>98470</v>
+        <v>98478</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -908,10 +908,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>741970</v>
+        <v>742050</v>
       </c>
       <c r="R4" t="n">
-        <v>7111969</v>
+        <v>7111963</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -971,45 +971,49 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128115311</v>
+        <v>128115305</v>
       </c>
       <c r="B5" t="n">
-        <v>79029</v>
+        <v>98478</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Selsknösen, Vb</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>742052</v>
+        <v>741970</v>
       </c>
       <c r="R5" t="n">
-        <v>7112024</v>
+        <v>7111969</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1050,6 +1054,7 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
+      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1068,49 +1073,45 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128115303</v>
+        <v>128115311</v>
       </c>
       <c r="B6" t="n">
-        <v>98470</v>
+        <v>79032</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
-      <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
-      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Selsknösen, Vb</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>742050</v>
+        <v>742052</v>
       </c>
       <c r="R6" t="n">
-        <v>7111963</v>
+        <v>7112024</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1151,7 +1152,6 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
-      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -1173,7 +1173,7 @@
         <v>128115285</v>
       </c>
       <c r="B7" t="n">
-        <v>91317</v>
+        <v>91325</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1267,45 +1267,49 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>128115289</v>
+        <v>128115290</v>
       </c>
       <c r="B8" t="n">
-        <v>91352</v>
+        <v>56864</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1202</v>
+        <v>100138</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr"/>
+      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Selsknösen, Vb</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>742020</v>
+        <v>742080</v>
       </c>
       <c r="R8" t="n">
-        <v>7111950</v>
+        <v>7112234</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1340,13 +1344,17 @@
           <t>2025-08-27</t>
         </is>
       </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Fjäder funnen</t>
+        </is>
+      </c>
       <c r="AD8" t="b">
         <v>0</v>
       </c>
       <c r="AE8" t="b">
         <v>0</v>
       </c>
-      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
@@ -1365,32 +1373,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>128115299</v>
+        <v>128115289</v>
       </c>
       <c r="B9" t="n">
-        <v>80168</v>
+        <v>91360</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6464</v>
+        <v>1202</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1400,10 +1408,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>742269</v>
+        <v>742020</v>
       </c>
       <c r="R9" t="n">
-        <v>7112162</v>
+        <v>7111950</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1444,6 +1452,7 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
+      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
@@ -1462,10 +1471,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>128115290</v>
+        <v>128115299</v>
       </c>
       <c r="B10" t="n">
-        <v>56864</v>
+        <v>80171</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1473,38 +1482,34 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100138</v>
+        <v>6464</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr"/>
-      <c r="M10" t="inlineStr"/>
-      <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Selsknösen, Vb</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>742080</v>
+        <v>742269</v>
       </c>
       <c r="R10" t="n">
-        <v>7112234</v>
+        <v>7112162</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1537,11 +1542,6 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-08-27</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Fjäder funnen</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1571,7 +1571,7 @@
         <v>128115295</v>
       </c>
       <c r="B11" t="n">
-        <v>57672</v>
+        <v>57673</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1678,49 +1678,45 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>128115293</v>
+        <v>128115294</v>
       </c>
       <c r="B12" t="n">
-        <v>57669</v>
+        <v>80039</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100049</v>
+        <v>6456</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="K12" t="inlineStr"/>
-      <c r="L12" t="inlineStr"/>
-      <c r="M12" t="inlineStr"/>
-      <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
           <t>Selsknösen, Vb</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>742018</v>
+        <v>742181</v>
       </c>
       <c r="R12" t="n">
-        <v>7112166</v>
+        <v>7112082</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1779,45 +1775,49 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>128115294</v>
+        <v>128115293</v>
       </c>
       <c r="B13" t="n">
-        <v>80036</v>
+        <v>57670</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6456</v>
+        <v>100049</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr"/>
+      <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>Selsknösen, Vb</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>742181</v>
+        <v>742018</v>
       </c>
       <c r="R13" t="n">
-        <v>7112082</v>
+        <v>7112166</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1879,7 +1879,7 @@
         <v>128115302</v>
       </c>
       <c r="B14" t="n">
-        <v>98470</v>
+        <v>98478</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1981,7 +1981,7 @@
         <v>128115367</v>
       </c>
       <c r="B15" t="n">
-        <v>57672</v>
+        <v>57673</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2091,7 +2091,7 @@
         <v>128115304</v>
       </c>
       <c r="B16" t="n">
-        <v>98470</v>
+        <v>98478</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2193,7 +2193,7 @@
         <v>128115314</v>
       </c>
       <c r="B17" t="n">
-        <v>98387</v>
+        <v>98395</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2290,7 +2290,7 @@
         <v>128115298</v>
       </c>
       <c r="B18" t="n">
-        <v>95702</v>
+        <v>95710</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2387,7 +2387,7 @@
         <v>128115288</v>
       </c>
       <c r="B19" t="n">
-        <v>96817</v>
+        <v>96825</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2485,7 +2485,7 @@
         <v>128115287</v>
       </c>
       <c r="B20" t="n">
-        <v>91317</v>
+        <v>91325</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2582,7 +2582,7 @@
         <v>128115286</v>
       </c>
       <c r="B21" t="n">
-        <v>91317</v>
+        <v>91325</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2679,7 +2679,7 @@
         <v>128115309</v>
       </c>
       <c r="B22" t="n">
-        <v>79029</v>
+        <v>79032</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2776,7 +2776,7 @@
         <v>128115313</v>
       </c>
       <c r="B23" t="n">
-        <v>82870</v>
+        <v>82873</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2873,7 +2873,7 @@
         <v>128314983</v>
       </c>
       <c r="B24" t="n">
-        <v>91710</v>
+        <v>91718</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2971,7 +2971,7 @@
         <v>128314982</v>
       </c>
       <c r="B25" t="n">
-        <v>91724</v>
+        <v>91732</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>

--- a/artfynd/A 38519-2025 artfynd.xlsx
+++ b/artfynd/A 38519-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128115307</v>
       </c>
       <c r="B2" t="n">
-        <v>91378</v>
+        <v>91470</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>128115310</v>
       </c>
       <c r="B3" t="n">
-        <v>79032</v>
+        <v>79083</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -869,49 +869,45 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>128115303</v>
+        <v>128115311</v>
       </c>
       <c r="B4" t="n">
-        <v>98478</v>
+        <v>79083</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
-      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Selsknösen, Vb</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>742050</v>
+        <v>742052</v>
       </c>
       <c r="R4" t="n">
-        <v>7111963</v>
+        <v>7112024</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -952,7 +948,6 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
-      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
@@ -971,10 +966,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128115305</v>
+        <v>128115303</v>
       </c>
       <c r="B5" t="n">
-        <v>98478</v>
+        <v>98571</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1010,10 +1005,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>741970</v>
+        <v>742050</v>
       </c>
       <c r="R5" t="n">
-        <v>7111969</v>
+        <v>7111963</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1073,45 +1068,49 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128115311</v>
+        <v>128115305</v>
       </c>
       <c r="B6" t="n">
-        <v>79032</v>
+        <v>98571</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Selsknösen, Vb</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>742052</v>
+        <v>741970</v>
       </c>
       <c r="R6" t="n">
-        <v>7112024</v>
+        <v>7111969</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1152,6 +1151,7 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
+      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -1173,7 +1173,7 @@
         <v>128115285</v>
       </c>
       <c r="B7" t="n">
-        <v>91325</v>
+        <v>91417</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1267,49 +1267,45 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>128115290</v>
+        <v>128115289</v>
       </c>
       <c r="B8" t="n">
-        <v>56864</v>
+        <v>91452</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100138</v>
+        <v>1202</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr"/>
-      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Selsknösen, Vb</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>742080</v>
+        <v>742020</v>
       </c>
       <c r="R8" t="n">
-        <v>7112234</v>
+        <v>7111950</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1344,17 +1340,13 @@
           <t>2025-08-27</t>
         </is>
       </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Fjäder funnen</t>
-        </is>
-      </c>
       <c r="AD8" t="b">
         <v>0</v>
       </c>
       <c r="AE8" t="b">
         <v>0</v>
       </c>
+      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
@@ -1373,32 +1365,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>128115289</v>
+        <v>128115299</v>
       </c>
       <c r="B9" t="n">
-        <v>91360</v>
+        <v>80224</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1202</v>
+        <v>6464</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1408,10 +1400,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>742020</v>
+        <v>742269</v>
       </c>
       <c r="R9" t="n">
-        <v>7111950</v>
+        <v>7112162</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1452,7 +1444,6 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
-      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
@@ -1471,10 +1462,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>128115299</v>
+        <v>128115290</v>
       </c>
       <c r="B10" t="n">
-        <v>80171</v>
+        <v>56876</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1482,34 +1473,38 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6464</v>
+        <v>100138</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr"/>
+      <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Selsknösen, Vb</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>742269</v>
+        <v>742080</v>
       </c>
       <c r="R10" t="n">
-        <v>7112162</v>
+        <v>7112234</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1542,6 +1537,11 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-08-27</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Fjäder funnen</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1571,7 +1571,7 @@
         <v>128115295</v>
       </c>
       <c r="B11" t="n">
-        <v>57673</v>
+        <v>57685</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1678,45 +1678,49 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>128115294</v>
+        <v>128115293</v>
       </c>
       <c r="B12" t="n">
-        <v>80039</v>
+        <v>57682</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6456</v>
+        <v>100049</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr"/>
+      <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
           <t>Selsknösen, Vb</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>742181</v>
+        <v>742018</v>
       </c>
       <c r="R12" t="n">
-        <v>7112082</v>
+        <v>7112166</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1775,49 +1779,45 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>128115293</v>
+        <v>128115294</v>
       </c>
       <c r="B13" t="n">
-        <v>57670</v>
+        <v>80092</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100049</v>
+        <v>6456</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="K13" t="inlineStr"/>
-      <c r="L13" t="inlineStr"/>
-      <c r="M13" t="inlineStr"/>
-      <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>Selsknösen, Vb</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>742018</v>
+        <v>742181</v>
       </c>
       <c r="R13" t="n">
-        <v>7112166</v>
+        <v>7112082</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1879,7 +1879,7 @@
         <v>128115302</v>
       </c>
       <c r="B14" t="n">
-        <v>98478</v>
+        <v>98571</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1981,7 +1981,7 @@
         <v>128115367</v>
       </c>
       <c r="B15" t="n">
-        <v>57673</v>
+        <v>57685</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2091,7 +2091,7 @@
         <v>128115304</v>
       </c>
       <c r="B16" t="n">
-        <v>98478</v>
+        <v>98571</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2193,7 +2193,7 @@
         <v>128115314</v>
       </c>
       <c r="B17" t="n">
-        <v>98395</v>
+        <v>98488</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2287,32 +2287,32 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>128115298</v>
+        <v>128115288</v>
       </c>
       <c r="B18" t="n">
-        <v>95710</v>
+        <v>96918</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>2809</v>
+        <v>1841</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Mörk husmossa</t>
+          <t>Vedflikmossa</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Hylocomiastrum umbratum</t>
+          <t>Lophozia guttulata</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Hedw.) M.Fleisch.</t>
+          <t>(Lindb. &amp; Arnell) A.Evans</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2322,10 +2322,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>742124</v>
+        <v>742438</v>
       </c>
       <c r="R18" t="n">
-        <v>7112073</v>
+        <v>7112145</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2366,6 +2366,7 @@
       <c r="AE18" t="b">
         <v>0</v>
       </c>
+      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>
@@ -2384,32 +2385,32 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>128115288</v>
+        <v>128115298</v>
       </c>
       <c r="B19" t="n">
-        <v>96825</v>
+        <v>95803</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>1841</v>
+        <v>2809</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Vedflikmossa</t>
+          <t>Mörk husmossa</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Lophozia guttulata</t>
+          <t>Hylocomiastrum umbratum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Lindb. &amp; Arnell) A.Evans</t>
+          <t>(Hedw.) M.Fleisch.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2419,10 +2420,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>742438</v>
+        <v>742124</v>
       </c>
       <c r="R19" t="n">
-        <v>7112145</v>
+        <v>7112073</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2463,7 +2464,6 @@
       <c r="AE19" t="b">
         <v>0</v>
       </c>
-      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
       </c>
@@ -2485,7 +2485,7 @@
         <v>128115287</v>
       </c>
       <c r="B20" t="n">
-        <v>91325</v>
+        <v>91417</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2582,7 +2582,7 @@
         <v>128115286</v>
       </c>
       <c r="B21" t="n">
-        <v>91325</v>
+        <v>91417</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2679,7 +2679,7 @@
         <v>128115309</v>
       </c>
       <c r="B22" t="n">
-        <v>79032</v>
+        <v>79083</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2776,7 +2776,7 @@
         <v>128115313</v>
       </c>
       <c r="B23" t="n">
-        <v>82873</v>
+        <v>82942</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2873,7 +2873,7 @@
         <v>128314983</v>
       </c>
       <c r="B24" t="n">
-        <v>91718</v>
+        <v>91810</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2971,7 +2971,7 @@
         <v>128314982</v>
       </c>
       <c r="B25" t="n">
-        <v>91732</v>
+        <v>91824</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>

--- a/artfynd/A 38519-2025 artfynd.xlsx
+++ b/artfynd/A 38519-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY25"/>
+  <dimension ref="A1:AY82"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -869,45 +869,49 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>128115311</v>
+        <v>128115303</v>
       </c>
       <c r="B4" t="n">
-        <v>79083</v>
+        <v>98571</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Selsknösen, Vb</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>742052</v>
+        <v>742050</v>
       </c>
       <c r="R4" t="n">
-        <v>7112024</v>
+        <v>7111963</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -948,6 +952,7 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
+      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
@@ -966,7 +971,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128115303</v>
+        <v>128115305</v>
       </c>
       <c r="B5" t="n">
         <v>98571</v>
@@ -1005,10 +1010,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>742050</v>
+        <v>741970</v>
       </c>
       <c r="R5" t="n">
-        <v>7111963</v>
+        <v>7111969</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1068,49 +1073,45 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128115305</v>
+        <v>128115311</v>
       </c>
       <c r="B6" t="n">
-        <v>98571</v>
+        <v>79083</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
-      <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
-      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Selsknösen, Vb</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>741970</v>
+        <v>742052</v>
       </c>
       <c r="R6" t="n">
-        <v>7111969</v>
+        <v>7112024</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1151,7 +1152,6 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
-      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -1267,32 +1267,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>128115289</v>
+        <v>128115299</v>
       </c>
       <c r="B8" t="n">
-        <v>91452</v>
+        <v>80224</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1202</v>
+        <v>6464</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1302,10 +1302,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>742020</v>
+        <v>742269</v>
       </c>
       <c r="R8" t="n">
-        <v>7111950</v>
+        <v>7112162</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1346,7 +1346,6 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
-      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
@@ -1365,10 +1364,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>128115299</v>
+        <v>128115290</v>
       </c>
       <c r="B9" t="n">
-        <v>80224</v>
+        <v>56876</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1376,34 +1375,38 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6464</v>
+        <v>100138</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr"/>
+      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Selsknösen, Vb</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>742269</v>
+        <v>742080</v>
       </c>
       <c r="R9" t="n">
-        <v>7112162</v>
+        <v>7112234</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1436,6 +1439,11 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-08-27</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Fjäder funnen</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1462,49 +1470,45 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>128115290</v>
+        <v>128115289</v>
       </c>
       <c r="B10" t="n">
-        <v>56876</v>
+        <v>91452</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100138</v>
+        <v>1202</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr"/>
-      <c r="M10" t="inlineStr"/>
-      <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Selsknösen, Vb</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>742080</v>
+        <v>742020</v>
       </c>
       <c r="R10" t="n">
-        <v>7112234</v>
+        <v>7111950</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1539,17 +1543,13 @@
           <t>2025-08-27</t>
         </is>
       </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Fjäder funnen</t>
-        </is>
-      </c>
       <c r="AD10" t="b">
         <v>0</v>
       </c>
       <c r="AE10" t="b">
         <v>0</v>
       </c>
+      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
@@ -1678,49 +1678,45 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>128115293</v>
+        <v>128115294</v>
       </c>
       <c r="B12" t="n">
-        <v>57682</v>
+        <v>80092</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100049</v>
+        <v>6456</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="K12" t="inlineStr"/>
-      <c r="L12" t="inlineStr"/>
-      <c r="M12" t="inlineStr"/>
-      <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
           <t>Selsknösen, Vb</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>742018</v>
+        <v>742181</v>
       </c>
       <c r="R12" t="n">
-        <v>7112166</v>
+        <v>7112082</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1779,45 +1775,49 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>128115294</v>
+        <v>128115293</v>
       </c>
       <c r="B13" t="n">
-        <v>80092</v>
+        <v>57682</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6456</v>
+        <v>100049</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr"/>
+      <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>Selsknösen, Vb</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>742181</v>
+        <v>742018</v>
       </c>
       <c r="R13" t="n">
-        <v>7112082</v>
+        <v>7112166</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1978,42 +1978,38 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>128115367</v>
+        <v>128115304</v>
       </c>
       <c r="B15" t="n">
-        <v>57685</v>
+        <v>98571</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr"/>
       <c r="K15" t="inlineStr"/>
       <c r="L15" t="inlineStr"/>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
       <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
@@ -2021,10 +2017,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>742063</v>
+        <v>741996</v>
       </c>
       <c r="R15" t="n">
-        <v>7111956</v>
+        <v>7111968</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2059,17 +2055,13 @@
           <t>2025-08-27</t>
         </is>
       </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
-        </is>
-      </c>
       <c r="AD15" t="b">
         <v>0</v>
       </c>
       <c r="AE15" t="b">
         <v>0</v>
       </c>
+      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
       </c>
@@ -2088,38 +2080,42 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>128115304</v>
+        <v>128115367</v>
       </c>
       <c r="B16" t="n">
-        <v>98571</v>
+        <v>57685</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="J16" t="inlineStr"/>
       <c r="K16" t="inlineStr"/>
       <c r="L16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
@@ -2127,10 +2123,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>741996</v>
+        <v>742063</v>
       </c>
       <c r="R16" t="n">
-        <v>7111968</v>
+        <v>7111956</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2165,13 +2161,17 @@
           <t>2025-08-27</t>
         </is>
       </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
+        </is>
+      </c>
       <c r="AD16" t="b">
         <v>0</v>
       </c>
       <c r="AE16" t="b">
         <v>0</v>
       </c>
-      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
@@ -2870,10 +2870,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>128314983</v>
+        <v>128120500</v>
       </c>
       <c r="B24" t="n">
-        <v>91810</v>
+        <v>98571</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2881,34 +2881,38 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>2062</v>
+        <v>220787</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Ulltickeporing</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Skeletocutis brevispora</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
+      <c r="J24" t="inlineStr"/>
+      <c r="K24" t="inlineStr"/>
+      <c r="L24" t="inlineStr"/>
+      <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
           <t>Selsknösen, Vb</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>742315</v>
+        <v>741939</v>
       </c>
       <c r="R24" t="n">
-        <v>7112279</v>
+        <v>7111973</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -2935,12 +2939,17 @@
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>2025-08-27</t>
+          <t>2025-08-23</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>2025-08-27</t>
+          <t>2025-08-23</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -2956,44 +2965,44 @@
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Maria Wikdahl</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Maria Wikdahl</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>128314982</v>
+        <v>128120479</v>
       </c>
       <c r="B25" t="n">
-        <v>91824</v>
+        <v>80217</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>1505</v>
+        <v>6462</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Kristallticka</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Skeletocutis stellae</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Pilát) Jean Keller</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3003,10 +3012,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>742153</v>
+        <v>741958</v>
       </c>
       <c r="R25" t="n">
-        <v>7112076</v>
+        <v>7111915</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3047,21 +3056,5741 @@
       <c r="AE25" t="b">
         <v>0</v>
       </c>
+      <c r="AF25" t="inlineStr"/>
       <c r="AG25" t="b">
         <v>0</v>
       </c>
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
+          <t>Maria Wikdahl</t>
+        </is>
+      </c>
+      <c r="AX25" t="inlineStr">
+        <is>
+          <t>Maria Wikdahl</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>128120481</v>
+      </c>
+      <c r="B26" t="n">
+        <v>57682</v>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
+      <c r="K26" t="inlineStr"/>
+      <c r="L26" t="inlineStr"/>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N26" t="inlineStr"/>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>Selsknösen, Vb</t>
+        </is>
+      </c>
+      <c r="Q26" t="n">
+        <v>742368</v>
+      </c>
+      <c r="R26" t="n">
+        <v>7112244</v>
+      </c>
+      <c r="S26" t="n">
+        <v>10</v>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>Umeå</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>Umeå socken</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>2025-08-27</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>2025-08-27</t>
+        </is>
+      </c>
+      <c r="AD26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT26" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>Maria Wikdahl</t>
+        </is>
+      </c>
+      <c r="AX26" t="inlineStr">
+        <is>
+          <t>Maria Wikdahl</t>
+        </is>
+      </c>
+      <c r="AY26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>128120473</v>
+      </c>
+      <c r="B27" t="n">
+        <v>57685</v>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
+      <c r="K27" t="inlineStr"/>
+      <c r="L27" t="inlineStr"/>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N27" t="inlineStr"/>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>Selsknösen, Vb</t>
+        </is>
+      </c>
+      <c r="Q27" t="n">
+        <v>742178</v>
+      </c>
+      <c r="R27" t="n">
+        <v>7112150</v>
+      </c>
+      <c r="S27" t="n">
+        <v>10</v>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>Umeå</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>Umeå socken</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>2025-08-23</t>
+        </is>
+      </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>2025-08-23</t>
+        </is>
+      </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
+        </is>
+      </c>
+      <c r="AD27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT27" t="inlineStr"/>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>Maria Wikdahl</t>
+        </is>
+      </c>
+      <c r="AX27" t="inlineStr">
+        <is>
+          <t>Maria Wikdahl</t>
+        </is>
+      </c>
+      <c r="AY27" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>128120471</v>
+      </c>
+      <c r="B28" t="n">
+        <v>57685</v>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
+      <c r="K28" t="inlineStr"/>
+      <c r="L28" t="inlineStr"/>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N28" t="inlineStr"/>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>Selsknösen, Vb</t>
+        </is>
+      </c>
+      <c r="Q28" t="n">
+        <v>742171</v>
+      </c>
+      <c r="R28" t="n">
+        <v>7112018</v>
+      </c>
+      <c r="S28" t="n">
+        <v>10</v>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>Umeå</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>Umeå socken</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>2025-08-27</t>
+        </is>
+      </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>2025-08-27</t>
+        </is>
+      </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>Ringhacksliknande på gran.</t>
+        </is>
+      </c>
+      <c r="AD28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT28" t="inlineStr"/>
+      <c r="AW28" t="inlineStr">
+        <is>
+          <t>Maria Wikdahl</t>
+        </is>
+      </c>
+      <c r="AX28" t="inlineStr">
+        <is>
+          <t>Maria Wikdahl</t>
+        </is>
+      </c>
+      <c r="AY28" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>128120482</v>
+      </c>
+      <c r="B29" t="n">
+        <v>57682</v>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
+      <c r="K29" t="inlineStr"/>
+      <c r="L29" t="inlineStr"/>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N29" t="inlineStr"/>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>Selsknösen, Vb</t>
+        </is>
+      </c>
+      <c r="Q29" t="n">
+        <v>742472</v>
+      </c>
+      <c r="R29" t="n">
+        <v>7112117</v>
+      </c>
+      <c r="S29" t="n">
+        <v>10</v>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>Umeå</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W29" t="inlineStr">
+        <is>
+          <t>Umeå socken</t>
+        </is>
+      </c>
+      <c r="Y29" t="inlineStr">
+        <is>
+          <t>2025-08-27</t>
+        </is>
+      </c>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>2025-08-27</t>
+        </is>
+      </c>
+      <c r="AD29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT29" t="inlineStr"/>
+      <c r="AW29" t="inlineStr">
+        <is>
+          <t>Maria Wikdahl</t>
+        </is>
+      </c>
+      <c r="AX29" t="inlineStr">
+        <is>
+          <t>Maria Wikdahl</t>
+        </is>
+      </c>
+      <c r="AY29" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>128120464</v>
+      </c>
+      <c r="B30" t="n">
+        <v>91417</v>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>5447</v>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Vedticka</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Fuscoporia viticola</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>Selsknösen, Vb</t>
+        </is>
+      </c>
+      <c r="Q30" t="n">
+        <v>742344</v>
+      </c>
+      <c r="R30" t="n">
+        <v>7112196</v>
+      </c>
+      <c r="S30" t="n">
+        <v>10</v>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>Umeå</t>
+        </is>
+      </c>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W30" t="inlineStr">
+        <is>
+          <t>Umeå socken</t>
+        </is>
+      </c>
+      <c r="Y30" t="inlineStr">
+        <is>
+          <t>2025-08-27</t>
+        </is>
+      </c>
+      <c r="AA30" t="inlineStr">
+        <is>
+          <t>2025-08-27</t>
+        </is>
+      </c>
+      <c r="AD30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT30" t="inlineStr"/>
+      <c r="AW30" t="inlineStr">
+        <is>
+          <t>Maria Wikdahl</t>
+        </is>
+      </c>
+      <c r="AX30" t="inlineStr">
+        <is>
+          <t>Maria Wikdahl</t>
+        </is>
+      </c>
+      <c r="AY30" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>128120512</v>
+      </c>
+      <c r="B31" t="n">
+        <v>91470</v>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>5432</v>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Granticka</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Porodaedalea chrysoloma</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>Selsknösen, Vb</t>
+        </is>
+      </c>
+      <c r="Q31" t="n">
+        <v>742457</v>
+      </c>
+      <c r="R31" t="n">
+        <v>7112145</v>
+      </c>
+      <c r="S31" t="n">
+        <v>10</v>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>Umeå</t>
+        </is>
+      </c>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W31" t="inlineStr">
+        <is>
+          <t>Umeå socken</t>
+        </is>
+      </c>
+      <c r="Y31" t="inlineStr">
+        <is>
+          <t>2025-08-27</t>
+        </is>
+      </c>
+      <c r="AA31" t="inlineStr">
+        <is>
+          <t>2025-08-27</t>
+        </is>
+      </c>
+      <c r="AD31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT31" t="inlineStr"/>
+      <c r="AW31" t="inlineStr">
+        <is>
+          <t>Maria Wikdahl</t>
+        </is>
+      </c>
+      <c r="AX31" t="inlineStr">
+        <is>
+          <t>Maria Wikdahl</t>
+        </is>
+      </c>
+      <c r="AY31" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>128120494</v>
+      </c>
+      <c r="B32" t="n">
+        <v>80188</v>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E32" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>Selsknösen, Vb</t>
+        </is>
+      </c>
+      <c r="Q32" t="n">
+        <v>741962</v>
+      </c>
+      <c r="R32" t="n">
+        <v>7111966</v>
+      </c>
+      <c r="S32" t="n">
+        <v>10</v>
+      </c>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>Umeå</t>
+        </is>
+      </c>
+      <c r="V32" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W32" t="inlineStr">
+        <is>
+          <t>Umeå socken</t>
+        </is>
+      </c>
+      <c r="Y32" t="inlineStr">
+        <is>
+          <t>2025-08-27</t>
+        </is>
+      </c>
+      <c r="AA32" t="inlineStr">
+        <is>
+          <t>2025-08-27</t>
+        </is>
+      </c>
+      <c r="AD32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT32" t="inlineStr"/>
+      <c r="AW32" t="inlineStr">
+        <is>
+          <t>Maria Wikdahl</t>
+        </is>
+      </c>
+      <c r="AX32" t="inlineStr">
+        <is>
+          <t>Maria Wikdahl</t>
+        </is>
+      </c>
+      <c r="AY32" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>128120489</v>
+      </c>
+      <c r="B33" t="n">
+        <v>57682</v>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E33" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr"/>
+      <c r="K33" t="inlineStr"/>
+      <c r="L33" t="inlineStr"/>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N33" t="inlineStr"/>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>Selsknösen, Vb</t>
+        </is>
+      </c>
+      <c r="Q33" t="n">
+        <v>742176</v>
+      </c>
+      <c r="R33" t="n">
+        <v>7112009</v>
+      </c>
+      <c r="S33" t="n">
+        <v>10</v>
+      </c>
+      <c r="T33" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U33" t="inlineStr">
+        <is>
+          <t>Umeå</t>
+        </is>
+      </c>
+      <c r="V33" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W33" t="inlineStr">
+        <is>
+          <t>Umeå socken</t>
+        </is>
+      </c>
+      <c r="Y33" t="inlineStr">
+        <is>
+          <t>2025-08-27</t>
+        </is>
+      </c>
+      <c r="AA33" t="inlineStr">
+        <is>
+          <t>2025-08-27</t>
+        </is>
+      </c>
+      <c r="AD33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT33" t="inlineStr"/>
+      <c r="AW33" t="inlineStr">
+        <is>
+          <t>Maria Wikdahl</t>
+        </is>
+      </c>
+      <c r="AX33" t="inlineStr">
+        <is>
+          <t>Maria Wikdahl</t>
+        </is>
+      </c>
+      <c r="AY33" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>128120515</v>
+      </c>
+      <c r="B34" t="n">
+        <v>91470</v>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E34" t="n">
+        <v>5432</v>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Granticka</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>Porodaedalea chrysoloma</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr"/>
+      <c r="P34" t="inlineStr">
+        <is>
+          <t>Selsknösen, Vb</t>
+        </is>
+      </c>
+      <c r="Q34" t="n">
+        <v>741977</v>
+      </c>
+      <c r="R34" t="n">
+        <v>7111967</v>
+      </c>
+      <c r="S34" t="n">
+        <v>10</v>
+      </c>
+      <c r="T34" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U34" t="inlineStr">
+        <is>
+          <t>Umeå</t>
+        </is>
+      </c>
+      <c r="V34" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W34" t="inlineStr">
+        <is>
+          <t>Umeå socken</t>
+        </is>
+      </c>
+      <c r="Y34" t="inlineStr">
+        <is>
+          <t>2025-08-23</t>
+        </is>
+      </c>
+      <c r="AA34" t="inlineStr">
+        <is>
+          <t>2025-08-23</t>
+        </is>
+      </c>
+      <c r="AD34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT34" t="inlineStr"/>
+      <c r="AW34" t="inlineStr">
+        <is>
+          <t>Maria Wikdahl</t>
+        </is>
+      </c>
+      <c r="AX34" t="inlineStr">
+        <is>
+          <t>Maria Wikdahl</t>
+        </is>
+      </c>
+      <c r="AY34" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>128120498</v>
+      </c>
+      <c r="B35" t="n">
+        <v>98571</v>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E35" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr"/>
+      <c r="P35" t="inlineStr">
+        <is>
+          <t>Selsknösen, Vb</t>
+        </is>
+      </c>
+      <c r="Q35" t="n">
+        <v>742472</v>
+      </c>
+      <c r="R35" t="n">
+        <v>7112142</v>
+      </c>
+      <c r="S35" t="n">
+        <v>10</v>
+      </c>
+      <c r="T35" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U35" t="inlineStr">
+        <is>
+          <t>Umeå</t>
+        </is>
+      </c>
+      <c r="V35" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W35" t="inlineStr">
+        <is>
+          <t>Umeå socken</t>
+        </is>
+      </c>
+      <c r="Y35" t="inlineStr">
+        <is>
+          <t>2025-08-27</t>
+        </is>
+      </c>
+      <c r="AA35" t="inlineStr">
+        <is>
+          <t>2025-08-27</t>
+        </is>
+      </c>
+      <c r="AC35" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
+        </is>
+      </c>
+      <c r="AD35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF35" t="inlineStr"/>
+      <c r="AG35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT35" t="inlineStr"/>
+      <c r="AW35" t="inlineStr">
+        <is>
+          <t>Maria Wikdahl</t>
+        </is>
+      </c>
+      <c r="AX35" t="inlineStr">
+        <is>
+          <t>Maria Wikdahl</t>
+        </is>
+      </c>
+      <c r="AY35" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>128120497</v>
+      </c>
+      <c r="B36" t="n">
+        <v>58055</v>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E36" t="n">
+        <v>103015</v>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Kungsfågel</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>Regulus regulus</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr"/>
+      <c r="P36" t="inlineStr">
+        <is>
+          <t>Selsknösen, Vb</t>
+        </is>
+      </c>
+      <c r="Q36" t="n">
+        <v>741902</v>
+      </c>
+      <c r="R36" t="n">
+        <v>7111998</v>
+      </c>
+      <c r="S36" t="n">
+        <v>10</v>
+      </c>
+      <c r="T36" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U36" t="inlineStr">
+        <is>
+          <t>Umeå</t>
+        </is>
+      </c>
+      <c r="V36" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W36" t="inlineStr">
+        <is>
+          <t>Umeå socken</t>
+        </is>
+      </c>
+      <c r="Y36" t="inlineStr">
+        <is>
+          <t>2025-08-27</t>
+        </is>
+      </c>
+      <c r="AA36" t="inlineStr">
+        <is>
+          <t>2025-08-27</t>
+        </is>
+      </c>
+      <c r="AD36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT36" t="inlineStr"/>
+      <c r="AW36" t="inlineStr">
+        <is>
+          <t>Maria Wikdahl</t>
+        </is>
+      </c>
+      <c r="AX36" t="inlineStr">
+        <is>
+          <t>Maria Wikdahl</t>
+        </is>
+      </c>
+      <c r="AY36" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>128120463</v>
+      </c>
+      <c r="B37" t="n">
+        <v>91417</v>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E37" t="n">
+        <v>5447</v>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>Vedticka</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>Fuscoporia viticola</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr"/>
+      <c r="P37" t="inlineStr">
+        <is>
+          <t>Selsknösen, Vb</t>
+        </is>
+      </c>
+      <c r="Q37" t="n">
+        <v>742161</v>
+      </c>
+      <c r="R37" t="n">
+        <v>7112190</v>
+      </c>
+      <c r="S37" t="n">
+        <v>10</v>
+      </c>
+      <c r="T37" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U37" t="inlineStr">
+        <is>
+          <t>Umeå</t>
+        </is>
+      </c>
+      <c r="V37" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W37" t="inlineStr">
+        <is>
+          <t>Umeå socken</t>
+        </is>
+      </c>
+      <c r="Y37" t="inlineStr">
+        <is>
+          <t>2025-08-27</t>
+        </is>
+      </c>
+      <c r="AA37" t="inlineStr">
+        <is>
+          <t>2025-08-27</t>
+        </is>
+      </c>
+      <c r="AD37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT37" t="inlineStr"/>
+      <c r="AW37" t="inlineStr">
+        <is>
+          <t>Maria Wikdahl</t>
+        </is>
+      </c>
+      <c r="AX37" t="inlineStr">
+        <is>
+          <t>Maria Wikdahl</t>
+        </is>
+      </c>
+      <c r="AY37" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>128120504</v>
+      </c>
+      <c r="B38" t="n">
+        <v>98571</v>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E38" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>Selsknösen, Vb</t>
+        </is>
+      </c>
+      <c r="Q38" t="n">
+        <v>741998</v>
+      </c>
+      <c r="R38" t="n">
+        <v>7111958</v>
+      </c>
+      <c r="S38" t="n">
+        <v>10</v>
+      </c>
+      <c r="T38" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U38" t="inlineStr">
+        <is>
+          <t>Umeå</t>
+        </is>
+      </c>
+      <c r="V38" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W38" t="inlineStr">
+        <is>
+          <t>Umeå socken</t>
+        </is>
+      </c>
+      <c r="Y38" t="inlineStr">
+        <is>
+          <t>2025-08-27</t>
+        </is>
+      </c>
+      <c r="AA38" t="inlineStr">
+        <is>
+          <t>2025-08-27</t>
+        </is>
+      </c>
+      <c r="AD38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF38" t="inlineStr"/>
+      <c r="AG38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT38" t="inlineStr"/>
+      <c r="AW38" t="inlineStr">
+        <is>
+          <t>Maria Wikdahl</t>
+        </is>
+      </c>
+      <c r="AX38" t="inlineStr">
+        <is>
+          <t>Maria Wikdahl</t>
+        </is>
+      </c>
+      <c r="AY38" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>128120509</v>
+      </c>
+      <c r="B39" t="n">
+        <v>98571</v>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E39" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr"/>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>Selsknösen, Vb</t>
+        </is>
+      </c>
+      <c r="Q39" t="n">
+        <v>742189</v>
+      </c>
+      <c r="R39" t="n">
+        <v>7112063</v>
+      </c>
+      <c r="S39" t="n">
+        <v>10</v>
+      </c>
+      <c r="T39" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U39" t="inlineStr">
+        <is>
+          <t>Umeå</t>
+        </is>
+      </c>
+      <c r="V39" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W39" t="inlineStr">
+        <is>
+          <t>Umeå socken</t>
+        </is>
+      </c>
+      <c r="Y39" t="inlineStr">
+        <is>
+          <t>2025-08-27</t>
+        </is>
+      </c>
+      <c r="AA39" t="inlineStr">
+        <is>
+          <t>2025-08-27</t>
+        </is>
+      </c>
+      <c r="AD39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT39" t="inlineStr"/>
+      <c r="AW39" t="inlineStr">
+        <is>
+          <t>Maria Wikdahl</t>
+        </is>
+      </c>
+      <c r="AX39" t="inlineStr">
+        <is>
+          <t>Maria Wikdahl</t>
+        </is>
+      </c>
+      <c r="AY39" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>128120469</v>
+      </c>
+      <c r="B40" t="n">
+        <v>91452</v>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E40" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr"/>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>Selsknösen, Vb</t>
+        </is>
+      </c>
+      <c r="Q40" t="n">
+        <v>742088</v>
+      </c>
+      <c r="R40" t="n">
+        <v>7111972</v>
+      </c>
+      <c r="S40" t="n">
+        <v>10</v>
+      </c>
+      <c r="T40" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U40" t="inlineStr">
+        <is>
+          <t>Umeå</t>
+        </is>
+      </c>
+      <c r="V40" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W40" t="inlineStr">
+        <is>
+          <t>Umeå socken</t>
+        </is>
+      </c>
+      <c r="Y40" t="inlineStr">
+        <is>
+          <t>2025-08-27</t>
+        </is>
+      </c>
+      <c r="AA40" t="inlineStr">
+        <is>
+          <t>2025-08-27</t>
+        </is>
+      </c>
+      <c r="AD40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT40" t="inlineStr"/>
+      <c r="AW40" t="inlineStr">
+        <is>
+          <t>Maria Wikdahl</t>
+        </is>
+      </c>
+      <c r="AX40" t="inlineStr">
+        <is>
+          <t>Maria Wikdahl</t>
+        </is>
+      </c>
+      <c r="AY40" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>128120517</v>
+      </c>
+      <c r="B41" t="n">
+        <v>91470</v>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E41" t="n">
+        <v>5432</v>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>Granticka</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>Porodaedalea chrysoloma</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr"/>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>Selsknösen, Vb</t>
+        </is>
+      </c>
+      <c r="Q41" t="n">
+        <v>741968</v>
+      </c>
+      <c r="R41" t="n">
+        <v>7111957</v>
+      </c>
+      <c r="S41" t="n">
+        <v>10</v>
+      </c>
+      <c r="T41" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U41" t="inlineStr">
+        <is>
+          <t>Umeå</t>
+        </is>
+      </c>
+      <c r="V41" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W41" t="inlineStr">
+        <is>
+          <t>Umeå socken</t>
+        </is>
+      </c>
+      <c r="Y41" t="inlineStr">
+        <is>
+          <t>2025-08-27</t>
+        </is>
+      </c>
+      <c r="AA41" t="inlineStr">
+        <is>
+          <t>2025-08-27</t>
+        </is>
+      </c>
+      <c r="AD41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT41" t="inlineStr"/>
+      <c r="AW41" t="inlineStr">
+        <is>
+          <t>Maria Wikdahl</t>
+        </is>
+      </c>
+      <c r="AX41" t="inlineStr">
+        <is>
+          <t>Maria Wikdahl</t>
+        </is>
+      </c>
+      <c r="AY41" t="inlineStr"/>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>128120484</v>
+      </c>
+      <c r="B42" t="n">
+        <v>57682</v>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E42" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr"/>
+      <c r="K42" t="inlineStr"/>
+      <c r="L42" t="inlineStr"/>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N42" t="inlineStr"/>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>Selsknösen, Vb</t>
+        </is>
+      </c>
+      <c r="Q42" t="n">
+        <v>741951</v>
+      </c>
+      <c r="R42" t="n">
+        <v>7111949</v>
+      </c>
+      <c r="S42" t="n">
+        <v>10</v>
+      </c>
+      <c r="T42" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U42" t="inlineStr">
+        <is>
+          <t>Umeå</t>
+        </is>
+      </c>
+      <c r="V42" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W42" t="inlineStr">
+        <is>
+          <t>Umeå socken</t>
+        </is>
+      </c>
+      <c r="Y42" t="inlineStr">
+        <is>
+          <t>2025-08-27</t>
+        </is>
+      </c>
+      <c r="AA42" t="inlineStr">
+        <is>
+          <t>2025-08-27</t>
+        </is>
+      </c>
+      <c r="AD42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT42" t="inlineStr"/>
+      <c r="AW42" t="inlineStr">
+        <is>
+          <t>Maria Wikdahl</t>
+        </is>
+      </c>
+      <c r="AX42" t="inlineStr">
+        <is>
+          <t>Maria Wikdahl</t>
+        </is>
+      </c>
+      <c r="AY42" t="inlineStr"/>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>128120467</v>
+      </c>
+      <c r="B43" t="n">
+        <v>91452</v>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E43" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr"/>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>Selsknösen, Vb</t>
+        </is>
+      </c>
+      <c r="Q43" t="n">
+        <v>742208</v>
+      </c>
+      <c r="R43" t="n">
+        <v>7112210</v>
+      </c>
+      <c r="S43" t="n">
+        <v>10</v>
+      </c>
+      <c r="T43" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U43" t="inlineStr">
+        <is>
+          <t>Umeå</t>
+        </is>
+      </c>
+      <c r="V43" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W43" t="inlineStr">
+        <is>
+          <t>Umeå socken</t>
+        </is>
+      </c>
+      <c r="Y43" t="inlineStr">
+        <is>
+          <t>2025-08-23</t>
+        </is>
+      </c>
+      <c r="AA43" t="inlineStr">
+        <is>
+          <t>2025-08-23</t>
+        </is>
+      </c>
+      <c r="AD43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT43" t="inlineStr"/>
+      <c r="AW43" t="inlineStr">
+        <is>
+          <t>Maria Wikdahl</t>
+        </is>
+      </c>
+      <c r="AX43" t="inlineStr">
+        <is>
+          <t>Maria Wikdahl</t>
+        </is>
+      </c>
+      <c r="AY43" t="inlineStr"/>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>128120483</v>
+      </c>
+      <c r="B44" t="n">
+        <v>57682</v>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E44" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr"/>
+      <c r="K44" t="inlineStr"/>
+      <c r="L44" t="inlineStr"/>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N44" t="inlineStr"/>
+      <c r="P44" t="inlineStr">
+        <is>
+          <t>Selsknösen, Vb</t>
+        </is>
+      </c>
+      <c r="Q44" t="n">
+        <v>742340</v>
+      </c>
+      <c r="R44" t="n">
+        <v>7112183</v>
+      </c>
+      <c r="S44" t="n">
+        <v>10</v>
+      </c>
+      <c r="T44" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U44" t="inlineStr">
+        <is>
+          <t>Umeå</t>
+        </is>
+      </c>
+      <c r="V44" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W44" t="inlineStr">
+        <is>
+          <t>Umeå socken</t>
+        </is>
+      </c>
+      <c r="Y44" t="inlineStr">
+        <is>
+          <t>2025-08-27</t>
+        </is>
+      </c>
+      <c r="AA44" t="inlineStr">
+        <is>
+          <t>2025-08-27</t>
+        </is>
+      </c>
+      <c r="AD44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT44" t="inlineStr"/>
+      <c r="AW44" t="inlineStr">
+        <is>
+          <t>Maria Wikdahl</t>
+        </is>
+      </c>
+      <c r="AX44" t="inlineStr">
+        <is>
+          <t>Maria Wikdahl</t>
+        </is>
+      </c>
+      <c r="AY44" t="inlineStr"/>
+    </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>128120507</v>
+      </c>
+      <c r="B45" t="n">
+        <v>98571</v>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E45" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr"/>
+      <c r="P45" t="inlineStr">
+        <is>
+          <t>Selsknösen, Vb</t>
+        </is>
+      </c>
+      <c r="Q45" t="n">
+        <v>742163</v>
+      </c>
+      <c r="R45" t="n">
+        <v>7112200</v>
+      </c>
+      <c r="S45" t="n">
+        <v>10</v>
+      </c>
+      <c r="T45" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U45" t="inlineStr">
+        <is>
+          <t>Umeå</t>
+        </is>
+      </c>
+      <c r="V45" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W45" t="inlineStr">
+        <is>
+          <t>Umeå socken</t>
+        </is>
+      </c>
+      <c r="Y45" t="inlineStr">
+        <is>
+          <t>2025-08-27</t>
+        </is>
+      </c>
+      <c r="AA45" t="inlineStr">
+        <is>
+          <t>2025-08-27</t>
+        </is>
+      </c>
+      <c r="AD45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT45" t="inlineStr"/>
+      <c r="AW45" t="inlineStr">
+        <is>
+          <t>Maria Wikdahl</t>
+        </is>
+      </c>
+      <c r="AX45" t="inlineStr">
+        <is>
+          <t>Maria Wikdahl</t>
+        </is>
+      </c>
+      <c r="AY45" t="inlineStr"/>
+    </row>
+    <row r="46">
+      <c r="A46" t="n">
+        <v>128120513</v>
+      </c>
+      <c r="B46" t="n">
+        <v>91470</v>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E46" t="n">
+        <v>5432</v>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>Granticka</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>Porodaedalea chrysoloma</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr"/>
+      <c r="P46" t="inlineStr">
+        <is>
+          <t>Selsknösen, Vb</t>
+        </is>
+      </c>
+      <c r="Q46" t="n">
+        <v>742161</v>
+      </c>
+      <c r="R46" t="n">
+        <v>7112111</v>
+      </c>
+      <c r="S46" t="n">
+        <v>10</v>
+      </c>
+      <c r="T46" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U46" t="inlineStr">
+        <is>
+          <t>Umeå</t>
+        </is>
+      </c>
+      <c r="V46" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W46" t="inlineStr">
+        <is>
+          <t>Umeå socken</t>
+        </is>
+      </c>
+      <c r="Y46" t="inlineStr">
+        <is>
+          <t>2025-08-27</t>
+        </is>
+      </c>
+      <c r="AA46" t="inlineStr">
+        <is>
+          <t>2025-08-27</t>
+        </is>
+      </c>
+      <c r="AD46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT46" t="inlineStr"/>
+      <c r="AW46" t="inlineStr">
+        <is>
+          <t>Maria Wikdahl</t>
+        </is>
+      </c>
+      <c r="AX46" t="inlineStr">
+        <is>
+          <t>Maria Wikdahl</t>
+        </is>
+      </c>
+      <c r="AY46" t="inlineStr"/>
+    </row>
+    <row r="47">
+      <c r="A47" t="n">
+        <v>128120514</v>
+      </c>
+      <c r="B47" t="n">
+        <v>91470</v>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E47" t="n">
+        <v>5432</v>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>Granticka</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>Porodaedalea chrysoloma</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr"/>
+      <c r="P47" t="inlineStr">
+        <is>
+          <t>Selsknösen, Vb</t>
+        </is>
+      </c>
+      <c r="Q47" t="n">
+        <v>742136</v>
+      </c>
+      <c r="R47" t="n">
+        <v>7112081</v>
+      </c>
+      <c r="S47" t="n">
+        <v>10</v>
+      </c>
+      <c r="T47" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U47" t="inlineStr">
+        <is>
+          <t>Umeå</t>
+        </is>
+      </c>
+      <c r="V47" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W47" t="inlineStr">
+        <is>
+          <t>Umeå socken</t>
+        </is>
+      </c>
+      <c r="Y47" t="inlineStr">
+        <is>
+          <t>2025-08-23</t>
+        </is>
+      </c>
+      <c r="AA47" t="inlineStr">
+        <is>
+          <t>2025-08-23</t>
+        </is>
+      </c>
+      <c r="AD47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT47" t="inlineStr"/>
+      <c r="AW47" t="inlineStr">
+        <is>
+          <t>Maria Wikdahl</t>
+        </is>
+      </c>
+      <c r="AX47" t="inlineStr">
+        <is>
+          <t>Maria Wikdahl</t>
+        </is>
+      </c>
+      <c r="AY47" t="inlineStr"/>
+    </row>
+    <row r="48">
+      <c r="A48" t="n">
+        <v>128120531</v>
+      </c>
+      <c r="B48" t="n">
+        <v>80223</v>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E48" t="n">
+        <v>6463</v>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>Bårdlav</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>Nephroma parile</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr"/>
+      <c r="P48" t="inlineStr">
+        <is>
+          <t>Selsknösen, Vb</t>
+        </is>
+      </c>
+      <c r="Q48" t="n">
+        <v>741963</v>
+      </c>
+      <c r="R48" t="n">
+        <v>7111967</v>
+      </c>
+      <c r="S48" t="n">
+        <v>10</v>
+      </c>
+      <c r="T48" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U48" t="inlineStr">
+        <is>
+          <t>Umeå</t>
+        </is>
+      </c>
+      <c r="V48" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W48" t="inlineStr">
+        <is>
+          <t>Umeå socken</t>
+        </is>
+      </c>
+      <c r="Y48" t="inlineStr">
+        <is>
+          <t>2025-08-27</t>
+        </is>
+      </c>
+      <c r="AA48" t="inlineStr">
+        <is>
+          <t>2025-08-27</t>
+        </is>
+      </c>
+      <c r="AD48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT48" t="inlineStr"/>
+      <c r="AW48" t="inlineStr">
+        <is>
+          <t>Maria Wikdahl</t>
+        </is>
+      </c>
+      <c r="AX48" t="inlineStr">
+        <is>
+          <t>Maria Wikdahl</t>
+        </is>
+      </c>
+      <c r="AY48" t="inlineStr"/>
+    </row>
+    <row r="49">
+      <c r="A49" t="n">
+        <v>128120524</v>
+      </c>
+      <c r="B49" t="n">
+        <v>79083</v>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E49" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr"/>
+      <c r="P49" t="inlineStr">
+        <is>
+          <t>Selsknösen, Vb</t>
+        </is>
+      </c>
+      <c r="Q49" t="n">
+        <v>742089</v>
+      </c>
+      <c r="R49" t="n">
+        <v>7112176</v>
+      </c>
+      <c r="S49" t="n">
+        <v>10</v>
+      </c>
+      <c r="T49" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U49" t="inlineStr">
+        <is>
+          <t>Umeå</t>
+        </is>
+      </c>
+      <c r="V49" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W49" t="inlineStr">
+        <is>
+          <t>Umeå socken</t>
+        </is>
+      </c>
+      <c r="Y49" t="inlineStr">
+        <is>
+          <t>2025-08-23</t>
+        </is>
+      </c>
+      <c r="AA49" t="inlineStr">
+        <is>
+          <t>2025-08-23</t>
+        </is>
+      </c>
+      <c r="AD49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT49" t="inlineStr"/>
+      <c r="AW49" t="inlineStr">
+        <is>
+          <t>Maria Wikdahl</t>
+        </is>
+      </c>
+      <c r="AX49" t="inlineStr">
+        <is>
+          <t>Maria Wikdahl</t>
+        </is>
+      </c>
+      <c r="AY49" t="inlineStr"/>
+    </row>
+    <row r="50">
+      <c r="A50" t="n">
+        <v>128120488</v>
+      </c>
+      <c r="B50" t="n">
+        <v>57682</v>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E50" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr"/>
+      <c r="K50" t="inlineStr"/>
+      <c r="L50" t="inlineStr"/>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N50" t="inlineStr"/>
+      <c r="P50" t="inlineStr">
+        <is>
+          <t>Selsknösen, Vb</t>
+        </is>
+      </c>
+      <c r="Q50" t="n">
+        <v>742135</v>
+      </c>
+      <c r="R50" t="n">
+        <v>7112060</v>
+      </c>
+      <c r="S50" t="n">
+        <v>10</v>
+      </c>
+      <c r="T50" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U50" t="inlineStr">
+        <is>
+          <t>Umeå</t>
+        </is>
+      </c>
+      <c r="V50" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W50" t="inlineStr">
+        <is>
+          <t>Umeå socken</t>
+        </is>
+      </c>
+      <c r="Y50" t="inlineStr">
+        <is>
+          <t>2025-08-27</t>
+        </is>
+      </c>
+      <c r="AA50" t="inlineStr">
+        <is>
+          <t>2025-08-27</t>
+        </is>
+      </c>
+      <c r="AD50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT50" t="inlineStr"/>
+      <c r="AW50" t="inlineStr">
+        <is>
+          <t>Maria Wikdahl</t>
+        </is>
+      </c>
+      <c r="AX50" t="inlineStr">
+        <is>
+          <t>Maria Wikdahl</t>
+        </is>
+      </c>
+      <c r="AY50" t="inlineStr"/>
+    </row>
+    <row r="51">
+      <c r="A51" t="n">
+        <v>128120480</v>
+      </c>
+      <c r="B51" t="n">
+        <v>57682</v>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E51" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr"/>
+      <c r="K51" t="inlineStr"/>
+      <c r="L51" t="inlineStr"/>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>gammalt bo</t>
+        </is>
+      </c>
+      <c r="N51" t="inlineStr"/>
+      <c r="P51" t="inlineStr">
+        <is>
+          <t>Selsknösen, Vb</t>
+        </is>
+      </c>
+      <c r="Q51" t="n">
+        <v>742020</v>
+      </c>
+      <c r="R51" t="n">
+        <v>7111987</v>
+      </c>
+      <c r="S51" t="n">
+        <v>10</v>
+      </c>
+      <c r="T51" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U51" t="inlineStr">
+        <is>
+          <t>Umeå</t>
+        </is>
+      </c>
+      <c r="V51" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W51" t="inlineStr">
+        <is>
+          <t>Umeå socken</t>
+        </is>
+      </c>
+      <c r="Y51" t="inlineStr">
+        <is>
+          <t>2025-08-27</t>
+        </is>
+      </c>
+      <c r="AA51" t="inlineStr">
+        <is>
+          <t>2025-08-27</t>
+        </is>
+      </c>
+      <c r="AD51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT51" t="inlineStr"/>
+      <c r="AW51" t="inlineStr">
+        <is>
+          <t>Maria Wikdahl</t>
+        </is>
+      </c>
+      <c r="AX51" t="inlineStr">
+        <is>
+          <t>Maria Wikdahl</t>
+        </is>
+      </c>
+      <c r="AY51" t="inlineStr"/>
+    </row>
+    <row r="52">
+      <c r="A52" t="n">
+        <v>128120521</v>
+      </c>
+      <c r="B52" t="n">
+        <v>79083</v>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E52" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr"/>
+      <c r="P52" t="inlineStr">
+        <is>
+          <t>Selsknösen, Vb</t>
+        </is>
+      </c>
+      <c r="Q52" t="n">
+        <v>741973</v>
+      </c>
+      <c r="R52" t="n">
+        <v>7112070</v>
+      </c>
+      <c r="S52" t="n">
+        <v>10</v>
+      </c>
+      <c r="T52" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U52" t="inlineStr">
+        <is>
+          <t>Umeå</t>
+        </is>
+      </c>
+      <c r="V52" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W52" t="inlineStr">
+        <is>
+          <t>Umeå socken</t>
+        </is>
+      </c>
+      <c r="Y52" t="inlineStr">
+        <is>
+          <t>2025-08-27</t>
+        </is>
+      </c>
+      <c r="AA52" t="inlineStr">
+        <is>
+          <t>2025-08-27</t>
+        </is>
+      </c>
+      <c r="AD52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT52" t="inlineStr"/>
+      <c r="AW52" t="inlineStr">
+        <is>
+          <t>Maria Wikdahl</t>
+        </is>
+      </c>
+      <c r="AX52" t="inlineStr">
+        <is>
+          <t>Maria Wikdahl</t>
+        </is>
+      </c>
+      <c r="AY52" t="inlineStr"/>
+    </row>
+    <row r="53">
+      <c r="A53" t="n">
+        <v>128120527</v>
+      </c>
+      <c r="B53" t="n">
+        <v>82942</v>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E53" t="n">
+        <v>1312</v>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>Gammelgransskål</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>Pseudographis pinicola</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>(Nyl.) Rehm</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr"/>
+      <c r="P53" t="inlineStr">
+        <is>
+          <t>Selsknösen, Vb</t>
+        </is>
+      </c>
+      <c r="Q53" t="n">
+        <v>742229</v>
+      </c>
+      <c r="R53" t="n">
+        <v>7112259</v>
+      </c>
+      <c r="S53" t="n">
+        <v>10</v>
+      </c>
+      <c r="T53" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U53" t="inlineStr">
+        <is>
+          <t>Umeå</t>
+        </is>
+      </c>
+      <c r="V53" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W53" t="inlineStr">
+        <is>
+          <t>Umeå socken</t>
+        </is>
+      </c>
+      <c r="Y53" t="inlineStr">
+        <is>
+          <t>2025-08-23</t>
+        </is>
+      </c>
+      <c r="AA53" t="inlineStr">
+        <is>
+          <t>2025-08-23</t>
+        </is>
+      </c>
+      <c r="AD53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT53" t="inlineStr"/>
+      <c r="AW53" t="inlineStr">
+        <is>
+          <t>Maria Wikdahl</t>
+        </is>
+      </c>
+      <c r="AX53" t="inlineStr">
+        <is>
+          <t>Maria Wikdahl</t>
+        </is>
+      </c>
+      <c r="AY53" t="inlineStr"/>
+    </row>
+    <row r="54">
+      <c r="A54" t="n">
+        <v>128120468</v>
+      </c>
+      <c r="B54" t="n">
+        <v>91452</v>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E54" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr"/>
+      <c r="P54" t="inlineStr">
+        <is>
+          <t>Selsknösen, Vb</t>
+        </is>
+      </c>
+      <c r="Q54" t="n">
+        <v>742464</v>
+      </c>
+      <c r="R54" t="n">
+        <v>7112167</v>
+      </c>
+      <c r="S54" t="n">
+        <v>10</v>
+      </c>
+      <c r="T54" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U54" t="inlineStr">
+        <is>
+          <t>Umeå</t>
+        </is>
+      </c>
+      <c r="V54" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W54" t="inlineStr">
+        <is>
+          <t>Umeå socken</t>
+        </is>
+      </c>
+      <c r="Y54" t="inlineStr">
+        <is>
+          <t>2025-08-27</t>
+        </is>
+      </c>
+      <c r="AA54" t="inlineStr">
+        <is>
+          <t>2025-08-27</t>
+        </is>
+      </c>
+      <c r="AD54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT54" t="inlineStr"/>
+      <c r="AW54" t="inlineStr">
+        <is>
+          <t>Maria Wikdahl</t>
+        </is>
+      </c>
+      <c r="AX54" t="inlineStr">
+        <is>
+          <t>Maria Wikdahl</t>
+        </is>
+      </c>
+      <c r="AY54" t="inlineStr"/>
+    </row>
+    <row r="55">
+      <c r="A55" t="n">
+        <v>128120522</v>
+      </c>
+      <c r="B55" t="n">
+        <v>79083</v>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E55" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr"/>
+      <c r="P55" t="inlineStr">
+        <is>
+          <t>Selsknösen, Vb</t>
+        </is>
+      </c>
+      <c r="Q55" t="n">
+        <v>741909</v>
+      </c>
+      <c r="R55" t="n">
+        <v>7111957</v>
+      </c>
+      <c r="S55" t="n">
+        <v>10</v>
+      </c>
+      <c r="T55" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U55" t="inlineStr">
+        <is>
+          <t>Umeå</t>
+        </is>
+      </c>
+      <c r="V55" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W55" t="inlineStr">
+        <is>
+          <t>Umeå socken</t>
+        </is>
+      </c>
+      <c r="Y55" t="inlineStr">
+        <is>
+          <t>2025-08-27</t>
+        </is>
+      </c>
+      <c r="AA55" t="inlineStr">
+        <is>
+          <t>2025-08-27</t>
+        </is>
+      </c>
+      <c r="AD55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT55" t="inlineStr"/>
+      <c r="AW55" t="inlineStr">
+        <is>
+          <t>Maria Wikdahl</t>
+        </is>
+      </c>
+      <c r="AX55" t="inlineStr">
+        <is>
+          <t>Maria Wikdahl</t>
+        </is>
+      </c>
+      <c r="AY55" t="inlineStr"/>
+    </row>
+    <row r="56">
+      <c r="A56" t="n">
+        <v>128120508</v>
+      </c>
+      <c r="B56" t="n">
+        <v>98571</v>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E56" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr"/>
+      <c r="P56" t="inlineStr">
+        <is>
+          <t>Selsknösen, Vb</t>
+        </is>
+      </c>
+      <c r="Q56" t="n">
+        <v>742177</v>
+      </c>
+      <c r="R56" t="n">
+        <v>7112084</v>
+      </c>
+      <c r="S56" t="n">
+        <v>10</v>
+      </c>
+      <c r="T56" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U56" t="inlineStr">
+        <is>
+          <t>Umeå</t>
+        </is>
+      </c>
+      <c r="V56" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W56" t="inlineStr">
+        <is>
+          <t>Umeå socken</t>
+        </is>
+      </c>
+      <c r="Y56" t="inlineStr">
+        <is>
+          <t>2025-08-27</t>
+        </is>
+      </c>
+      <c r="AA56" t="inlineStr">
+        <is>
+          <t>2025-08-27</t>
+        </is>
+      </c>
+      <c r="AD56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT56" t="inlineStr"/>
+      <c r="AW56" t="inlineStr">
+        <is>
+          <t>Maria Wikdahl</t>
+        </is>
+      </c>
+      <c r="AX56" t="inlineStr">
+        <is>
+          <t>Maria Wikdahl</t>
+        </is>
+      </c>
+      <c r="AY56" t="inlineStr"/>
+    </row>
+    <row r="57">
+      <c r="A57" t="n">
+        <v>128120478</v>
+      </c>
+      <c r="B57" t="n">
+        <v>57845</v>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E57" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr"/>
+      <c r="P57" t="inlineStr">
+        <is>
+          <t>Selsknösen, Vb</t>
+        </is>
+      </c>
+      <c r="Q57" t="n">
+        <v>741940</v>
+      </c>
+      <c r="R57" t="n">
+        <v>7111944</v>
+      </c>
+      <c r="S57" t="n">
+        <v>10</v>
+      </c>
+      <c r="T57" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U57" t="inlineStr">
+        <is>
+          <t>Umeå</t>
+        </is>
+      </c>
+      <c r="V57" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W57" t="inlineStr">
+        <is>
+          <t>Umeå socken</t>
+        </is>
+      </c>
+      <c r="Y57" t="inlineStr">
+        <is>
+          <t>2025-08-27</t>
+        </is>
+      </c>
+      <c r="AA57" t="inlineStr">
+        <is>
+          <t>2025-08-27</t>
+        </is>
+      </c>
+      <c r="AD57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT57" t="inlineStr"/>
+      <c r="AW57" t="inlineStr">
+        <is>
+          <t>Maria Wikdahl</t>
+        </is>
+      </c>
+      <c r="AX57" t="inlineStr">
+        <is>
+          <t>Maria Wikdahl</t>
+        </is>
+      </c>
+      <c r="AY57" t="inlineStr"/>
+    </row>
+    <row r="58">
+      <c r="A58" t="n">
+        <v>128120523</v>
+      </c>
+      <c r="B58" t="n">
+        <v>79083</v>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E58" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr"/>
+      <c r="P58" t="inlineStr">
+        <is>
+          <t>Selsknösen, Vb</t>
+        </is>
+      </c>
+      <c r="Q58" t="n">
+        <v>742019</v>
+      </c>
+      <c r="R58" t="n">
+        <v>7112056</v>
+      </c>
+      <c r="S58" t="n">
+        <v>10</v>
+      </c>
+      <c r="T58" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U58" t="inlineStr">
+        <is>
+          <t>Umeå</t>
+        </is>
+      </c>
+      <c r="V58" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W58" t="inlineStr">
+        <is>
+          <t>Umeå socken</t>
+        </is>
+      </c>
+      <c r="Y58" t="inlineStr">
+        <is>
+          <t>2025-08-23</t>
+        </is>
+      </c>
+      <c r="AA58" t="inlineStr">
+        <is>
+          <t>2025-08-23</t>
+        </is>
+      </c>
+      <c r="AD58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT58" t="inlineStr"/>
+      <c r="AW58" t="inlineStr">
+        <is>
+          <t>Maria Wikdahl</t>
+        </is>
+      </c>
+      <c r="AX58" t="inlineStr">
+        <is>
+          <t>Maria Wikdahl</t>
+        </is>
+      </c>
+      <c r="AY58" t="inlineStr"/>
+    </row>
+    <row r="59">
+      <c r="A59" t="n">
+        <v>128120506</v>
+      </c>
+      <c r="B59" t="n">
+        <v>98571</v>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E59" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr"/>
+      <c r="P59" t="inlineStr">
+        <is>
+          <t>Selsknösen, Vb</t>
+        </is>
+      </c>
+      <c r="Q59" t="n">
+        <v>741991</v>
+      </c>
+      <c r="R59" t="n">
+        <v>7111978</v>
+      </c>
+      <c r="S59" t="n">
+        <v>10</v>
+      </c>
+      <c r="T59" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U59" t="inlineStr">
+        <is>
+          <t>Umeå</t>
+        </is>
+      </c>
+      <c r="V59" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W59" t="inlineStr">
+        <is>
+          <t>Umeå socken</t>
+        </is>
+      </c>
+      <c r="Y59" t="inlineStr">
+        <is>
+          <t>2025-08-27</t>
+        </is>
+      </c>
+      <c r="AA59" t="inlineStr">
+        <is>
+          <t>2025-08-27</t>
+        </is>
+      </c>
+      <c r="AD59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT59" t="inlineStr"/>
+      <c r="AW59" t="inlineStr">
+        <is>
+          <t>Maria Wikdahl</t>
+        </is>
+      </c>
+      <c r="AX59" t="inlineStr">
+        <is>
+          <t>Maria Wikdahl</t>
+        </is>
+      </c>
+      <c r="AY59" t="inlineStr"/>
+    </row>
+    <row r="60">
+      <c r="A60" t="n">
+        <v>128120485</v>
+      </c>
+      <c r="B60" t="n">
+        <v>57682</v>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E60" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr"/>
+      <c r="K60" t="inlineStr"/>
+      <c r="L60" t="inlineStr"/>
+      <c r="M60" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N60" t="inlineStr"/>
+      <c r="P60" t="inlineStr">
+        <is>
+          <t>Selsknösen, Vb</t>
+        </is>
+      </c>
+      <c r="Q60" t="n">
+        <v>742170</v>
+      </c>
+      <c r="R60" t="n">
+        <v>7112262</v>
+      </c>
+      <c r="S60" t="n">
+        <v>10</v>
+      </c>
+      <c r="T60" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U60" t="inlineStr">
+        <is>
+          <t>Umeå</t>
+        </is>
+      </c>
+      <c r="V60" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W60" t="inlineStr">
+        <is>
+          <t>Umeå socken</t>
+        </is>
+      </c>
+      <c r="Y60" t="inlineStr">
+        <is>
+          <t>2025-08-23</t>
+        </is>
+      </c>
+      <c r="AA60" t="inlineStr">
+        <is>
+          <t>2025-08-23</t>
+        </is>
+      </c>
+      <c r="AD60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT60" t="inlineStr"/>
+      <c r="AW60" t="inlineStr">
+        <is>
+          <t>Maria Wikdahl</t>
+        </is>
+      </c>
+      <c r="AX60" t="inlineStr">
+        <is>
+          <t>Maria Wikdahl</t>
+        </is>
+      </c>
+      <c r="AY60" t="inlineStr"/>
+    </row>
+    <row r="61">
+      <c r="A61" t="n">
+        <v>128120492</v>
+      </c>
+      <c r="B61" t="n">
+        <v>80092</v>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E61" t="n">
+        <v>6456</v>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>Skinnlav</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>Leptogium saturninum</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>(Dicks.) Nyl.</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr"/>
+      <c r="P61" t="inlineStr">
+        <is>
+          <t>Selsknösen, Vb</t>
+        </is>
+      </c>
+      <c r="Q61" t="n">
+        <v>741909</v>
+      </c>
+      <c r="R61" t="n">
+        <v>7111939</v>
+      </c>
+      <c r="S61" t="n">
+        <v>10</v>
+      </c>
+      <c r="T61" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U61" t="inlineStr">
+        <is>
+          <t>Umeå</t>
+        </is>
+      </c>
+      <c r="V61" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W61" t="inlineStr">
+        <is>
+          <t>Umeå socken</t>
+        </is>
+      </c>
+      <c r="Y61" t="inlineStr">
+        <is>
+          <t>2025-08-27</t>
+        </is>
+      </c>
+      <c r="AA61" t="inlineStr">
+        <is>
+          <t>2025-08-27</t>
+        </is>
+      </c>
+      <c r="AD61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT61" t="inlineStr"/>
+      <c r="AW61" t="inlineStr">
+        <is>
+          <t>Maria Wikdahl</t>
+        </is>
+      </c>
+      <c r="AX61" t="inlineStr">
+        <is>
+          <t>Maria Wikdahl</t>
+        </is>
+      </c>
+      <c r="AY61" t="inlineStr"/>
+    </row>
+    <row r="62">
+      <c r="A62" t="n">
+        <v>128120502</v>
+      </c>
+      <c r="B62" t="n">
+        <v>98571</v>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E62" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="P62" t="inlineStr">
+        <is>
+          <t>Selsknösen, Vb</t>
+        </is>
+      </c>
+      <c r="Q62" t="n">
+        <v>741962</v>
+      </c>
+      <c r="R62" t="n">
+        <v>7111971</v>
+      </c>
+      <c r="S62" t="n">
+        <v>10</v>
+      </c>
+      <c r="T62" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U62" t="inlineStr">
+        <is>
+          <t>Umeå</t>
+        </is>
+      </c>
+      <c r="V62" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W62" t="inlineStr">
+        <is>
+          <t>Umeå socken</t>
+        </is>
+      </c>
+      <c r="Y62" t="inlineStr">
+        <is>
+          <t>2025-08-27</t>
+        </is>
+      </c>
+      <c r="AA62" t="inlineStr">
+        <is>
+          <t>2025-08-27</t>
+        </is>
+      </c>
+      <c r="AD62" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE62" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF62" t="inlineStr"/>
+      <c r="AG62" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT62" t="inlineStr"/>
+      <c r="AW62" t="inlineStr">
+        <is>
+          <t>Maria Wikdahl</t>
+        </is>
+      </c>
+      <c r="AX62" t="inlineStr">
+        <is>
+          <t>Maria Wikdahl</t>
+        </is>
+      </c>
+      <c r="AY62" t="inlineStr"/>
+    </row>
+    <row r="63">
+      <c r="A63" t="n">
+        <v>128120516</v>
+      </c>
+      <c r="B63" t="n">
+        <v>91470</v>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E63" t="n">
+        <v>5432</v>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>Granticka</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>Porodaedalea chrysoloma</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr"/>
+      <c r="P63" t="inlineStr">
+        <is>
+          <t>Selsknösen, Vb</t>
+        </is>
+      </c>
+      <c r="Q63" t="n">
+        <v>742047</v>
+      </c>
+      <c r="R63" t="n">
+        <v>7111978</v>
+      </c>
+      <c r="S63" t="n">
+        <v>10</v>
+      </c>
+      <c r="T63" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U63" t="inlineStr">
+        <is>
+          <t>Umeå</t>
+        </is>
+      </c>
+      <c r="V63" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W63" t="inlineStr">
+        <is>
+          <t>Umeå socken</t>
+        </is>
+      </c>
+      <c r="Y63" t="inlineStr">
+        <is>
+          <t>2025-08-27</t>
+        </is>
+      </c>
+      <c r="AA63" t="inlineStr">
+        <is>
+          <t>2025-08-27</t>
+        </is>
+      </c>
+      <c r="AD63" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE63" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG63" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT63" t="inlineStr"/>
+      <c r="AW63" t="inlineStr">
+        <is>
+          <t>Maria Wikdahl</t>
+        </is>
+      </c>
+      <c r="AX63" t="inlineStr">
+        <is>
+          <t>Maria Wikdahl</t>
+        </is>
+      </c>
+      <c r="AY63" t="inlineStr"/>
+    </row>
+    <row r="64">
+      <c r="A64" t="n">
+        <v>128120510</v>
+      </c>
+      <c r="B64" t="n">
+        <v>98571</v>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E64" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr"/>
+      <c r="P64" t="inlineStr">
+        <is>
+          <t>Selsknösen, Vb</t>
+        </is>
+      </c>
+      <c r="Q64" t="n">
+        <v>742050</v>
+      </c>
+      <c r="R64" t="n">
+        <v>7111983</v>
+      </c>
+      <c r="S64" t="n">
+        <v>10</v>
+      </c>
+      <c r="T64" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U64" t="inlineStr">
+        <is>
+          <t>Umeå</t>
+        </is>
+      </c>
+      <c r="V64" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W64" t="inlineStr">
+        <is>
+          <t>Umeå socken</t>
+        </is>
+      </c>
+      <c r="Y64" t="inlineStr">
+        <is>
+          <t>2025-08-27</t>
+        </is>
+      </c>
+      <c r="AA64" t="inlineStr">
+        <is>
+          <t>2025-08-27</t>
+        </is>
+      </c>
+      <c r="AD64" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE64" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG64" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT64" t="inlineStr"/>
+      <c r="AW64" t="inlineStr">
+        <is>
+          <t>Maria Wikdahl</t>
+        </is>
+      </c>
+      <c r="AX64" t="inlineStr">
+        <is>
+          <t>Maria Wikdahl</t>
+        </is>
+      </c>
+      <c r="AY64" t="inlineStr"/>
+    </row>
+    <row r="65">
+      <c r="A65" t="n">
+        <v>128120511</v>
+      </c>
+      <c r="B65" t="n">
+        <v>98571</v>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E65" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr"/>
+      <c r="P65" t="inlineStr">
+        <is>
+          <t>Selsknösen, Vb</t>
+        </is>
+      </c>
+      <c r="Q65" t="n">
+        <v>742032</v>
+      </c>
+      <c r="R65" t="n">
+        <v>7111965</v>
+      </c>
+      <c r="S65" t="n">
+        <v>10</v>
+      </c>
+      <c r="T65" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U65" t="inlineStr">
+        <is>
+          <t>Umeå</t>
+        </is>
+      </c>
+      <c r="V65" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W65" t="inlineStr">
+        <is>
+          <t>Umeå socken</t>
+        </is>
+      </c>
+      <c r="Y65" t="inlineStr">
+        <is>
+          <t>2025-08-27</t>
+        </is>
+      </c>
+      <c r="AA65" t="inlineStr">
+        <is>
+          <t>2025-08-27</t>
+        </is>
+      </c>
+      <c r="AD65" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE65" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG65" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT65" t="inlineStr"/>
+      <c r="AW65" t="inlineStr">
+        <is>
+          <t>Maria Wikdahl</t>
+        </is>
+      </c>
+      <c r="AX65" t="inlineStr">
+        <is>
+          <t>Maria Wikdahl</t>
+        </is>
+      </c>
+      <c r="AY65" t="inlineStr"/>
+    </row>
+    <row r="66">
+      <c r="A66" t="n">
+        <v>128120499</v>
+      </c>
+      <c r="B66" t="n">
+        <v>98571</v>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E66" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr"/>
+      <c r="J66" t="inlineStr"/>
+      <c r="K66" t="inlineStr"/>
+      <c r="L66" t="inlineStr"/>
+      <c r="N66" t="inlineStr"/>
+      <c r="P66" t="inlineStr">
+        <is>
+          <t>Selsknösen, Vb</t>
+        </is>
+      </c>
+      <c r="Q66" t="n">
+        <v>741963</v>
+      </c>
+      <c r="R66" t="n">
+        <v>7111964</v>
+      </c>
+      <c r="S66" t="n">
+        <v>10</v>
+      </c>
+      <c r="T66" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U66" t="inlineStr">
+        <is>
+          <t>Umeå</t>
+        </is>
+      </c>
+      <c r="V66" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W66" t="inlineStr">
+        <is>
+          <t>Umeå socken</t>
+        </is>
+      </c>
+      <c r="Y66" t="inlineStr">
+        <is>
+          <t>2025-08-27</t>
+        </is>
+      </c>
+      <c r="AA66" t="inlineStr">
+        <is>
+          <t>2025-08-27</t>
+        </is>
+      </c>
+      <c r="AC66" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
+        </is>
+      </c>
+      <c r="AD66" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE66" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF66" t="inlineStr"/>
+      <c r="AG66" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT66" t="inlineStr"/>
+      <c r="AW66" t="inlineStr">
+        <is>
+          <t>Maria Wikdahl</t>
+        </is>
+      </c>
+      <c r="AX66" t="inlineStr">
+        <is>
+          <t>Maria Wikdahl</t>
+        </is>
+      </c>
+      <c r="AY66" t="inlineStr"/>
+    </row>
+    <row r="67">
+      <c r="A67" t="n">
+        <v>128120487</v>
+      </c>
+      <c r="B67" t="n">
+        <v>57682</v>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E67" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr"/>
+      <c r="K67" t="inlineStr"/>
+      <c r="L67" t="inlineStr"/>
+      <c r="M67" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N67" t="inlineStr"/>
+      <c r="P67" t="inlineStr">
+        <is>
+          <t>Selsknösen, Vb</t>
+        </is>
+      </c>
+      <c r="Q67" t="n">
+        <v>741971</v>
+      </c>
+      <c r="R67" t="n">
+        <v>7111953</v>
+      </c>
+      <c r="S67" t="n">
+        <v>10</v>
+      </c>
+      <c r="T67" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U67" t="inlineStr">
+        <is>
+          <t>Umeå</t>
+        </is>
+      </c>
+      <c r="V67" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W67" t="inlineStr">
+        <is>
+          <t>Umeå socken</t>
+        </is>
+      </c>
+      <c r="Y67" t="inlineStr">
+        <is>
+          <t>2025-08-27</t>
+        </is>
+      </c>
+      <c r="AA67" t="inlineStr">
+        <is>
+          <t>2025-08-27</t>
+        </is>
+      </c>
+      <c r="AC67" t="inlineStr">
+        <is>
+          <t>Mycket färska spår, se bild.</t>
+        </is>
+      </c>
+      <c r="AD67" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE67" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG67" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT67" t="inlineStr"/>
+      <c r="AW67" t="inlineStr">
+        <is>
+          <t>Maria Wikdahl</t>
+        </is>
+      </c>
+      <c r="AX67" t="inlineStr">
+        <is>
+          <t>Maria Wikdahl</t>
+        </is>
+      </c>
+      <c r="AY67" t="inlineStr"/>
+    </row>
+    <row r="68">
+      <c r="A68" t="n">
+        <v>128120475</v>
+      </c>
+      <c r="B68" t="n">
+        <v>57685</v>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E68" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr"/>
+      <c r="K68" t="inlineStr"/>
+      <c r="L68" t="inlineStr"/>
+      <c r="M68" t="inlineStr">
+        <is>
+          <t>gammalt bo</t>
+        </is>
+      </c>
+      <c r="N68" t="inlineStr"/>
+      <c r="P68" t="inlineStr">
+        <is>
+          <t>Selsknösen, Vb</t>
+        </is>
+      </c>
+      <c r="Q68" t="n">
+        <v>742203</v>
+      </c>
+      <c r="R68" t="n">
+        <v>7112188</v>
+      </c>
+      <c r="S68" t="n">
+        <v>10</v>
+      </c>
+      <c r="T68" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U68" t="inlineStr">
+        <is>
+          <t>Umeå</t>
+        </is>
+      </c>
+      <c r="V68" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W68" t="inlineStr">
+        <is>
+          <t>Umeå socken</t>
+        </is>
+      </c>
+      <c r="Y68" t="inlineStr">
+        <is>
+          <t>2025-08-27</t>
+        </is>
+      </c>
+      <c r="AA68" t="inlineStr">
+        <is>
+          <t>2025-08-27</t>
+        </is>
+      </c>
+      <c r="AD68" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE68" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG68" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT68" t="inlineStr"/>
+      <c r="AW68" t="inlineStr">
+        <is>
+          <t>Maria Wikdahl</t>
+        </is>
+      </c>
+      <c r="AX68" t="inlineStr">
+        <is>
+          <t>Maria Wikdahl</t>
+        </is>
+      </c>
+      <c r="AY68" t="inlineStr"/>
+    </row>
+    <row r="69">
+      <c r="A69" t="n">
+        <v>128120491</v>
+      </c>
+      <c r="B69" t="n">
+        <v>80092</v>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E69" t="n">
+        <v>6456</v>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>Skinnlav</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>Leptogium saturninum</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>(Dicks.) Nyl.</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr"/>
+      <c r="P69" t="inlineStr">
+        <is>
+          <t>Selsknösen, Vb</t>
+        </is>
+      </c>
+      <c r="Q69" t="n">
+        <v>742255</v>
+      </c>
+      <c r="R69" t="n">
+        <v>7112289</v>
+      </c>
+      <c r="S69" t="n">
+        <v>10</v>
+      </c>
+      <c r="T69" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U69" t="inlineStr">
+        <is>
+          <t>Umeå</t>
+        </is>
+      </c>
+      <c r="V69" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W69" t="inlineStr">
+        <is>
+          <t>Umeå socken</t>
+        </is>
+      </c>
+      <c r="Y69" t="inlineStr">
+        <is>
+          <t>2025-08-27</t>
+        </is>
+      </c>
+      <c r="AA69" t="inlineStr">
+        <is>
+          <t>2025-08-27</t>
+        </is>
+      </c>
+      <c r="AD69" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE69" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG69" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT69" t="inlineStr"/>
+      <c r="AW69" t="inlineStr">
+        <is>
+          <t>Maria Wikdahl</t>
+        </is>
+      </c>
+      <c r="AX69" t="inlineStr">
+        <is>
+          <t>Maria Wikdahl</t>
+        </is>
+      </c>
+      <c r="AY69" t="inlineStr"/>
+    </row>
+    <row r="70">
+      <c r="A70" t="n">
+        <v>128120526</v>
+      </c>
+      <c r="B70" t="n">
+        <v>82942</v>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E70" t="n">
+        <v>1312</v>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>Gammelgransskål</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>Pseudographis pinicola</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>(Nyl.) Rehm</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr"/>
+      <c r="P70" t="inlineStr">
+        <is>
+          <t>Selsknösen, Vb</t>
+        </is>
+      </c>
+      <c r="Q70" t="n">
+        <v>742268</v>
+      </c>
+      <c r="R70" t="n">
+        <v>7112227</v>
+      </c>
+      <c r="S70" t="n">
+        <v>10</v>
+      </c>
+      <c r="T70" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U70" t="inlineStr">
+        <is>
+          <t>Umeå</t>
+        </is>
+      </c>
+      <c r="V70" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W70" t="inlineStr">
+        <is>
+          <t>Umeå socken</t>
+        </is>
+      </c>
+      <c r="Y70" t="inlineStr">
+        <is>
+          <t>2025-08-23</t>
+        </is>
+      </c>
+      <c r="AA70" t="inlineStr">
+        <is>
+          <t>2025-08-23</t>
+        </is>
+      </c>
+      <c r="AD70" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE70" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG70" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT70" t="inlineStr"/>
+      <c r="AW70" t="inlineStr">
+        <is>
+          <t>Maria Wikdahl</t>
+        </is>
+      </c>
+      <c r="AX70" t="inlineStr">
+        <is>
+          <t>Maria Wikdahl</t>
+        </is>
+      </c>
+      <c r="AY70" t="inlineStr"/>
+    </row>
+    <row r="71">
+      <c r="A71" t="n">
+        <v>128120490</v>
+      </c>
+      <c r="B71" t="n">
+        <v>57682</v>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E71" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr"/>
+      <c r="K71" t="inlineStr"/>
+      <c r="L71" t="inlineStr"/>
+      <c r="M71" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N71" t="inlineStr"/>
+      <c r="P71" t="inlineStr">
+        <is>
+          <t>Selsknösen, Vb</t>
+        </is>
+      </c>
+      <c r="Q71" t="n">
+        <v>741943</v>
+      </c>
+      <c r="R71" t="n">
+        <v>7111915</v>
+      </c>
+      <c r="S71" t="n">
+        <v>10</v>
+      </c>
+      <c r="T71" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U71" t="inlineStr">
+        <is>
+          <t>Umeå</t>
+        </is>
+      </c>
+      <c r="V71" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W71" t="inlineStr">
+        <is>
+          <t>Umeå socken</t>
+        </is>
+      </c>
+      <c r="Y71" t="inlineStr">
+        <is>
+          <t>2025-08-27</t>
+        </is>
+      </c>
+      <c r="AA71" t="inlineStr">
+        <is>
+          <t>2025-08-27</t>
+        </is>
+      </c>
+      <c r="AD71" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE71" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG71" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT71" t="inlineStr"/>
+      <c r="AW71" t="inlineStr">
+        <is>
+          <t>Maria Wikdahl</t>
+        </is>
+      </c>
+      <c r="AX71" t="inlineStr">
+        <is>
+          <t>Maria Wikdahl</t>
+        </is>
+      </c>
+      <c r="AY71" t="inlineStr"/>
+    </row>
+    <row r="72">
+      <c r="A72" t="n">
+        <v>128120501</v>
+      </c>
+      <c r="B72" t="n">
+        <v>98571</v>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E72" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="P72" t="inlineStr">
+        <is>
+          <t>Selsknösen, Vb</t>
+        </is>
+      </c>
+      <c r="Q72" t="n">
+        <v>742340</v>
+      </c>
+      <c r="R72" t="n">
+        <v>7112209</v>
+      </c>
+      <c r="S72" t="n">
+        <v>10</v>
+      </c>
+      <c r="T72" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U72" t="inlineStr">
+        <is>
+          <t>Umeå</t>
+        </is>
+      </c>
+      <c r="V72" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W72" t="inlineStr">
+        <is>
+          <t>Umeå socken</t>
+        </is>
+      </c>
+      <c r="Y72" t="inlineStr">
+        <is>
+          <t>2025-08-27</t>
+        </is>
+      </c>
+      <c r="AA72" t="inlineStr">
+        <is>
+          <t>2025-08-27</t>
+        </is>
+      </c>
+      <c r="AD72" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE72" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF72" t="inlineStr"/>
+      <c r="AG72" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT72" t="inlineStr"/>
+      <c r="AW72" t="inlineStr">
+        <is>
+          <t>Maria Wikdahl</t>
+        </is>
+      </c>
+      <c r="AX72" t="inlineStr">
+        <is>
+          <t>Maria Wikdahl</t>
+        </is>
+      </c>
+      <c r="AY72" t="inlineStr"/>
+    </row>
+    <row r="73">
+      <c r="A73" t="n">
+        <v>128120486</v>
+      </c>
+      <c r="B73" t="n">
+        <v>57682</v>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E73" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr"/>
+      <c r="K73" t="inlineStr"/>
+      <c r="L73" t="inlineStr"/>
+      <c r="M73" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N73" t="inlineStr"/>
+      <c r="P73" t="inlineStr">
+        <is>
+          <t>Selsknösen, Vb</t>
+        </is>
+      </c>
+      <c r="Q73" t="n">
+        <v>742107</v>
+      </c>
+      <c r="R73" t="n">
+        <v>7112066</v>
+      </c>
+      <c r="S73" t="n">
+        <v>10</v>
+      </c>
+      <c r="T73" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U73" t="inlineStr">
+        <is>
+          <t>Umeå</t>
+        </is>
+      </c>
+      <c r="V73" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W73" t="inlineStr">
+        <is>
+          <t>Umeå socken</t>
+        </is>
+      </c>
+      <c r="Y73" t="inlineStr">
+        <is>
+          <t>2025-08-23</t>
+        </is>
+      </c>
+      <c r="AA73" t="inlineStr">
+        <is>
+          <t>2025-08-23</t>
+        </is>
+      </c>
+      <c r="AD73" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE73" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG73" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT73" t="inlineStr"/>
+      <c r="AW73" t="inlineStr">
+        <is>
+          <t>Maria Wikdahl</t>
+        </is>
+      </c>
+      <c r="AX73" t="inlineStr">
+        <is>
+          <t>Maria Wikdahl</t>
+        </is>
+      </c>
+      <c r="AY73" t="inlineStr"/>
+    </row>
+    <row r="74">
+      <c r="A74" t="n">
+        <v>128120474</v>
+      </c>
+      <c r="B74" t="n">
+        <v>57685</v>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E74" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr"/>
+      <c r="K74" t="inlineStr"/>
+      <c r="L74" t="inlineStr"/>
+      <c r="M74" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N74" t="inlineStr"/>
+      <c r="P74" t="inlineStr">
+        <is>
+          <t>Selsknösen, Vb</t>
+        </is>
+      </c>
+      <c r="Q74" t="n">
+        <v>742191</v>
+      </c>
+      <c r="R74" t="n">
+        <v>7112251</v>
+      </c>
+      <c r="S74" t="n">
+        <v>10</v>
+      </c>
+      <c r="T74" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U74" t="inlineStr">
+        <is>
+          <t>Umeå</t>
+        </is>
+      </c>
+      <c r="V74" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W74" t="inlineStr">
+        <is>
+          <t>Umeå socken</t>
+        </is>
+      </c>
+      <c r="Y74" t="inlineStr">
+        <is>
+          <t>2025-08-27</t>
+        </is>
+      </c>
+      <c r="AA74" t="inlineStr">
+        <is>
+          <t>2025-08-27</t>
+        </is>
+      </c>
+      <c r="AC74" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
+        </is>
+      </c>
+      <c r="AD74" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE74" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG74" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT74" t="inlineStr"/>
+      <c r="AW74" t="inlineStr">
+        <is>
+          <t>Maria Wikdahl</t>
+        </is>
+      </c>
+      <c r="AX74" t="inlineStr">
+        <is>
+          <t>Maria Wikdahl</t>
+        </is>
+      </c>
+      <c r="AY74" t="inlineStr"/>
+    </row>
+    <row r="75">
+      <c r="A75" t="n">
+        <v>128120470</v>
+      </c>
+      <c r="B75" t="n">
+        <v>91452</v>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E75" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I75" t="inlineStr"/>
+      <c r="P75" t="inlineStr">
+        <is>
+          <t>Selsknösen, Vb</t>
+        </is>
+      </c>
+      <c r="Q75" t="n">
+        <v>741946</v>
+      </c>
+      <c r="R75" t="n">
+        <v>7111928</v>
+      </c>
+      <c r="S75" t="n">
+        <v>10</v>
+      </c>
+      <c r="T75" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U75" t="inlineStr">
+        <is>
+          <t>Umeå</t>
+        </is>
+      </c>
+      <c r="V75" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W75" t="inlineStr">
+        <is>
+          <t>Umeå socken</t>
+        </is>
+      </c>
+      <c r="Y75" t="inlineStr">
+        <is>
+          <t>2025-08-27</t>
+        </is>
+      </c>
+      <c r="AA75" t="inlineStr">
+        <is>
+          <t>2025-08-27</t>
+        </is>
+      </c>
+      <c r="AD75" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE75" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG75" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT75" t="inlineStr"/>
+      <c r="AW75" t="inlineStr">
+        <is>
+          <t>Maria Wikdahl</t>
+        </is>
+      </c>
+      <c r="AX75" t="inlineStr">
+        <is>
+          <t>Maria Wikdahl</t>
+        </is>
+      </c>
+      <c r="AY75" t="inlineStr"/>
+    </row>
+    <row r="76">
+      <c r="A76" t="n">
+        <v>128120466</v>
+      </c>
+      <c r="B76" t="n">
+        <v>91452</v>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E76" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I76" t="inlineStr"/>
+      <c r="P76" t="inlineStr">
+        <is>
+          <t>Selsknösen, Vb</t>
+        </is>
+      </c>
+      <c r="Q76" t="n">
+        <v>741977</v>
+      </c>
+      <c r="R76" t="n">
+        <v>7111936</v>
+      </c>
+      <c r="S76" t="n">
+        <v>10</v>
+      </c>
+      <c r="T76" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U76" t="inlineStr">
+        <is>
+          <t>Umeå</t>
+        </is>
+      </c>
+      <c r="V76" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W76" t="inlineStr">
+        <is>
+          <t>Umeå socken</t>
+        </is>
+      </c>
+      <c r="Y76" t="inlineStr">
+        <is>
+          <t>2025-08-27</t>
+        </is>
+      </c>
+      <c r="AA76" t="inlineStr">
+        <is>
+          <t>2025-08-27</t>
+        </is>
+      </c>
+      <c r="AD76" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE76" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG76" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT76" t="inlineStr"/>
+      <c r="AW76" t="inlineStr">
+        <is>
+          <t>Maria Wikdahl</t>
+        </is>
+      </c>
+      <c r="AX76" t="inlineStr">
+        <is>
+          <t>Maria Wikdahl</t>
+        </is>
+      </c>
+      <c r="AY76" t="inlineStr"/>
+    </row>
+    <row r="77">
+      <c r="A77" t="n">
+        <v>128120520</v>
+      </c>
+      <c r="B77" t="n">
+        <v>79083</v>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E77" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I77" t="inlineStr"/>
+      <c r="P77" t="inlineStr">
+        <is>
+          <t>Selsknösen, Vb</t>
+        </is>
+      </c>
+      <c r="Q77" t="n">
+        <v>741965</v>
+      </c>
+      <c r="R77" t="n">
+        <v>7112091</v>
+      </c>
+      <c r="S77" t="n">
+        <v>10</v>
+      </c>
+      <c r="T77" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U77" t="inlineStr">
+        <is>
+          <t>Umeå</t>
+        </is>
+      </c>
+      <c r="V77" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W77" t="inlineStr">
+        <is>
+          <t>Umeå socken</t>
+        </is>
+      </c>
+      <c r="Y77" t="inlineStr">
+        <is>
+          <t>2025-08-27</t>
+        </is>
+      </c>
+      <c r="AA77" t="inlineStr">
+        <is>
+          <t>2025-08-27</t>
+        </is>
+      </c>
+      <c r="AD77" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE77" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG77" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT77" t="inlineStr"/>
+      <c r="AW77" t="inlineStr">
+        <is>
+          <t>Maria Wikdahl</t>
+        </is>
+      </c>
+      <c r="AX77" t="inlineStr">
+        <is>
+          <t>Maria Wikdahl</t>
+        </is>
+      </c>
+      <c r="AY77" t="inlineStr"/>
+    </row>
+    <row r="78">
+      <c r="A78" t="n">
+        <v>128120472</v>
+      </c>
+      <c r="B78" t="n">
+        <v>57685</v>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E78" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I78" t="inlineStr"/>
+      <c r="K78" t="inlineStr"/>
+      <c r="L78" t="inlineStr"/>
+      <c r="M78" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N78" t="inlineStr"/>
+      <c r="P78" t="inlineStr">
+        <is>
+          <t>Selsknösen, Vb</t>
+        </is>
+      </c>
+      <c r="Q78" t="n">
+        <v>741931</v>
+      </c>
+      <c r="R78" t="n">
+        <v>7111932</v>
+      </c>
+      <c r="S78" t="n">
+        <v>10</v>
+      </c>
+      <c r="T78" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U78" t="inlineStr">
+        <is>
+          <t>Umeå</t>
+        </is>
+      </c>
+      <c r="V78" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W78" t="inlineStr">
+        <is>
+          <t>Umeå socken</t>
+        </is>
+      </c>
+      <c r="Y78" t="inlineStr">
+        <is>
+          <t>2025-08-27</t>
+        </is>
+      </c>
+      <c r="AA78" t="inlineStr">
+        <is>
+          <t>2025-08-27</t>
+        </is>
+      </c>
+      <c r="AC78" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på tall.</t>
+        </is>
+      </c>
+      <c r="AD78" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE78" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG78" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT78" t="inlineStr"/>
+      <c r="AW78" t="inlineStr">
+        <is>
+          <t>Maria Wikdahl</t>
+        </is>
+      </c>
+      <c r="AX78" t="inlineStr">
+        <is>
+          <t>Maria Wikdahl</t>
+        </is>
+      </c>
+      <c r="AY78" t="inlineStr"/>
+    </row>
+    <row r="79">
+      <c r="A79" t="n">
+        <v>128120477</v>
+      </c>
+      <c r="B79" t="n">
+        <v>57845</v>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E79" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H79" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I79" t="inlineStr"/>
+      <c r="P79" t="inlineStr">
+        <is>
+          <t>Selsknösen, Vb</t>
+        </is>
+      </c>
+      <c r="Q79" t="n">
+        <v>742054</v>
+      </c>
+      <c r="R79" t="n">
+        <v>7112013</v>
+      </c>
+      <c r="S79" t="n">
+        <v>10</v>
+      </c>
+      <c r="T79" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U79" t="inlineStr">
+        <is>
+          <t>Umeå</t>
+        </is>
+      </c>
+      <c r="V79" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W79" t="inlineStr">
+        <is>
+          <t>Umeå socken</t>
+        </is>
+      </c>
+      <c r="Y79" t="inlineStr">
+        <is>
+          <t>2025-08-27</t>
+        </is>
+      </c>
+      <c r="AA79" t="inlineStr">
+        <is>
+          <t>2025-08-27</t>
+        </is>
+      </c>
+      <c r="AD79" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE79" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG79" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT79" t="inlineStr"/>
+      <c r="AW79" t="inlineStr">
+        <is>
+          <t>Maria Wikdahl</t>
+        </is>
+      </c>
+      <c r="AX79" t="inlineStr">
+        <is>
+          <t>Maria Wikdahl</t>
+        </is>
+      </c>
+      <c r="AY79" t="inlineStr"/>
+    </row>
+    <row r="80">
+      <c r="A80" t="n">
+        <v>128120503</v>
+      </c>
+      <c r="B80" t="n">
+        <v>98571</v>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E80" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H80" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I80" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="P80" t="inlineStr">
+        <is>
+          <t>Selsknösen, Vb</t>
+        </is>
+      </c>
+      <c r="Q80" t="n">
+        <v>742010</v>
+      </c>
+      <c r="R80" t="n">
+        <v>7111949</v>
+      </c>
+      <c r="S80" t="n">
+        <v>10</v>
+      </c>
+      <c r="T80" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U80" t="inlineStr">
+        <is>
+          <t>Umeå</t>
+        </is>
+      </c>
+      <c r="V80" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W80" t="inlineStr">
+        <is>
+          <t>Umeå socken</t>
+        </is>
+      </c>
+      <c r="Y80" t="inlineStr">
+        <is>
+          <t>2025-08-27</t>
+        </is>
+      </c>
+      <c r="AA80" t="inlineStr">
+        <is>
+          <t>2025-08-27</t>
+        </is>
+      </c>
+      <c r="AD80" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE80" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF80" t="inlineStr"/>
+      <c r="AG80" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT80" t="inlineStr"/>
+      <c r="AW80" t="inlineStr">
+        <is>
+          <t>Maria Wikdahl</t>
+        </is>
+      </c>
+      <c r="AX80" t="inlineStr">
+        <is>
+          <t>Maria Wikdahl</t>
+        </is>
+      </c>
+      <c r="AY80" t="inlineStr"/>
+    </row>
+    <row r="81">
+      <c r="A81" t="n">
+        <v>128314983</v>
+      </c>
+      <c r="B81" t="n">
+        <v>91810</v>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E81" t="n">
+        <v>2062</v>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>Ulltickeporing</t>
+        </is>
+      </c>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>Skeletocutis brevispora</t>
+        </is>
+      </c>
+      <c r="H81" t="inlineStr">
+        <is>
+          <t>Niemelä</t>
+        </is>
+      </c>
+      <c r="I81" t="inlineStr"/>
+      <c r="P81" t="inlineStr">
+        <is>
+          <t>Selsknösen, Vb</t>
+        </is>
+      </c>
+      <c r="Q81" t="n">
+        <v>742315</v>
+      </c>
+      <c r="R81" t="n">
+        <v>7112279</v>
+      </c>
+      <c r="S81" t="n">
+        <v>10</v>
+      </c>
+      <c r="T81" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U81" t="inlineStr">
+        <is>
+          <t>Umeå</t>
+        </is>
+      </c>
+      <c r="V81" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W81" t="inlineStr">
+        <is>
+          <t>Umeå socken</t>
+        </is>
+      </c>
+      <c r="Y81" t="inlineStr">
+        <is>
+          <t>2025-08-27</t>
+        </is>
+      </c>
+      <c r="AA81" t="inlineStr">
+        <is>
+          <t>2025-08-27</t>
+        </is>
+      </c>
+      <c r="AD81" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE81" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF81" t="inlineStr"/>
+      <c r="AG81" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT81" t="inlineStr"/>
+      <c r="AW81" t="inlineStr">
+        <is>
           <t>Elin Kannerby</t>
         </is>
       </c>
-      <c r="AX25" t="inlineStr">
+      <c r="AX81" t="inlineStr">
         <is>
           <t>Elin Kannerby</t>
         </is>
       </c>
-      <c r="AY25" t="inlineStr"/>
+      <c r="AY81" t="inlineStr"/>
+    </row>
+    <row r="82">
+      <c r="A82" t="n">
+        <v>128314982</v>
+      </c>
+      <c r="B82" t="n">
+        <v>91824</v>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E82" t="n">
+        <v>1505</v>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>Kristallticka</t>
+        </is>
+      </c>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>Skeletocutis stellae</t>
+        </is>
+      </c>
+      <c r="H82" t="inlineStr">
+        <is>
+          <t>(Pilát) Jean Keller</t>
+        </is>
+      </c>
+      <c r="I82" t="inlineStr"/>
+      <c r="P82" t="inlineStr">
+        <is>
+          <t>Selsknösen, Vb</t>
+        </is>
+      </c>
+      <c r="Q82" t="n">
+        <v>742153</v>
+      </c>
+      <c r="R82" t="n">
+        <v>7112076</v>
+      </c>
+      <c r="S82" t="n">
+        <v>10</v>
+      </c>
+      <c r="T82" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U82" t="inlineStr">
+        <is>
+          <t>Umeå</t>
+        </is>
+      </c>
+      <c r="V82" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W82" t="inlineStr">
+        <is>
+          <t>Umeå socken</t>
+        </is>
+      </c>
+      <c r="Y82" t="inlineStr">
+        <is>
+          <t>2025-08-27</t>
+        </is>
+      </c>
+      <c r="AA82" t="inlineStr">
+        <is>
+          <t>2025-08-27</t>
+        </is>
+      </c>
+      <c r="AD82" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE82" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG82" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT82" t="inlineStr"/>
+      <c r="AW82" t="inlineStr">
+        <is>
+          <t>Elin Kannerby</t>
+        </is>
+      </c>
+      <c r="AX82" t="inlineStr">
+        <is>
+          <t>Elin Kannerby</t>
+        </is>
+      </c>
+      <c r="AY82" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 38519-2025 artfynd.xlsx
+++ b/artfynd/A 38519-2025 artfynd.xlsx
@@ -869,49 +869,45 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>128115303</v>
+        <v>128115311</v>
       </c>
       <c r="B4" t="n">
-        <v>98571</v>
+        <v>79083</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
-      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Selsknösen, Vb</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>742050</v>
+        <v>742052</v>
       </c>
       <c r="R4" t="n">
-        <v>7111963</v>
+        <v>7112024</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -952,7 +948,6 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
-      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
@@ -971,7 +966,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128115305</v>
+        <v>128115303</v>
       </c>
       <c r="B5" t="n">
         <v>98571</v>
@@ -1010,10 +1005,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>741970</v>
+        <v>742050</v>
       </c>
       <c r="R5" t="n">
-        <v>7111969</v>
+        <v>7111963</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1073,45 +1068,49 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128115311</v>
+        <v>128115305</v>
       </c>
       <c r="B6" t="n">
-        <v>79083</v>
+        <v>98571</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Selsknösen, Vb</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>742052</v>
+        <v>741970</v>
       </c>
       <c r="R6" t="n">
-        <v>7112024</v>
+        <v>7111969</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1152,6 +1151,7 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
+      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -1364,49 +1364,45 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>128115290</v>
+        <v>128115289</v>
       </c>
       <c r="B9" t="n">
-        <v>56876</v>
+        <v>91452</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100138</v>
+        <v>1202</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr"/>
-      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Selsknösen, Vb</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>742080</v>
+        <v>742020</v>
       </c>
       <c r="R9" t="n">
-        <v>7112234</v>
+        <v>7111950</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1441,17 +1437,13 @@
           <t>2025-08-27</t>
         </is>
       </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Fjäder funnen</t>
-        </is>
-      </c>
       <c r="AD9" t="b">
         <v>0</v>
       </c>
       <c r="AE9" t="b">
         <v>0</v>
       </c>
+      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
@@ -1470,45 +1462,49 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>128115289</v>
+        <v>128115290</v>
       </c>
       <c r="B10" t="n">
-        <v>91452</v>
+        <v>56876</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1202</v>
+        <v>100138</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr"/>
+      <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Selsknösen, Vb</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>742020</v>
+        <v>742080</v>
       </c>
       <c r="R10" t="n">
-        <v>7111950</v>
+        <v>7112234</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1543,13 +1539,17 @@
           <t>2025-08-27</t>
         </is>
       </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Fjäder funnen</t>
+        </is>
+      </c>
       <c r="AD10" t="b">
         <v>0</v>
       </c>
       <c r="AE10" t="b">
         <v>0</v>
       </c>
-      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
@@ -1678,45 +1678,49 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>128115294</v>
+        <v>128115293</v>
       </c>
       <c r="B12" t="n">
-        <v>80092</v>
+        <v>57682</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6456</v>
+        <v>100049</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr"/>
+      <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
           <t>Selsknösen, Vb</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>742181</v>
+        <v>742018</v>
       </c>
       <c r="R12" t="n">
-        <v>7112082</v>
+        <v>7112166</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1775,49 +1779,45 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>128115293</v>
+        <v>128115294</v>
       </c>
       <c r="B13" t="n">
-        <v>57682</v>
+        <v>80092</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100049</v>
+        <v>6456</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="K13" t="inlineStr"/>
-      <c r="L13" t="inlineStr"/>
-      <c r="M13" t="inlineStr"/>
-      <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>Selsknösen, Vb</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>742018</v>
+        <v>742181</v>
       </c>
       <c r="R13" t="n">
-        <v>7112166</v>
+        <v>7112082</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1978,38 +1978,42 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>128115304</v>
+        <v>128115367</v>
       </c>
       <c r="B15" t="n">
-        <v>98571</v>
+        <v>57685</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
-      <c r="J15" t="inlineStr"/>
       <c r="K15" t="inlineStr"/>
       <c r="L15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
@@ -2017,10 +2021,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>741996</v>
+        <v>742063</v>
       </c>
       <c r="R15" t="n">
-        <v>7111968</v>
+        <v>7111956</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2055,13 +2059,17 @@
           <t>2025-08-27</t>
         </is>
       </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
+        </is>
+      </c>
       <c r="AD15" t="b">
         <v>0</v>
       </c>
       <c r="AE15" t="b">
         <v>0</v>
       </c>
-      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
       </c>
@@ -2080,42 +2088,38 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>128115367</v>
+        <v>128115304</v>
       </c>
       <c r="B16" t="n">
-        <v>57685</v>
+        <v>98571</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr"/>
       <c r="K16" t="inlineStr"/>
       <c r="L16" t="inlineStr"/>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
       <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
@@ -2123,10 +2127,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>742063</v>
+        <v>741996</v>
       </c>
       <c r="R16" t="n">
-        <v>7111956</v>
+        <v>7111968</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2161,17 +2165,13 @@
           <t>2025-08-27</t>
         </is>
       </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
-        </is>
-      </c>
       <c r="AD16" t="b">
         <v>0</v>
       </c>
       <c r="AE16" t="b">
         <v>0</v>
       </c>
+      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
@@ -2287,32 +2287,32 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>128115288</v>
+        <v>128115298</v>
       </c>
       <c r="B18" t="n">
-        <v>96918</v>
+        <v>95803</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>1841</v>
+        <v>2809</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Vedflikmossa</t>
+          <t>Mörk husmossa</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Lophozia guttulata</t>
+          <t>Hylocomiastrum umbratum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Lindb. &amp; Arnell) A.Evans</t>
+          <t>(Hedw.) M.Fleisch.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2322,10 +2322,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>742438</v>
+        <v>742124</v>
       </c>
       <c r="R18" t="n">
-        <v>7112145</v>
+        <v>7112073</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2366,7 +2366,6 @@
       <c r="AE18" t="b">
         <v>0</v>
       </c>
-      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>
@@ -2385,32 +2384,32 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>128115298</v>
+        <v>128115288</v>
       </c>
       <c r="B19" t="n">
-        <v>95803</v>
+        <v>96918</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>2809</v>
+        <v>1841</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Mörk husmossa</t>
+          <t>Vedflikmossa</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Hylocomiastrum umbratum</t>
+          <t>Lophozia guttulata</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Hedw.) M.Fleisch.</t>
+          <t>(Lindb. &amp; Arnell) A.Evans</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2420,10 +2419,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>742124</v>
+        <v>742438</v>
       </c>
       <c r="R19" t="n">
-        <v>7112073</v>
+        <v>7112145</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2464,6 +2463,7 @@
       <c r="AE19" t="b">
         <v>0</v>
       </c>
+      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
       </c>
@@ -2870,38 +2870,42 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>128120500</v>
+        <v>128120473</v>
       </c>
       <c r="B24" t="n">
-        <v>98571</v>
+        <v>57685</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
-      <c r="J24" t="inlineStr"/>
       <c r="K24" t="inlineStr"/>
       <c r="L24" t="inlineStr"/>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
@@ -2909,10 +2913,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>741939</v>
+        <v>742178</v>
       </c>
       <c r="R24" t="n">
-        <v>7111973</v>
+        <v>7112150</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -2949,7 +2953,7 @@
       </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>Rikligt</t>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -2958,7 +2962,6 @@
       <c r="AE24" t="b">
         <v>0</v>
       </c>
-      <c r="AF24" t="inlineStr"/>
       <c r="AG24" t="b">
         <v>0</v>
       </c>
@@ -2977,45 +2980,53 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>128120479</v>
+        <v>128120471</v>
       </c>
       <c r="B25" t="n">
-        <v>80217</v>
+        <v>57685</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6462</v>
+        <v>100109</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
+      <c r="K25" t="inlineStr"/>
+      <c r="L25" t="inlineStr"/>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
           <t>Selsknösen, Vb</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>741958</v>
+        <v>742171</v>
       </c>
       <c r="R25" t="n">
-        <v>7111915</v>
+        <v>7112018</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3050,13 +3061,17 @@
           <t>2025-08-27</t>
         </is>
       </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>Ringhacksliknande på gran.</t>
+        </is>
+      </c>
       <c r="AD25" t="b">
         <v>0</v>
       </c>
       <c r="AE25" t="b">
         <v>0</v>
       </c>
-      <c r="AF25" t="inlineStr"/>
       <c r="AG25" t="b">
         <v>0</v>
       </c>
@@ -3180,53 +3195,45 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>128120473</v>
+        <v>128120479</v>
       </c>
       <c r="B27" t="n">
-        <v>57685</v>
+        <v>80217</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>100109</v>
+        <v>6462</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
-      <c r="K27" t="inlineStr"/>
-      <c r="L27" t="inlineStr"/>
-      <c r="M27" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
           <t>Selsknösen, Vb</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>742178</v>
+        <v>741958</v>
       </c>
       <c r="R27" t="n">
-        <v>7112150</v>
+        <v>7111915</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3253,17 +3260,12 @@
       </c>
       <c r="Y27" t="inlineStr">
         <is>
-          <t>2025-08-23</t>
+          <t>2025-08-27</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
         <is>
-          <t>2025-08-23</t>
-        </is>
-      </c>
-      <c r="AC27" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
+          <t>2025-08-27</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3272,6 +3274,7 @@
       <c r="AE27" t="b">
         <v>0</v>
       </c>
+      <c r="AF27" t="inlineStr"/>
       <c r="AG27" t="b">
         <v>0</v>
       </c>
@@ -3290,42 +3293,38 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>128120471</v>
+        <v>128120500</v>
       </c>
       <c r="B28" t="n">
-        <v>57685</v>
+        <v>98571</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
+      <c r="J28" t="inlineStr"/>
       <c r="K28" t="inlineStr"/>
       <c r="L28" t="inlineStr"/>
-      <c r="M28" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
@@ -3333,10 +3332,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>742171</v>
+        <v>741939</v>
       </c>
       <c r="R28" t="n">
-        <v>7112018</v>
+        <v>7111973</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3363,17 +3362,17 @@
       </c>
       <c r="Y28" t="inlineStr">
         <is>
-          <t>2025-08-27</t>
+          <t>2025-08-23</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
         <is>
-          <t>2025-08-27</t>
+          <t>2025-08-23</t>
         </is>
       </c>
       <c r="AC28" t="inlineStr">
         <is>
-          <t>Ringhacksliknande på gran.</t>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3382,6 +3381,7 @@
       <c r="AE28" t="b">
         <v>0</v>
       </c>
+      <c r="AF28" t="inlineStr"/>
       <c r="AG28" t="b">
         <v>0</v>
       </c>
@@ -3901,32 +3901,32 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>128120515</v>
+        <v>128120498</v>
       </c>
       <c r="B34" t="n">
-        <v>91470</v>
+        <v>98571</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>5432</v>
+        <v>220787</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -3936,10 +3936,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>741977</v>
+        <v>742472</v>
       </c>
       <c r="R34" t="n">
-        <v>7111967</v>
+        <v>7112142</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -3966,12 +3966,17 @@
       </c>
       <c r="Y34" t="inlineStr">
         <is>
-          <t>2025-08-23</t>
+          <t>2025-08-27</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
         <is>
-          <t>2025-08-23</t>
+          <t>2025-08-27</t>
+        </is>
+      </c>
+      <c r="AC34" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -3980,6 +3985,7 @@
       <c r="AE34" t="b">
         <v>0</v>
       </c>
+      <c r="AF34" t="inlineStr"/>
       <c r="AG34" t="b">
         <v>0</v>
       </c>
@@ -3998,32 +4004,32 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>128120498</v>
+        <v>128120515</v>
       </c>
       <c r="B35" t="n">
-        <v>98571</v>
+        <v>91470</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>220787</v>
+        <v>5432</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4033,10 +4039,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>742472</v>
+        <v>741977</v>
       </c>
       <c r="R35" t="n">
-        <v>7112142</v>
+        <v>7111967</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4063,17 +4069,12 @@
       </c>
       <c r="Y35" t="inlineStr">
         <is>
-          <t>2025-08-27</t>
+          <t>2025-08-23</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
         <is>
-          <t>2025-08-27</t>
-        </is>
-      </c>
-      <c r="AC35" t="inlineStr">
-        <is>
-          <t>Rikligt</t>
+          <t>2025-08-23</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4082,7 +4083,6 @@
       <c r="AE35" t="b">
         <v>0</v>
       </c>
-      <c r="AF35" t="inlineStr"/>
       <c r="AG35" t="b">
         <v>0</v>
       </c>
@@ -4295,49 +4295,53 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>128120504</v>
+        <v>128120484</v>
       </c>
       <c r="B38" t="n">
-        <v>98571</v>
+        <v>57682</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I38" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr"/>
+      <c r="K38" t="inlineStr"/>
+      <c r="L38" t="inlineStr"/>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
           <t>Selsknösen, Vb</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>741998</v>
+        <v>741951</v>
       </c>
       <c r="R38" t="n">
-        <v>7111958</v>
+        <v>7111949</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4378,7 +4382,6 @@
       <c r="AE38" t="b">
         <v>0</v>
       </c>
-      <c r="AF38" t="inlineStr"/>
       <c r="AG38" t="b">
         <v>0</v>
       </c>
@@ -4397,32 +4400,32 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>128120509</v>
+        <v>128120517</v>
       </c>
       <c r="B39" t="n">
-        <v>98571</v>
+        <v>91470</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>220787</v>
+        <v>5432</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4432,10 +4435,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>742189</v>
+        <v>741968</v>
       </c>
       <c r="R39" t="n">
-        <v>7112063</v>
+        <v>7111957</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4591,45 +4594,49 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>128120517</v>
+        <v>128120504</v>
       </c>
       <c r="B41" t="n">
-        <v>91470</v>
+        <v>98571</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>5432</v>
+        <v>220787</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I41" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
       <c r="P41" t="inlineStr">
         <is>
           <t>Selsknösen, Vb</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>741968</v>
+        <v>741998</v>
       </c>
       <c r="R41" t="n">
-        <v>7111957</v>
+        <v>7111958</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4670,6 +4677,7 @@
       <c r="AE41" t="b">
         <v>0</v>
       </c>
+      <c r="AF41" t="inlineStr"/>
       <c r="AG41" t="b">
         <v>0</v>
       </c>
@@ -4688,53 +4696,45 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>128120484</v>
+        <v>128120509</v>
       </c>
       <c r="B42" t="n">
-        <v>57682</v>
+        <v>98571</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
-      <c r="K42" t="inlineStr"/>
-      <c r="L42" t="inlineStr"/>
-      <c r="M42" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
           <t>Selsknösen, Vb</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>741951</v>
+        <v>742189</v>
       </c>
       <c r="R42" t="n">
-        <v>7111949</v>
+        <v>7112063</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4793,10 +4793,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>128120467</v>
+        <v>128120483</v>
       </c>
       <c r="B43" t="n">
-        <v>91452</v>
+        <v>57682</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4804,34 +4804,42 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>1202</v>
+        <v>100049</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
+      <c r="K43" t="inlineStr"/>
+      <c r="L43" t="inlineStr"/>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
           <t>Selsknösen, Vb</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>742208</v>
+        <v>742340</v>
       </c>
       <c r="R43" t="n">
-        <v>7112210</v>
+        <v>7112183</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4858,12 +4866,12 @@
       </c>
       <c r="Y43" t="inlineStr">
         <is>
-          <t>2025-08-23</t>
+          <t>2025-08-27</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
         <is>
-          <t>2025-08-23</t>
+          <t>2025-08-27</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -4890,10 +4898,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>128120483</v>
+        <v>128120467</v>
       </c>
       <c r="B44" t="n">
-        <v>57682</v>
+        <v>91452</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4901,42 +4909,34 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>100049</v>
+        <v>1202</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
-      <c r="K44" t="inlineStr"/>
-      <c r="L44" t="inlineStr"/>
-      <c r="M44" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
           <t>Selsknösen, Vb</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>742340</v>
+        <v>742208</v>
       </c>
       <c r="R44" t="n">
-        <v>7112183</v>
+        <v>7112210</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -4963,12 +4963,12 @@
       </c>
       <c r="Y44" t="inlineStr">
         <is>
-          <t>2025-08-27</t>
+          <t>2025-08-23</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
         <is>
-          <t>2025-08-27</t>
+          <t>2025-08-23</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5286,27 +5286,27 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>128120531</v>
+        <v>128120524</v>
       </c>
       <c r="B48" t="n">
-        <v>80223</v>
+        <v>79083</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6463</v>
+        <v>6425</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
@@ -5321,10 +5321,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>741963</v>
+        <v>742089</v>
       </c>
       <c r="R48" t="n">
-        <v>7111967</v>
+        <v>7112176</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5351,12 +5351,12 @@
       </c>
       <c r="Y48" t="inlineStr">
         <is>
-          <t>2025-08-27</t>
+          <t>2025-08-23</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
         <is>
-          <t>2025-08-27</t>
+          <t>2025-08-23</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5383,27 +5383,27 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>128120524</v>
+        <v>128120531</v>
       </c>
       <c r="B49" t="n">
-        <v>79083</v>
+        <v>80223</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6425</v>
+        <v>6463</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
@@ -5418,10 +5418,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>742089</v>
+        <v>741963</v>
       </c>
       <c r="R49" t="n">
-        <v>7112176</v>
+        <v>7111967</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5448,12 +5448,12 @@
       </c>
       <c r="Y49" t="inlineStr">
         <is>
-          <t>2025-08-23</t>
+          <t>2025-08-27</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
         <is>
-          <t>2025-08-23</t>
+          <t>2025-08-27</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5480,10 +5480,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>128120488</v>
+        <v>128120521</v>
       </c>
       <c r="B50" t="n">
-        <v>57682</v>
+        <v>79083</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5491,42 +5491,34 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
-      <c r="K50" t="inlineStr"/>
-      <c r="L50" t="inlineStr"/>
-      <c r="M50" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
           <t>Selsknösen, Vb</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>742135</v>
+        <v>741973</v>
       </c>
       <c r="R50" t="n">
-        <v>7112060</v>
+        <v>7112070</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5585,7 +5577,7 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>128120480</v>
+        <v>128120488</v>
       </c>
       <c r="B51" t="n">
         <v>57682</v>
@@ -5618,7 +5610,7 @@
       <c r="L51" t="inlineStr"/>
       <c r="M51" t="inlineStr">
         <is>
-          <t>gammalt bo</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N51" t="inlineStr"/>
@@ -5628,10 +5620,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>742020</v>
+        <v>742135</v>
       </c>
       <c r="R51" t="n">
-        <v>7111987</v>
+        <v>7112060</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5690,10 +5682,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>128120521</v>
+        <v>128120480</v>
       </c>
       <c r="B52" t="n">
-        <v>79083</v>
+        <v>57682</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5701,34 +5693,42 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
+      <c r="K52" t="inlineStr"/>
+      <c r="L52" t="inlineStr"/>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>gammalt bo</t>
+        </is>
+      </c>
+      <c r="N52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
           <t>Selsknösen, Vb</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>741973</v>
+        <v>742020</v>
       </c>
       <c r="R52" t="n">
-        <v>7112070</v>
+        <v>7111987</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5884,10 +5884,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>128120468</v>
+        <v>128120478</v>
       </c>
       <c r="B54" t="n">
-        <v>91452</v>
+        <v>57845</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -5895,21 +5895,21 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>1202</v>
+        <v>103021</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -5919,10 +5919,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>742464</v>
+        <v>741940</v>
       </c>
       <c r="R54" t="n">
-        <v>7112167</v>
+        <v>7111944</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6078,32 +6078,32 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>128120508</v>
+        <v>128120468</v>
       </c>
       <c r="B56" t="n">
-        <v>98571</v>
+        <v>91452</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6113,10 +6113,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>742177</v>
+        <v>742464</v>
       </c>
       <c r="R56" t="n">
-        <v>7112084</v>
+        <v>7112167</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6175,32 +6175,32 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>128120478</v>
+        <v>128120508</v>
       </c>
       <c r="B57" t="n">
-        <v>57845</v>
+        <v>98571</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>103021</v>
+        <v>220787</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6210,10 +6210,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>741940</v>
+        <v>742177</v>
       </c>
       <c r="R57" t="n">
-        <v>7111944</v>
+        <v>7112084</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6466,53 +6466,45 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>128120485</v>
+        <v>128120492</v>
       </c>
       <c r="B60" t="n">
-        <v>57682</v>
+        <v>80092</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>100049</v>
+        <v>6456</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
-      <c r="K60" t="inlineStr"/>
-      <c r="L60" t="inlineStr"/>
-      <c r="M60" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
           <t>Selsknösen, Vb</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>742170</v>
+        <v>741909</v>
       </c>
       <c r="R60" t="n">
-        <v>7112262</v>
+        <v>7111939</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6539,12 +6531,12 @@
       </c>
       <c r="Y60" t="inlineStr">
         <is>
-          <t>2025-08-23</t>
+          <t>2025-08-27</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
         <is>
-          <t>2025-08-23</t>
+          <t>2025-08-27</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -6571,45 +6563,53 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>128120492</v>
+        <v>128120485</v>
       </c>
       <c r="B61" t="n">
-        <v>80092</v>
+        <v>57682</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>6456</v>
+        <v>100049</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
+      <c r="K61" t="inlineStr"/>
+      <c r="L61" t="inlineStr"/>
+      <c r="M61" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
           <t>Selsknösen, Vb</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>741909</v>
+        <v>742170</v>
       </c>
       <c r="R61" t="n">
-        <v>7111939</v>
+        <v>7112262</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -6636,12 +6636,12 @@
       </c>
       <c r="Y61" t="inlineStr">
         <is>
-          <t>2025-08-27</t>
+          <t>2025-08-23</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
         <is>
-          <t>2025-08-27</t>
+          <t>2025-08-23</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7480,10 +7480,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>128120526</v>
+        <v>128120490</v>
       </c>
       <c r="B70" t="n">
-        <v>82942</v>
+        <v>57682</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7491,34 +7491,42 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>1312</v>
+        <v>100049</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
+      <c r="K70" t="inlineStr"/>
+      <c r="L70" t="inlineStr"/>
+      <c r="M70" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N70" t="inlineStr"/>
       <c r="P70" t="inlineStr">
         <is>
           <t>Selsknösen, Vb</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>742268</v>
+        <v>741943</v>
       </c>
       <c r="R70" t="n">
-        <v>7112227</v>
+        <v>7111915</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7545,12 +7553,12 @@
       </c>
       <c r="Y70" t="inlineStr">
         <is>
-          <t>2025-08-23</t>
+          <t>2025-08-27</t>
         </is>
       </c>
       <c r="AA70" t="inlineStr">
         <is>
-          <t>2025-08-23</t>
+          <t>2025-08-27</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -7577,10 +7585,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>128120490</v>
+        <v>128120526</v>
       </c>
       <c r="B71" t="n">
-        <v>57682</v>
+        <v>82942</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -7588,42 +7596,34 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>100049</v>
+        <v>1312</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
-      <c r="K71" t="inlineStr"/>
-      <c r="L71" t="inlineStr"/>
-      <c r="M71" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N71" t="inlineStr"/>
       <c r="P71" t="inlineStr">
         <is>
           <t>Selsknösen, Vb</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>741943</v>
+        <v>742268</v>
       </c>
       <c r="R71" t="n">
-        <v>7111915</v>
+        <v>7112227</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -7650,12 +7650,12 @@
       </c>
       <c r="Y71" t="inlineStr">
         <is>
-          <t>2025-08-27</t>
+          <t>2025-08-23</t>
         </is>
       </c>
       <c r="AA71" t="inlineStr">
         <is>
-          <t>2025-08-27</t>
+          <t>2025-08-23</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -7999,10 +7999,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>128120470</v>
+        <v>128120520</v>
       </c>
       <c r="B75" t="n">
-        <v>91452</v>
+        <v>79083</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8010,21 +8010,21 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -8034,10 +8034,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>741946</v>
+        <v>741965</v>
       </c>
       <c r="R75" t="n">
-        <v>7111928</v>
+        <v>7112091</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8096,10 +8096,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>128120466</v>
+        <v>128120472</v>
       </c>
       <c r="B76" t="n">
-        <v>91452</v>
+        <v>57685</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8107,34 +8107,42 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
+      <c r="K76" t="inlineStr"/>
+      <c r="L76" t="inlineStr"/>
+      <c r="M76" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N76" t="inlineStr"/>
       <c r="P76" t="inlineStr">
         <is>
           <t>Selsknösen, Vb</t>
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>741977</v>
+        <v>741931</v>
       </c>
       <c r="R76" t="n">
-        <v>7111936</v>
+        <v>7111932</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8167,6 +8175,11 @@
       <c r="AA76" t="inlineStr">
         <is>
           <t>2025-08-27</t>
+        </is>
+      </c>
+      <c r="AC76" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på tall.</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -8193,10 +8206,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>128120520</v>
+        <v>128120466</v>
       </c>
       <c r="B77" t="n">
-        <v>79083</v>
+        <v>91452</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8204,21 +8217,21 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
@@ -8228,10 +8241,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>741965</v>
+        <v>741977</v>
       </c>
       <c r="R77" t="n">
-        <v>7112091</v>
+        <v>7111936</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8290,10 +8303,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>128120472</v>
+        <v>128120470</v>
       </c>
       <c r="B78" t="n">
-        <v>57685</v>
+        <v>91452</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -8301,42 +8314,34 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
-      <c r="K78" t="inlineStr"/>
-      <c r="L78" t="inlineStr"/>
-      <c r="M78" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N78" t="inlineStr"/>
       <c r="P78" t="inlineStr">
         <is>
           <t>Selsknösen, Vb</t>
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>741931</v>
+        <v>741946</v>
       </c>
       <c r="R78" t="n">
-        <v>7111932</v>
+        <v>7111928</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -8369,11 +8374,6 @@
       <c r="AA78" t="inlineStr">
         <is>
           <t>2025-08-27</t>
-        </is>
-      </c>
-      <c r="AC78" t="inlineStr">
-        <is>
-          <t>Äldre ringhack på tall.</t>
         </is>
       </c>
       <c r="AD78" t="b">

--- a/artfynd/A 38519-2025 artfynd.xlsx
+++ b/artfynd/A 38519-2025 artfynd.xlsx
@@ -3901,32 +3901,32 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>128120498</v>
+        <v>128120497</v>
       </c>
       <c r="B34" t="n">
-        <v>98571</v>
+        <v>58055</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>220787</v>
+        <v>103015</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -3936,10 +3936,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>742472</v>
+        <v>741902</v>
       </c>
       <c r="R34" t="n">
-        <v>7112142</v>
+        <v>7111998</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -3974,18 +3974,12 @@
           <t>2025-08-27</t>
         </is>
       </c>
-      <c r="AC34" t="inlineStr">
-        <is>
-          <t>Rikligt</t>
-        </is>
-      </c>
       <c r="AD34" t="b">
         <v>0</v>
       </c>
       <c r="AE34" t="b">
         <v>0</v>
       </c>
-      <c r="AF34" t="inlineStr"/>
       <c r="AG34" t="b">
         <v>0</v>
       </c>
@@ -4004,32 +3998,32 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>128120515</v>
+        <v>128120498</v>
       </c>
       <c r="B35" t="n">
-        <v>91470</v>
+        <v>98571</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>5432</v>
+        <v>220787</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4039,10 +4033,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>741977</v>
+        <v>742472</v>
       </c>
       <c r="R35" t="n">
-        <v>7111967</v>
+        <v>7112142</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4069,12 +4063,17 @@
       </c>
       <c r="Y35" t="inlineStr">
         <is>
-          <t>2025-08-23</t>
+          <t>2025-08-27</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
         <is>
-          <t>2025-08-23</t>
+          <t>2025-08-27</t>
+        </is>
+      </c>
+      <c r="AC35" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4083,6 +4082,7 @@
       <c r="AE35" t="b">
         <v>0</v>
       </c>
+      <c r="AF35" t="inlineStr"/>
       <c r="AG35" t="b">
         <v>0</v>
       </c>
@@ -4101,32 +4101,32 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>128120497</v>
+        <v>128120515</v>
       </c>
       <c r="B36" t="n">
-        <v>58055</v>
+        <v>91470</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>103015</v>
+        <v>5432</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4136,10 +4136,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>741902</v>
+        <v>741977</v>
       </c>
       <c r="R36" t="n">
-        <v>7111998</v>
+        <v>7111967</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4166,12 +4166,12 @@
       </c>
       <c r="Y36" t="inlineStr">
         <is>
-          <t>2025-08-27</t>
+          <t>2025-08-23</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
         <is>
-          <t>2025-08-27</t>
+          <t>2025-08-23</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -5884,10 +5884,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>128120478</v>
+        <v>128120522</v>
       </c>
       <c r="B54" t="n">
-        <v>57845</v>
+        <v>79083</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -5895,21 +5895,21 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -5919,10 +5919,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>741940</v>
+        <v>741909</v>
       </c>
       <c r="R54" t="n">
-        <v>7111944</v>
+        <v>7111957</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -5981,10 +5981,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>128120522</v>
+        <v>128120468</v>
       </c>
       <c r="B55" t="n">
-        <v>79083</v>
+        <v>91452</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -5992,21 +5992,21 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6016,10 +6016,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>741909</v>
+        <v>742464</v>
       </c>
       <c r="R55" t="n">
-        <v>7111957</v>
+        <v>7112167</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6078,10 +6078,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>128120468</v>
+        <v>128120478</v>
       </c>
       <c r="B56" t="n">
-        <v>91452</v>
+        <v>57845</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6089,21 +6089,21 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>1202</v>
+        <v>103021</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6113,10 +6113,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>742464</v>
+        <v>741940</v>
       </c>
       <c r="R56" t="n">
-        <v>7112167</v>
+        <v>7111944</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6466,45 +6466,53 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>128120492</v>
+        <v>128120485</v>
       </c>
       <c r="B60" t="n">
-        <v>80092</v>
+        <v>57682</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>6456</v>
+        <v>100049</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
+      <c r="K60" t="inlineStr"/>
+      <c r="L60" t="inlineStr"/>
+      <c r="M60" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
           <t>Selsknösen, Vb</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>741909</v>
+        <v>742170</v>
       </c>
       <c r="R60" t="n">
-        <v>7111939</v>
+        <v>7112262</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6531,12 +6539,12 @@
       </c>
       <c r="Y60" t="inlineStr">
         <is>
-          <t>2025-08-27</t>
+          <t>2025-08-23</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
         <is>
-          <t>2025-08-27</t>
+          <t>2025-08-23</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -6563,53 +6571,45 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>128120485</v>
+        <v>128120492</v>
       </c>
       <c r="B61" t="n">
-        <v>57682</v>
+        <v>80092</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>100049</v>
+        <v>6456</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
-      <c r="K61" t="inlineStr"/>
-      <c r="L61" t="inlineStr"/>
-      <c r="M61" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
           <t>Selsknösen, Vb</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>742170</v>
+        <v>741909</v>
       </c>
       <c r="R61" t="n">
-        <v>7112262</v>
+        <v>7111939</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -6636,12 +6636,12 @@
       </c>
       <c r="Y61" t="inlineStr">
         <is>
-          <t>2025-08-23</t>
+          <t>2025-08-27</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
         <is>
-          <t>2025-08-23</t>
+          <t>2025-08-27</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -8400,45 +8400,49 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>128120477</v>
+        <v>128120503</v>
       </c>
       <c r="B79" t="n">
-        <v>57845</v>
+        <v>98571</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>103021</v>
+        <v>220787</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I79" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I79" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
       <c r="P79" t="inlineStr">
         <is>
           <t>Selsknösen, Vb</t>
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>742054</v>
+        <v>742010</v>
       </c>
       <c r="R79" t="n">
-        <v>7112013</v>
+        <v>7111949</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -8479,6 +8483,7 @@
       <c r="AE79" t="b">
         <v>0</v>
       </c>
+      <c r="AF79" t="inlineStr"/>
       <c r="AG79" t="b">
         <v>0</v>
       </c>
@@ -8497,49 +8502,45 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>128120503</v>
+        <v>128120477</v>
       </c>
       <c r="B80" t="n">
-        <v>98571</v>
+        <v>57845</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I80" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I80" t="inlineStr"/>
       <c r="P80" t="inlineStr">
         <is>
           <t>Selsknösen, Vb</t>
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>742010</v>
+        <v>742054</v>
       </c>
       <c r="R80" t="n">
-        <v>7111949</v>
+        <v>7112013</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -8580,7 +8581,6 @@
       <c r="AE80" t="b">
         <v>0</v>
       </c>
-      <c r="AF80" t="inlineStr"/>
       <c r="AG80" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 38519-2025 artfynd.xlsx
+++ b/artfynd/A 38519-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128115307</v>
       </c>
       <c r="B2" t="n">
-        <v>91470</v>
+        <v>91482</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>128115310</v>
       </c>
       <c r="B3" t="n">
-        <v>79083</v>
+        <v>79087</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
         <v>128115311</v>
       </c>
       <c r="B4" t="n">
-        <v>79083</v>
+        <v>79087</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -969,7 +969,7 @@
         <v>128115303</v>
       </c>
       <c r="B5" t="n">
-        <v>98571</v>
+        <v>98585</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1071,7 +1071,7 @@
         <v>128115305</v>
       </c>
       <c r="B6" t="n">
-        <v>98571</v>
+        <v>98585</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1173,7 +1173,7 @@
         <v>128115285</v>
       </c>
       <c r="B7" t="n">
-        <v>91417</v>
+        <v>91429</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1267,32 +1267,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>128115299</v>
+        <v>128115289</v>
       </c>
       <c r="B8" t="n">
-        <v>80224</v>
+        <v>91464</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6464</v>
+        <v>1202</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1302,10 +1302,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>742269</v>
+        <v>742020</v>
       </c>
       <c r="R8" t="n">
-        <v>7112162</v>
+        <v>7111950</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1346,6 +1346,7 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
+      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
@@ -1364,32 +1365,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>128115289</v>
+        <v>128115299</v>
       </c>
       <c r="B9" t="n">
-        <v>91452</v>
+        <v>80228</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1202</v>
+        <v>6464</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1399,10 +1400,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>742020</v>
+        <v>742269</v>
       </c>
       <c r="R9" t="n">
-        <v>7111950</v>
+        <v>7112162</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1443,7 +1444,6 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
-      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
@@ -1465,7 +1465,7 @@
         <v>128115290</v>
       </c>
       <c r="B10" t="n">
-        <v>56876</v>
+        <v>56880</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1571,7 +1571,7 @@
         <v>128115295</v>
       </c>
       <c r="B11" t="n">
-        <v>57685</v>
+        <v>57689</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1681,7 +1681,7 @@
         <v>128115293</v>
       </c>
       <c r="B12" t="n">
-        <v>57682</v>
+        <v>57686</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1782,7 +1782,7 @@
         <v>128115294</v>
       </c>
       <c r="B13" t="n">
-        <v>80092</v>
+        <v>80096</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1879,7 +1879,7 @@
         <v>128115302</v>
       </c>
       <c r="B14" t="n">
-        <v>98571</v>
+        <v>98585</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1978,42 +1978,38 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>128115367</v>
+        <v>128115304</v>
       </c>
       <c r="B15" t="n">
-        <v>57685</v>
+        <v>98585</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr"/>
       <c r="K15" t="inlineStr"/>
       <c r="L15" t="inlineStr"/>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
       <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
@@ -2021,10 +2017,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>742063</v>
+        <v>741996</v>
       </c>
       <c r="R15" t="n">
-        <v>7111956</v>
+        <v>7111968</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2059,17 +2055,13 @@
           <t>2025-08-27</t>
         </is>
       </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
-        </is>
-      </c>
       <c r="AD15" t="b">
         <v>0</v>
       </c>
       <c r="AE15" t="b">
         <v>0</v>
       </c>
+      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
       </c>
@@ -2088,38 +2080,42 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>128115304</v>
+        <v>128115367</v>
       </c>
       <c r="B16" t="n">
-        <v>98571</v>
+        <v>57689</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="J16" t="inlineStr"/>
       <c r="K16" t="inlineStr"/>
       <c r="L16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
@@ -2127,10 +2123,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>741996</v>
+        <v>742063</v>
       </c>
       <c r="R16" t="n">
-        <v>7111968</v>
+        <v>7111956</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2165,13 +2161,17 @@
           <t>2025-08-27</t>
         </is>
       </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
+        </is>
+      </c>
       <c r="AD16" t="b">
         <v>0</v>
       </c>
       <c r="AE16" t="b">
         <v>0</v>
       </c>
-      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
@@ -2193,7 +2193,7 @@
         <v>128115314</v>
       </c>
       <c r="B17" t="n">
-        <v>98488</v>
+        <v>98502</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2287,32 +2287,32 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>128115298</v>
+        <v>128115288</v>
       </c>
       <c r="B18" t="n">
-        <v>95803</v>
+        <v>96930</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>2809</v>
+        <v>1841</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Mörk husmossa</t>
+          <t>Vedflikmossa</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Hylocomiastrum umbratum</t>
+          <t>Lophozia guttulata</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Hedw.) M.Fleisch.</t>
+          <t>(Lindb. &amp; Arnell) A.Evans</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2322,10 +2322,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>742124</v>
+        <v>742438</v>
       </c>
       <c r="R18" t="n">
-        <v>7112073</v>
+        <v>7112145</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2366,6 +2366,7 @@
       <c r="AE18" t="b">
         <v>0</v>
       </c>
+      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>
@@ -2384,32 +2385,32 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>128115288</v>
+        <v>128115298</v>
       </c>
       <c r="B19" t="n">
-        <v>96918</v>
+        <v>95815</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>1841</v>
+        <v>2809</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Vedflikmossa</t>
+          <t>Mörk husmossa</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Lophozia guttulata</t>
+          <t>Hylocomiastrum umbratum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Lindb. &amp; Arnell) A.Evans</t>
+          <t>(Hedw.) M.Fleisch.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2419,10 +2420,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>742438</v>
+        <v>742124</v>
       </c>
       <c r="R19" t="n">
-        <v>7112145</v>
+        <v>7112073</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2463,7 +2464,6 @@
       <c r="AE19" t="b">
         <v>0</v>
       </c>
-      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
       </c>
@@ -2485,7 +2485,7 @@
         <v>128115287</v>
       </c>
       <c r="B20" t="n">
-        <v>91417</v>
+        <v>91429</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2582,7 +2582,7 @@
         <v>128115286</v>
       </c>
       <c r="B21" t="n">
-        <v>91417</v>
+        <v>91429</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2679,7 +2679,7 @@
         <v>128115309</v>
       </c>
       <c r="B22" t="n">
-        <v>79083</v>
+        <v>79087</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2776,7 +2776,7 @@
         <v>128115313</v>
       </c>
       <c r="B23" t="n">
-        <v>82942</v>
+        <v>82946</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2873,7 +2873,7 @@
         <v>128120473</v>
       </c>
       <c r="B24" t="n">
-        <v>57685</v>
+        <v>57689</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2983,7 +2983,7 @@
         <v>128120471</v>
       </c>
       <c r="B25" t="n">
-        <v>57685</v>
+        <v>57689</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3090,42 +3090,38 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>128120481</v>
+        <v>128120500</v>
       </c>
       <c r="B26" t="n">
-        <v>57682</v>
+        <v>98585</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
+      <c r="J26" t="inlineStr"/>
       <c r="K26" t="inlineStr"/>
       <c r="L26" t="inlineStr"/>
-      <c r="M26" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
@@ -3133,10 +3129,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>742368</v>
+        <v>741939</v>
       </c>
       <c r="R26" t="n">
-        <v>7112244</v>
+        <v>7111973</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3163,12 +3159,17 @@
       </c>
       <c r="Y26" t="inlineStr">
         <is>
-          <t>2025-08-27</t>
+          <t>2025-08-23</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>2025-08-27</t>
+          <t>2025-08-23</t>
+        </is>
+      </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3177,6 +3178,7 @@
       <c r="AE26" t="b">
         <v>0</v>
       </c>
+      <c r="AF26" t="inlineStr"/>
       <c r="AG26" t="b">
         <v>0</v>
       </c>
@@ -3195,45 +3197,53 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>128120479</v>
+        <v>128120481</v>
       </c>
       <c r="B27" t="n">
-        <v>80217</v>
+        <v>57686</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6462</v>
+        <v>100049</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
+      <c r="K27" t="inlineStr"/>
+      <c r="L27" t="inlineStr"/>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
           <t>Selsknösen, Vb</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>741958</v>
+        <v>742368</v>
       </c>
       <c r="R27" t="n">
-        <v>7111915</v>
+        <v>7112244</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3274,7 +3284,6 @@
       <c r="AE27" t="b">
         <v>0</v>
       </c>
-      <c r="AF27" t="inlineStr"/>
       <c r="AG27" t="b">
         <v>0</v>
       </c>
@@ -3293,49 +3302,45 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>128120500</v>
+        <v>128120479</v>
       </c>
       <c r="B28" t="n">
-        <v>98571</v>
+        <v>80221</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>220787</v>
+        <v>6462</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
-      <c r="J28" t="inlineStr"/>
-      <c r="K28" t="inlineStr"/>
-      <c r="L28" t="inlineStr"/>
-      <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
           <t>Selsknösen, Vb</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>741939</v>
+        <v>741958</v>
       </c>
       <c r="R28" t="n">
-        <v>7111973</v>
+        <v>7111915</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3362,17 +3367,12 @@
       </c>
       <c r="Y28" t="inlineStr">
         <is>
-          <t>2025-08-23</t>
+          <t>2025-08-27</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
         <is>
-          <t>2025-08-23</t>
-        </is>
-      </c>
-      <c r="AC28" t="inlineStr">
-        <is>
-          <t>Rikligt</t>
+          <t>2025-08-27</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3403,7 +3403,7 @@
         <v>128120482</v>
       </c>
       <c r="B29" t="n">
-        <v>57682</v>
+        <v>57686</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3505,32 +3505,32 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>128120464</v>
+        <v>128120512</v>
       </c>
       <c r="B30" t="n">
-        <v>91417</v>
+        <v>91482</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>5447</v>
+        <v>5432</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3540,10 +3540,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>742344</v>
+        <v>742457</v>
       </c>
       <c r="R30" t="n">
-        <v>7112196</v>
+        <v>7112145</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3602,32 +3602,32 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>128120512</v>
+        <v>128120464</v>
       </c>
       <c r="B31" t="n">
-        <v>91470</v>
+        <v>91429</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>5432</v>
+        <v>5447</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3637,10 +3637,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>742457</v>
+        <v>742344</v>
       </c>
       <c r="R31" t="n">
-        <v>7112145</v>
+        <v>7112196</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3699,10 +3699,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>128120494</v>
+        <v>128120489</v>
       </c>
       <c r="B32" t="n">
-        <v>80188</v>
+        <v>57686</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3710,34 +3710,42 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6458</v>
+        <v>100049</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
+      <c r="K32" t="inlineStr"/>
+      <c r="L32" t="inlineStr"/>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
           <t>Selsknösen, Vb</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>741962</v>
+        <v>742176</v>
       </c>
       <c r="R32" t="n">
-        <v>7111966</v>
+        <v>7112009</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3796,10 +3804,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>128120489</v>
+        <v>128120494</v>
       </c>
       <c r="B33" t="n">
-        <v>57682</v>
+        <v>80192</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3807,42 +3815,34 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>100049</v>
+        <v>6458</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
-      <c r="K33" t="inlineStr"/>
-      <c r="L33" t="inlineStr"/>
-      <c r="M33" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
           <t>Selsknösen, Vb</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>742176</v>
+        <v>741962</v>
       </c>
       <c r="R33" t="n">
-        <v>7112009</v>
+        <v>7111966</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3904,7 +3904,7 @@
         <v>128120497</v>
       </c>
       <c r="B34" t="n">
-        <v>58055</v>
+        <v>58059</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4001,7 +4001,7 @@
         <v>128120498</v>
       </c>
       <c r="B35" t="n">
-        <v>98571</v>
+        <v>98585</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4104,7 +4104,7 @@
         <v>128120515</v>
       </c>
       <c r="B36" t="n">
-        <v>91470</v>
+        <v>91482</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4201,7 +4201,7 @@
         <v>128120463</v>
       </c>
       <c r="B37" t="n">
-        <v>91417</v>
+        <v>91429</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4298,7 +4298,7 @@
         <v>128120484</v>
       </c>
       <c r="B38" t="n">
-        <v>57682</v>
+        <v>57686</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4403,7 +4403,7 @@
         <v>128120517</v>
       </c>
       <c r="B39" t="n">
-        <v>91470</v>
+        <v>91482</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4497,45 +4497,49 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>128120469</v>
+        <v>128120504</v>
       </c>
       <c r="B40" t="n">
-        <v>91452</v>
+        <v>98585</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I40" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
       <c r="P40" t="inlineStr">
         <is>
           <t>Selsknösen, Vb</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>742088</v>
+        <v>741998</v>
       </c>
       <c r="R40" t="n">
-        <v>7111972</v>
+        <v>7111958</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4576,6 +4580,7 @@
       <c r="AE40" t="b">
         <v>0</v>
       </c>
+      <c r="AF40" t="inlineStr"/>
       <c r="AG40" t="b">
         <v>0</v>
       </c>
@@ -4594,10 +4599,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>128120504</v>
+        <v>128120509</v>
       </c>
       <c r="B41" t="n">
-        <v>98571</v>
+        <v>98585</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4622,21 +4627,17 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I41" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
+      <c r="I41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
           <t>Selsknösen, Vb</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>741998</v>
+        <v>742189</v>
       </c>
       <c r="R41" t="n">
-        <v>7111958</v>
+        <v>7112063</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4677,7 +4678,6 @@
       <c r="AE41" t="b">
         <v>0</v>
       </c>
-      <c r="AF41" t="inlineStr"/>
       <c r="AG41" t="b">
         <v>0</v>
       </c>
@@ -4696,32 +4696,32 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>128120509</v>
+        <v>128120469</v>
       </c>
       <c r="B42" t="n">
-        <v>98571</v>
+        <v>91464</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4731,10 +4731,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>742189</v>
+        <v>742088</v>
       </c>
       <c r="R42" t="n">
-        <v>7112063</v>
+        <v>7111972</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4793,10 +4793,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>128120483</v>
+        <v>128120467</v>
       </c>
       <c r="B43" t="n">
-        <v>57682</v>
+        <v>91464</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4804,42 +4804,34 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>100049</v>
+        <v>1202</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
-      <c r="K43" t="inlineStr"/>
-      <c r="L43" t="inlineStr"/>
-      <c r="M43" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
           <t>Selsknösen, Vb</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>742340</v>
+        <v>742208</v>
       </c>
       <c r="R43" t="n">
-        <v>7112183</v>
+        <v>7112210</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4866,12 +4858,12 @@
       </c>
       <c r="Y43" t="inlineStr">
         <is>
-          <t>2025-08-27</t>
+          <t>2025-08-23</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
         <is>
-          <t>2025-08-27</t>
+          <t>2025-08-23</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -4898,10 +4890,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>128120467</v>
+        <v>128120483</v>
       </c>
       <c r="B44" t="n">
-        <v>91452</v>
+        <v>57686</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4909,34 +4901,42 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>1202</v>
+        <v>100049</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
+      <c r="K44" t="inlineStr"/>
+      <c r="L44" t="inlineStr"/>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
           <t>Selsknösen, Vb</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>742208</v>
+        <v>742340</v>
       </c>
       <c r="R44" t="n">
-        <v>7112210</v>
+        <v>7112183</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -4963,12 +4963,12 @@
       </c>
       <c r="Y44" t="inlineStr">
         <is>
-          <t>2025-08-23</t>
+          <t>2025-08-27</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
         <is>
-          <t>2025-08-23</t>
+          <t>2025-08-27</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -4998,7 +4998,7 @@
         <v>128120507</v>
       </c>
       <c r="B45" t="n">
-        <v>98571</v>
+        <v>98585</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5095,7 +5095,7 @@
         <v>128120513</v>
       </c>
       <c r="B46" t="n">
-        <v>91470</v>
+        <v>91482</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5189,10 +5189,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>128120514</v>
+        <v>128120524</v>
       </c>
       <c r="B47" t="n">
-        <v>91470</v>
+        <v>79087</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5200,21 +5200,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5224,10 +5224,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>742136</v>
+        <v>742089</v>
       </c>
       <c r="R47" t="n">
-        <v>7112081</v>
+        <v>7112176</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5286,10 +5286,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>128120524</v>
+        <v>128120514</v>
       </c>
       <c r="B48" t="n">
-        <v>79083</v>
+        <v>91482</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5297,21 +5297,21 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5321,10 +5321,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>742089</v>
+        <v>742136</v>
       </c>
       <c r="R48" t="n">
-        <v>7112176</v>
+        <v>7112081</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5386,7 +5386,7 @@
         <v>128120531</v>
       </c>
       <c r="B49" t="n">
-        <v>80223</v>
+        <v>80227</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5480,10 +5480,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>128120521</v>
+        <v>128120527</v>
       </c>
       <c r="B50" t="n">
-        <v>79083</v>
+        <v>82946</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5491,21 +5491,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6425</v>
+        <v>1312</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5515,10 +5515,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>741973</v>
+        <v>742229</v>
       </c>
       <c r="R50" t="n">
-        <v>7112070</v>
+        <v>7112259</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5545,12 +5545,12 @@
       </c>
       <c r="Y50" t="inlineStr">
         <is>
-          <t>2025-08-27</t>
+          <t>2025-08-23</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
         <is>
-          <t>2025-08-27</t>
+          <t>2025-08-23</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -5580,7 +5580,7 @@
         <v>128120488</v>
       </c>
       <c r="B51" t="n">
-        <v>57682</v>
+        <v>57686</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5685,7 +5685,7 @@
         <v>128120480</v>
       </c>
       <c r="B52" t="n">
-        <v>57682</v>
+        <v>57686</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5787,10 +5787,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>128120527</v>
+        <v>128120521</v>
       </c>
       <c r="B53" t="n">
-        <v>82942</v>
+        <v>79087</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5798,21 +5798,21 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>1312</v>
+        <v>6425</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -5822,10 +5822,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>742229</v>
+        <v>741973</v>
       </c>
       <c r="R53" t="n">
-        <v>7112259</v>
+        <v>7112070</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -5852,12 +5852,12 @@
       </c>
       <c r="Y53" t="inlineStr">
         <is>
-          <t>2025-08-23</t>
+          <t>2025-08-27</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
         <is>
-          <t>2025-08-23</t>
+          <t>2025-08-27</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -5884,10 +5884,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>128120522</v>
+        <v>128120468</v>
       </c>
       <c r="B54" t="n">
-        <v>79083</v>
+        <v>91464</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -5895,21 +5895,21 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -5919,10 +5919,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>741909</v>
+        <v>742464</v>
       </c>
       <c r="R54" t="n">
-        <v>7111957</v>
+        <v>7112167</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -5981,10 +5981,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>128120468</v>
+        <v>128120522</v>
       </c>
       <c r="B55" t="n">
-        <v>91452</v>
+        <v>79087</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -5992,21 +5992,21 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6016,10 +6016,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>742464</v>
+        <v>741909</v>
       </c>
       <c r="R55" t="n">
-        <v>7112167</v>
+        <v>7111957</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6081,7 +6081,7 @@
         <v>128120478</v>
       </c>
       <c r="B56" t="n">
-        <v>57845</v>
+        <v>57849</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6178,7 +6178,7 @@
         <v>128120508</v>
       </c>
       <c r="B57" t="n">
-        <v>98571</v>
+        <v>98585</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6275,7 +6275,7 @@
         <v>128120523</v>
       </c>
       <c r="B58" t="n">
-        <v>79083</v>
+        <v>79087</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6372,7 +6372,7 @@
         <v>128120506</v>
       </c>
       <c r="B59" t="n">
-        <v>98571</v>
+        <v>98585</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6466,53 +6466,45 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>128120485</v>
+        <v>128120492</v>
       </c>
       <c r="B60" t="n">
-        <v>57682</v>
+        <v>80096</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>100049</v>
+        <v>6456</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
-      <c r="K60" t="inlineStr"/>
-      <c r="L60" t="inlineStr"/>
-      <c r="M60" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
           <t>Selsknösen, Vb</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>742170</v>
+        <v>741909</v>
       </c>
       <c r="R60" t="n">
-        <v>7112262</v>
+        <v>7111939</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6539,12 +6531,12 @@
       </c>
       <c r="Y60" t="inlineStr">
         <is>
-          <t>2025-08-23</t>
+          <t>2025-08-27</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
         <is>
-          <t>2025-08-23</t>
+          <t>2025-08-27</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -6571,45 +6563,53 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>128120492</v>
+        <v>128120485</v>
       </c>
       <c r="B61" t="n">
-        <v>80092</v>
+        <v>57686</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>6456</v>
+        <v>100049</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
+      <c r="K61" t="inlineStr"/>
+      <c r="L61" t="inlineStr"/>
+      <c r="M61" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
           <t>Selsknösen, Vb</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>741909</v>
+        <v>742170</v>
       </c>
       <c r="R61" t="n">
-        <v>7111939</v>
+        <v>7112262</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -6636,12 +6636,12 @@
       </c>
       <c r="Y61" t="inlineStr">
         <is>
-          <t>2025-08-27</t>
+          <t>2025-08-23</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
         <is>
-          <t>2025-08-27</t>
+          <t>2025-08-23</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -6671,7 +6671,7 @@
         <v>128120502</v>
       </c>
       <c r="B62" t="n">
-        <v>98571</v>
+        <v>98585</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6770,10 +6770,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>128120516</v>
+        <v>128120487</v>
       </c>
       <c r="B63" t="n">
-        <v>91470</v>
+        <v>57686</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -6781,34 +6781,42 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>5432</v>
+        <v>100049</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
+      <c r="K63" t="inlineStr"/>
+      <c r="L63" t="inlineStr"/>
+      <c r="M63" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N63" t="inlineStr"/>
       <c r="P63" t="inlineStr">
         <is>
           <t>Selsknösen, Vb</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>742047</v>
+        <v>741971</v>
       </c>
       <c r="R63" t="n">
-        <v>7111978</v>
+        <v>7111953</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -6841,6 +6849,11 @@
       <c r="AA63" t="inlineStr">
         <is>
           <t>2025-08-27</t>
+        </is>
+      </c>
+      <c r="AC63" t="inlineStr">
+        <is>
+          <t>Mycket färska spår, se bild.</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -6870,7 +6883,7 @@
         <v>128120510</v>
       </c>
       <c r="B64" t="n">
-        <v>98571</v>
+        <v>98585</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -6967,7 +6980,7 @@
         <v>128120511</v>
       </c>
       <c r="B65" t="n">
-        <v>98571</v>
+        <v>98585</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7064,7 +7077,7 @@
         <v>128120499</v>
       </c>
       <c r="B66" t="n">
-        <v>98571</v>
+        <v>98585</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7168,10 +7181,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>128120487</v>
+        <v>128120516</v>
       </c>
       <c r="B67" t="n">
-        <v>57682</v>
+        <v>91482</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7179,42 +7192,34 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>100049</v>
+        <v>5432</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
-      <c r="K67" t="inlineStr"/>
-      <c r="L67" t="inlineStr"/>
-      <c r="M67" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N67" t="inlineStr"/>
       <c r="P67" t="inlineStr">
         <is>
           <t>Selsknösen, Vb</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>741971</v>
+        <v>742047</v>
       </c>
       <c r="R67" t="n">
-        <v>7111953</v>
+        <v>7111978</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7247,11 +7252,6 @@
       <c r="AA67" t="inlineStr">
         <is>
           <t>2025-08-27</t>
-        </is>
-      </c>
-      <c r="AC67" t="inlineStr">
-        <is>
-          <t>Mycket färska spår, se bild.</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -7281,7 +7281,7 @@
         <v>128120475</v>
       </c>
       <c r="B68" t="n">
-        <v>57685</v>
+        <v>57689</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7386,7 +7386,7 @@
         <v>128120491</v>
       </c>
       <c r="B69" t="n">
-        <v>80092</v>
+        <v>80096</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7480,10 +7480,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>128120490</v>
+        <v>128120526</v>
       </c>
       <c r="B70" t="n">
-        <v>57682</v>
+        <v>82946</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7491,42 +7491,34 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>100049</v>
+        <v>1312</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
-      <c r="K70" t="inlineStr"/>
-      <c r="L70" t="inlineStr"/>
-      <c r="M70" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N70" t="inlineStr"/>
       <c r="P70" t="inlineStr">
         <is>
           <t>Selsknösen, Vb</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>741943</v>
+        <v>742268</v>
       </c>
       <c r="R70" t="n">
-        <v>7111915</v>
+        <v>7112227</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7553,12 +7545,12 @@
       </c>
       <c r="Y70" t="inlineStr">
         <is>
-          <t>2025-08-27</t>
+          <t>2025-08-23</t>
         </is>
       </c>
       <c r="AA70" t="inlineStr">
         <is>
-          <t>2025-08-27</t>
+          <t>2025-08-23</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -7585,10 +7577,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>128120526</v>
+        <v>128120490</v>
       </c>
       <c r="B71" t="n">
-        <v>82942</v>
+        <v>57686</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -7596,34 +7588,42 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>1312</v>
+        <v>100049</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
+      <c r="K71" t="inlineStr"/>
+      <c r="L71" t="inlineStr"/>
+      <c r="M71" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N71" t="inlineStr"/>
       <c r="P71" t="inlineStr">
         <is>
           <t>Selsknösen, Vb</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>742268</v>
+        <v>741943</v>
       </c>
       <c r="R71" t="n">
-        <v>7112227</v>
+        <v>7111915</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -7650,12 +7650,12 @@
       </c>
       <c r="Y71" t="inlineStr">
         <is>
-          <t>2025-08-23</t>
+          <t>2025-08-27</t>
         </is>
       </c>
       <c r="AA71" t="inlineStr">
         <is>
-          <t>2025-08-23</t>
+          <t>2025-08-27</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -7682,49 +7682,53 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>128120501</v>
+        <v>128120486</v>
       </c>
       <c r="B72" t="n">
-        <v>98571</v>
+        <v>57686</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I72" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr"/>
+      <c r="K72" t="inlineStr"/>
+      <c r="L72" t="inlineStr"/>
+      <c r="M72" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N72" t="inlineStr"/>
       <c r="P72" t="inlineStr">
         <is>
           <t>Selsknösen, Vb</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>742340</v>
+        <v>742107</v>
       </c>
       <c r="R72" t="n">
-        <v>7112209</v>
+        <v>7112066</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -7751,12 +7755,12 @@
       </c>
       <c r="Y72" t="inlineStr">
         <is>
-          <t>2025-08-27</t>
+          <t>2025-08-23</t>
         </is>
       </c>
       <c r="AA72" t="inlineStr">
         <is>
-          <t>2025-08-27</t>
+          <t>2025-08-23</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -7765,7 +7769,6 @@
       <c r="AE72" t="b">
         <v>0</v>
       </c>
-      <c r="AF72" t="inlineStr"/>
       <c r="AG72" t="b">
         <v>0</v>
       </c>
@@ -7784,53 +7787,49 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>128120486</v>
+        <v>128120501</v>
       </c>
       <c r="B73" t="n">
-        <v>57682</v>
+        <v>98585</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I73" t="inlineStr"/>
-      <c r="K73" t="inlineStr"/>
-      <c r="L73" t="inlineStr"/>
-      <c r="M73" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N73" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
       <c r="P73" t="inlineStr">
         <is>
           <t>Selsknösen, Vb</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>742107</v>
+        <v>742340</v>
       </c>
       <c r="R73" t="n">
-        <v>7112066</v>
+        <v>7112209</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -7857,12 +7856,12 @@
       </c>
       <c r="Y73" t="inlineStr">
         <is>
-          <t>2025-08-23</t>
+          <t>2025-08-27</t>
         </is>
       </c>
       <c r="AA73" t="inlineStr">
         <is>
-          <t>2025-08-23</t>
+          <t>2025-08-27</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -7871,6 +7870,7 @@
       <c r="AE73" t="b">
         <v>0</v>
       </c>
+      <c r="AF73" t="inlineStr"/>
       <c r="AG73" t="b">
         <v>0</v>
       </c>
@@ -7892,7 +7892,7 @@
         <v>128120474</v>
       </c>
       <c r="B74" t="n">
-        <v>57685</v>
+        <v>57689</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -7999,10 +7999,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>128120520</v>
+        <v>128120466</v>
       </c>
       <c r="B75" t="n">
-        <v>79083</v>
+        <v>91464</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8010,21 +8010,21 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -8034,10 +8034,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>741965</v>
+        <v>741977</v>
       </c>
       <c r="R75" t="n">
-        <v>7112091</v>
+        <v>7111936</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8096,10 +8096,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>128120472</v>
+        <v>128120470</v>
       </c>
       <c r="B76" t="n">
-        <v>57685</v>
+        <v>91464</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8107,42 +8107,34 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
-      <c r="K76" t="inlineStr"/>
-      <c r="L76" t="inlineStr"/>
-      <c r="M76" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N76" t="inlineStr"/>
       <c r="P76" t="inlineStr">
         <is>
           <t>Selsknösen, Vb</t>
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>741931</v>
+        <v>741946</v>
       </c>
       <c r="R76" t="n">
-        <v>7111932</v>
+        <v>7111928</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8175,11 +8167,6 @@
       <c r="AA76" t="inlineStr">
         <is>
           <t>2025-08-27</t>
-        </is>
-      </c>
-      <c r="AC76" t="inlineStr">
-        <is>
-          <t>Äldre ringhack på tall.</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -8206,10 +8193,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>128120466</v>
+        <v>128120520</v>
       </c>
       <c r="B77" t="n">
-        <v>91452</v>
+        <v>79087</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8217,21 +8204,21 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
@@ -8241,10 +8228,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>741977</v>
+        <v>741965</v>
       </c>
       <c r="R77" t="n">
-        <v>7111936</v>
+        <v>7112091</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8303,10 +8290,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>128120470</v>
+        <v>128120472</v>
       </c>
       <c r="B78" t="n">
-        <v>91452</v>
+        <v>57689</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -8314,34 +8301,42 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
+      <c r="K78" t="inlineStr"/>
+      <c r="L78" t="inlineStr"/>
+      <c r="M78" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N78" t="inlineStr"/>
       <c r="P78" t="inlineStr">
         <is>
           <t>Selsknösen, Vb</t>
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>741946</v>
+        <v>741931</v>
       </c>
       <c r="R78" t="n">
-        <v>7111928</v>
+        <v>7111932</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -8374,6 +8369,11 @@
       <c r="AA78" t="inlineStr">
         <is>
           <t>2025-08-27</t>
+        </is>
+      </c>
+      <c r="AC78" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på tall.</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -8403,7 +8403,7 @@
         <v>128120503</v>
       </c>
       <c r="B79" t="n">
-        <v>98571</v>
+        <v>98585</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -8505,7 +8505,7 @@
         <v>128120477</v>
       </c>
       <c r="B80" t="n">
-        <v>57845</v>
+        <v>57849</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -8602,7 +8602,7 @@
         <v>128314983</v>
       </c>
       <c r="B81" t="n">
-        <v>91810</v>
+        <v>91822</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -8700,7 +8700,7 @@
         <v>128314982</v>
       </c>
       <c r="B82" t="n">
-        <v>91824</v>
+        <v>91836</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>

--- a/artfynd/A 38519-2025 artfynd.xlsx
+++ b/artfynd/A 38519-2025 artfynd.xlsx
@@ -966,7 +966,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128115303</v>
+        <v>128115305</v>
       </c>
       <c r="B5" t="n">
         <v>98585</v>
@@ -1005,10 +1005,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>742050</v>
+        <v>741970</v>
       </c>
       <c r="R5" t="n">
-        <v>7111963</v>
+        <v>7111969</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1068,7 +1068,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128115305</v>
+        <v>128115303</v>
       </c>
       <c r="B6" t="n">
         <v>98585</v>
@@ -1107,10 +1107,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>741970</v>
+        <v>742050</v>
       </c>
       <c r="R6" t="n">
-        <v>7111969</v>
+        <v>7111963</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1267,32 +1267,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>128115289</v>
+        <v>128115299</v>
       </c>
       <c r="B8" t="n">
-        <v>91464</v>
+        <v>80228</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1202</v>
+        <v>6464</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1302,10 +1302,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>742020</v>
+        <v>742269</v>
       </c>
       <c r="R8" t="n">
-        <v>7111950</v>
+        <v>7112162</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1346,7 +1346,6 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
-      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
@@ -1365,32 +1364,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>128115299</v>
+        <v>128115289</v>
       </c>
       <c r="B9" t="n">
-        <v>80228</v>
+        <v>91464</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6464</v>
+        <v>1202</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1400,10 +1399,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>742269</v>
+        <v>742020</v>
       </c>
       <c r="R9" t="n">
-        <v>7112162</v>
+        <v>7111950</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1444,6 +1443,7 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
+      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
@@ -1678,49 +1678,45 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>128115293</v>
+        <v>128115294</v>
       </c>
       <c r="B12" t="n">
-        <v>57686</v>
+        <v>80096</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100049</v>
+        <v>6456</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="K12" t="inlineStr"/>
-      <c r="L12" t="inlineStr"/>
-      <c r="M12" t="inlineStr"/>
-      <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
           <t>Selsknösen, Vb</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>742018</v>
+        <v>742181</v>
       </c>
       <c r="R12" t="n">
-        <v>7112166</v>
+        <v>7112082</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1779,45 +1775,49 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>128115294</v>
+        <v>128115293</v>
       </c>
       <c r="B13" t="n">
-        <v>80096</v>
+        <v>57686</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6456</v>
+        <v>100049</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr"/>
+      <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>Selsknösen, Vb</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>742181</v>
+        <v>742018</v>
       </c>
       <c r="R13" t="n">
-        <v>7112082</v>
+        <v>7112166</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1978,38 +1978,42 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>128115304</v>
+        <v>128115367</v>
       </c>
       <c r="B15" t="n">
-        <v>98585</v>
+        <v>57689</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
-      <c r="J15" t="inlineStr"/>
       <c r="K15" t="inlineStr"/>
       <c r="L15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
@@ -2017,10 +2021,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>741996</v>
+        <v>742063</v>
       </c>
       <c r="R15" t="n">
-        <v>7111968</v>
+        <v>7111956</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2055,13 +2059,17 @@
           <t>2025-08-27</t>
         </is>
       </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
+        </is>
+      </c>
       <c r="AD15" t="b">
         <v>0</v>
       </c>
       <c r="AE15" t="b">
         <v>0</v>
       </c>
-      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
       </c>
@@ -2080,42 +2088,38 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>128115367</v>
+        <v>128115304</v>
       </c>
       <c r="B16" t="n">
-        <v>57689</v>
+        <v>98585</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr"/>
       <c r="K16" t="inlineStr"/>
       <c r="L16" t="inlineStr"/>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
       <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
@@ -2123,10 +2127,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>742063</v>
+        <v>741996</v>
       </c>
       <c r="R16" t="n">
-        <v>7111956</v>
+        <v>7111968</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2161,17 +2165,13 @@
           <t>2025-08-27</t>
         </is>
       </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
-        </is>
-      </c>
       <c r="AD16" t="b">
         <v>0</v>
       </c>
       <c r="AE16" t="b">
         <v>0</v>
       </c>
+      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
@@ -2287,32 +2287,32 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>128115288</v>
+        <v>128115298</v>
       </c>
       <c r="B18" t="n">
-        <v>96930</v>
+        <v>95815</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>1841</v>
+        <v>2809</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Vedflikmossa</t>
+          <t>Mörk husmossa</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Lophozia guttulata</t>
+          <t>Hylocomiastrum umbratum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Lindb. &amp; Arnell) A.Evans</t>
+          <t>(Hedw.) M.Fleisch.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2322,10 +2322,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>742438</v>
+        <v>742124</v>
       </c>
       <c r="R18" t="n">
-        <v>7112145</v>
+        <v>7112073</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2366,7 +2366,6 @@
       <c r="AE18" t="b">
         <v>0</v>
       </c>
-      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>
@@ -2385,32 +2384,32 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>128115298</v>
+        <v>128115288</v>
       </c>
       <c r="B19" t="n">
-        <v>95815</v>
+        <v>96930</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>2809</v>
+        <v>1841</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Mörk husmossa</t>
+          <t>Vedflikmossa</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Hylocomiastrum umbratum</t>
+          <t>Lophozia guttulata</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Hedw.) M.Fleisch.</t>
+          <t>(Lindb. &amp; Arnell) A.Evans</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2420,10 +2419,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>742124</v>
+        <v>742438</v>
       </c>
       <c r="R19" t="n">
-        <v>7112073</v>
+        <v>7112145</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2464,6 +2463,7 @@
       <c r="AE19" t="b">
         <v>0</v>
       </c>
+      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
       </c>
@@ -6770,10 +6770,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>128120487</v>
+        <v>128120516</v>
       </c>
       <c r="B63" t="n">
-        <v>57686</v>
+        <v>91482</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -6781,42 +6781,34 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>100049</v>
+        <v>5432</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
-      <c r="K63" t="inlineStr"/>
-      <c r="L63" t="inlineStr"/>
-      <c r="M63" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N63" t="inlineStr"/>
       <c r="P63" t="inlineStr">
         <is>
           <t>Selsknösen, Vb</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>741971</v>
+        <v>742047</v>
       </c>
       <c r="R63" t="n">
-        <v>7111953</v>
+        <v>7111978</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -6849,11 +6841,6 @@
       <c r="AA63" t="inlineStr">
         <is>
           <t>2025-08-27</t>
-        </is>
-      </c>
-      <c r="AC63" t="inlineStr">
-        <is>
-          <t>Mycket färska spår, se bild.</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -6880,45 +6867,53 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>128120510</v>
+        <v>128120475</v>
       </c>
       <c r="B64" t="n">
-        <v>98585</v>
+        <v>57689</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
+      <c r="K64" t="inlineStr"/>
+      <c r="L64" t="inlineStr"/>
+      <c r="M64" t="inlineStr">
+        <is>
+          <t>gammalt bo</t>
+        </is>
+      </c>
+      <c r="N64" t="inlineStr"/>
       <c r="P64" t="inlineStr">
         <is>
           <t>Selsknösen, Vb</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>742050</v>
+        <v>742203</v>
       </c>
       <c r="R64" t="n">
-        <v>7111983</v>
+        <v>7112188</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -6977,7 +6972,7 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>128120511</v>
+        <v>128120510</v>
       </c>
       <c r="B65" t="n">
         <v>98585</v>
@@ -7012,10 +7007,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>742032</v>
+        <v>742050</v>
       </c>
       <c r="R65" t="n">
-        <v>7111965</v>
+        <v>7111983</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7074,7 +7069,7 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>128120499</v>
+        <v>128120511</v>
       </c>
       <c r="B66" t="n">
         <v>98585</v>
@@ -7103,20 +7098,16 @@
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
-      <c r="J66" t="inlineStr"/>
-      <c r="K66" t="inlineStr"/>
-      <c r="L66" t="inlineStr"/>
-      <c r="N66" t="inlineStr"/>
       <c r="P66" t="inlineStr">
         <is>
           <t>Selsknösen, Vb</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>741963</v>
+        <v>742032</v>
       </c>
       <c r="R66" t="n">
-        <v>7111964</v>
+        <v>7111965</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7151,18 +7142,12 @@
           <t>2025-08-27</t>
         </is>
       </c>
-      <c r="AC66" t="inlineStr">
-        <is>
-          <t>Rikligt</t>
-        </is>
-      </c>
       <c r="AD66" t="b">
         <v>0</v>
       </c>
       <c r="AE66" t="b">
         <v>0</v>
       </c>
-      <c r="AF66" t="inlineStr"/>
       <c r="AG66" t="b">
         <v>0</v>
       </c>
@@ -7181,45 +7166,49 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>128120516</v>
+        <v>128120499</v>
       </c>
       <c r="B67" t="n">
-        <v>91482</v>
+        <v>98585</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>5432</v>
+        <v>220787</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
+      <c r="J67" t="inlineStr"/>
+      <c r="K67" t="inlineStr"/>
+      <c r="L67" t="inlineStr"/>
+      <c r="N67" t="inlineStr"/>
       <c r="P67" t="inlineStr">
         <is>
           <t>Selsknösen, Vb</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>742047</v>
+        <v>741963</v>
       </c>
       <c r="R67" t="n">
-        <v>7111978</v>
+        <v>7111964</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7254,12 +7243,18 @@
           <t>2025-08-27</t>
         </is>
       </c>
+      <c r="AC67" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
+        </is>
+      </c>
       <c r="AD67" t="b">
         <v>0</v>
       </c>
       <c r="AE67" t="b">
         <v>0</v>
       </c>
+      <c r="AF67" t="inlineStr"/>
       <c r="AG67" t="b">
         <v>0</v>
       </c>
@@ -7278,10 +7273,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>128120475</v>
+        <v>128120487</v>
       </c>
       <c r="B68" t="n">
-        <v>57689</v>
+        <v>57686</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7289,16 +7284,16 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
@@ -7311,7 +7306,7 @@
       <c r="L68" t="inlineStr"/>
       <c r="M68" t="inlineStr">
         <is>
-          <t>gammalt bo</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N68" t="inlineStr"/>
@@ -7321,10 +7316,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>742203</v>
+        <v>741971</v>
       </c>
       <c r="R68" t="n">
-        <v>7112188</v>
+        <v>7111953</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7357,6 +7352,11 @@
       <c r="AA68" t="inlineStr">
         <is>
           <t>2025-08-27</t>
+        </is>
+      </c>
+      <c r="AC68" t="inlineStr">
+        <is>
+          <t>Mycket färska spår, se bild.</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -7383,45 +7383,53 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>128120491</v>
+        <v>128120490</v>
       </c>
       <c r="B69" t="n">
-        <v>80096</v>
+        <v>57686</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>6456</v>
+        <v>100049</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
+      <c r="K69" t="inlineStr"/>
+      <c r="L69" t="inlineStr"/>
+      <c r="M69" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N69" t="inlineStr"/>
       <c r="P69" t="inlineStr">
         <is>
           <t>Selsknösen, Vb</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>742255</v>
+        <v>741943</v>
       </c>
       <c r="R69" t="n">
-        <v>7112289</v>
+        <v>7111915</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7480,32 +7488,32 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>128120526</v>
+        <v>128120491</v>
       </c>
       <c r="B70" t="n">
-        <v>82946</v>
+        <v>80096</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>1312</v>
+        <v>6456</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -7515,10 +7523,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>742268</v>
+        <v>742255</v>
       </c>
       <c r="R70" t="n">
-        <v>7112227</v>
+        <v>7112289</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7545,12 +7553,12 @@
       </c>
       <c r="Y70" t="inlineStr">
         <is>
-          <t>2025-08-23</t>
+          <t>2025-08-27</t>
         </is>
       </c>
       <c r="AA70" t="inlineStr">
         <is>
-          <t>2025-08-23</t>
+          <t>2025-08-27</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -7577,10 +7585,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>128120490</v>
+        <v>128120526</v>
       </c>
       <c r="B71" t="n">
-        <v>57686</v>
+        <v>82946</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -7588,42 +7596,34 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>100049</v>
+        <v>1312</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
-      <c r="K71" t="inlineStr"/>
-      <c r="L71" t="inlineStr"/>
-      <c r="M71" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N71" t="inlineStr"/>
       <c r="P71" t="inlineStr">
         <is>
           <t>Selsknösen, Vb</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>741943</v>
+        <v>742268</v>
       </c>
       <c r="R71" t="n">
-        <v>7111915</v>
+        <v>7112227</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -7650,12 +7650,12 @@
       </c>
       <c r="Y71" t="inlineStr">
         <is>
-          <t>2025-08-27</t>
+          <t>2025-08-23</t>
         </is>
       </c>
       <c r="AA71" t="inlineStr">
         <is>
-          <t>2025-08-27</t>
+          <t>2025-08-23</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -7999,10 +7999,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>128120466</v>
+        <v>128120520</v>
       </c>
       <c r="B75" t="n">
-        <v>91464</v>
+        <v>79087</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8010,21 +8010,21 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -8034,10 +8034,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>741977</v>
+        <v>741965</v>
       </c>
       <c r="R75" t="n">
-        <v>7111936</v>
+        <v>7112091</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8096,10 +8096,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>128120470</v>
+        <v>128120472</v>
       </c>
       <c r="B76" t="n">
-        <v>91464</v>
+        <v>57689</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8107,34 +8107,42 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
+      <c r="K76" t="inlineStr"/>
+      <c r="L76" t="inlineStr"/>
+      <c r="M76" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N76" t="inlineStr"/>
       <c r="P76" t="inlineStr">
         <is>
           <t>Selsknösen, Vb</t>
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>741946</v>
+        <v>741931</v>
       </c>
       <c r="R76" t="n">
-        <v>7111928</v>
+        <v>7111932</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8167,6 +8175,11 @@
       <c r="AA76" t="inlineStr">
         <is>
           <t>2025-08-27</t>
+        </is>
+      </c>
+      <c r="AC76" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på tall.</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -8193,10 +8206,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>128120520</v>
+        <v>128120466</v>
       </c>
       <c r="B77" t="n">
-        <v>79087</v>
+        <v>91464</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8204,21 +8217,21 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
@@ -8228,10 +8241,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>741965</v>
+        <v>741977</v>
       </c>
       <c r="R77" t="n">
-        <v>7112091</v>
+        <v>7111936</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8290,10 +8303,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>128120472</v>
+        <v>128120470</v>
       </c>
       <c r="B78" t="n">
-        <v>57689</v>
+        <v>91464</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -8301,42 +8314,34 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
-      <c r="K78" t="inlineStr"/>
-      <c r="L78" t="inlineStr"/>
-      <c r="M78" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N78" t="inlineStr"/>
       <c r="P78" t="inlineStr">
         <is>
           <t>Selsknösen, Vb</t>
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>741931</v>
+        <v>741946</v>
       </c>
       <c r="R78" t="n">
-        <v>7111932</v>
+        <v>7111928</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -8369,11 +8374,6 @@
       <c r="AA78" t="inlineStr">
         <is>
           <t>2025-08-27</t>
-        </is>
-      </c>
-      <c r="AC78" t="inlineStr">
-        <is>
-          <t>Äldre ringhack på tall.</t>
         </is>
       </c>
       <c r="AD78" t="b">

--- a/artfynd/A 38519-2025 artfynd.xlsx
+++ b/artfynd/A 38519-2025 artfynd.xlsx
@@ -869,45 +869,49 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>128115311</v>
+        <v>128115305</v>
       </c>
       <c r="B4" t="n">
-        <v>79087</v>
+        <v>98585</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Selsknösen, Vb</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>742052</v>
+        <v>741970</v>
       </c>
       <c r="R4" t="n">
-        <v>7112024</v>
+        <v>7111969</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -948,6 +952,7 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
+      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
@@ -966,7 +971,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128115305</v>
+        <v>128115303</v>
       </c>
       <c r="B5" t="n">
         <v>98585</v>
@@ -1005,10 +1010,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>741970</v>
+        <v>742050</v>
       </c>
       <c r="R5" t="n">
-        <v>7111969</v>
+        <v>7111963</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1068,49 +1073,45 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128115303</v>
+        <v>128115311</v>
       </c>
       <c r="B6" t="n">
-        <v>98585</v>
+        <v>79087</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
-      <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
-      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Selsknösen, Vb</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>742050</v>
+        <v>742052</v>
       </c>
       <c r="R6" t="n">
-        <v>7111963</v>
+        <v>7112024</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1151,7 +1152,6 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
-      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -1267,32 +1267,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>128115299</v>
+        <v>128115289</v>
       </c>
       <c r="B8" t="n">
-        <v>80228</v>
+        <v>91464</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6464</v>
+        <v>1202</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1302,10 +1302,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>742269</v>
+        <v>742020</v>
       </c>
       <c r="R8" t="n">
-        <v>7112162</v>
+        <v>7111950</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1346,6 +1346,7 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
+      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
@@ -1364,32 +1365,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>128115289</v>
+        <v>128115299</v>
       </c>
       <c r="B9" t="n">
-        <v>91464</v>
+        <v>80228</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1202</v>
+        <v>6464</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1399,10 +1400,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>742020</v>
+        <v>742269</v>
       </c>
       <c r="R9" t="n">
-        <v>7111950</v>
+        <v>7112162</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1443,7 +1444,6 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
-      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
@@ -1678,45 +1678,49 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>128115294</v>
+        <v>128115293</v>
       </c>
       <c r="B12" t="n">
-        <v>80096</v>
+        <v>57686</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6456</v>
+        <v>100049</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr"/>
+      <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
           <t>Selsknösen, Vb</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>742181</v>
+        <v>742018</v>
       </c>
       <c r="R12" t="n">
-        <v>7112082</v>
+        <v>7112166</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1775,49 +1779,45 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>128115293</v>
+        <v>128115294</v>
       </c>
       <c r="B13" t="n">
-        <v>57686</v>
+        <v>80096</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100049</v>
+        <v>6456</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="K13" t="inlineStr"/>
-      <c r="L13" t="inlineStr"/>
-      <c r="M13" t="inlineStr"/>
-      <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>Selsknösen, Vb</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>742018</v>
+        <v>742181</v>
       </c>
       <c r="R13" t="n">
-        <v>7112166</v>
+        <v>7112082</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2287,10 +2287,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>128115298</v>
+        <v>128115287</v>
       </c>
       <c r="B18" t="n">
-        <v>95815</v>
+        <v>91429</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2298,21 +2298,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>2809</v>
+        <v>5447</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Mörk husmossa</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Hylocomiastrum umbratum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Hedw.) M.Fleisch.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2322,10 +2322,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>742124</v>
+        <v>742039</v>
       </c>
       <c r="R18" t="n">
-        <v>7112073</v>
+        <v>7111970</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2482,10 +2482,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>128115287</v>
+        <v>128115298</v>
       </c>
       <c r="B20" t="n">
-        <v>91429</v>
+        <v>95815</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2493,21 +2493,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>5447</v>
+        <v>2809</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Mörk husmossa</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Hylocomiastrum umbratum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Hedw.) M.Fleisch.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2517,10 +2517,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>742039</v>
+        <v>742124</v>
       </c>
       <c r="R20" t="n">
-        <v>7111970</v>
+        <v>7112073</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2870,42 +2870,38 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>128120473</v>
+        <v>128120500</v>
       </c>
       <c r="B24" t="n">
-        <v>57689</v>
+        <v>98588</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
+      <c r="J24" t="inlineStr"/>
       <c r="K24" t="inlineStr"/>
       <c r="L24" t="inlineStr"/>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
@@ -2913,10 +2909,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>742178</v>
+        <v>741939</v>
       </c>
       <c r="R24" t="n">
-        <v>7112150</v>
+        <v>7111973</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -2953,7 +2949,7 @@
       </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>Äldre ringhack</t>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -2962,6 +2958,7 @@
       <c r="AE24" t="b">
         <v>0</v>
       </c>
+      <c r="AF24" t="inlineStr"/>
       <c r="AG24" t="b">
         <v>0</v>
       </c>
@@ -2980,53 +2977,45 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>128120471</v>
+        <v>128120479</v>
       </c>
       <c r="B25" t="n">
-        <v>57689</v>
+        <v>80223</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>100109</v>
+        <v>6462</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
-      <c r="K25" t="inlineStr"/>
-      <c r="L25" t="inlineStr"/>
-      <c r="M25" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
           <t>Selsknösen, Vb</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>742171</v>
+        <v>741958</v>
       </c>
       <c r="R25" t="n">
-        <v>7112018</v>
+        <v>7111915</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3061,17 +3050,13 @@
           <t>2025-08-27</t>
         </is>
       </c>
-      <c r="AC25" t="inlineStr">
-        <is>
-          <t>Ringhacksliknande på gran.</t>
-        </is>
-      </c>
       <c r="AD25" t="b">
         <v>0</v>
       </c>
       <c r="AE25" t="b">
         <v>0</v>
       </c>
+      <c r="AF25" t="inlineStr"/>
       <c r="AG25" t="b">
         <v>0</v>
       </c>
@@ -3090,38 +3075,42 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>128120500</v>
+        <v>128120481</v>
       </c>
       <c r="B26" t="n">
-        <v>98585</v>
+        <v>57686</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
-      <c r="J26" t="inlineStr"/>
       <c r="K26" t="inlineStr"/>
       <c r="L26" t="inlineStr"/>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
@@ -3129,10 +3118,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>741939</v>
+        <v>742368</v>
       </c>
       <c r="R26" t="n">
-        <v>7111973</v>
+        <v>7112244</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3159,17 +3148,12 @@
       </c>
       <c r="Y26" t="inlineStr">
         <is>
-          <t>2025-08-23</t>
+          <t>2025-08-27</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>2025-08-23</t>
-        </is>
-      </c>
-      <c r="AC26" t="inlineStr">
-        <is>
-          <t>Rikligt</t>
+          <t>2025-08-27</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3178,7 +3162,6 @@
       <c r="AE26" t="b">
         <v>0</v>
       </c>
-      <c r="AF26" t="inlineStr"/>
       <c r="AG26" t="b">
         <v>0</v>
       </c>
@@ -3197,10 +3180,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>128120481</v>
+        <v>128120473</v>
       </c>
       <c r="B27" t="n">
-        <v>57686</v>
+        <v>57689</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3208,16 +3191,16 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
@@ -3240,10 +3223,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>742368</v>
+        <v>742178</v>
       </c>
       <c r="R27" t="n">
-        <v>7112244</v>
+        <v>7112150</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3270,12 +3253,17 @@
       </c>
       <c r="Y27" t="inlineStr">
         <is>
-          <t>2025-08-27</t>
+          <t>2025-08-23</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
         <is>
-          <t>2025-08-27</t>
+          <t>2025-08-23</t>
+        </is>
+      </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3302,45 +3290,53 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>128120479</v>
+        <v>128120471</v>
       </c>
       <c r="B28" t="n">
-        <v>80221</v>
+        <v>57689</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6462</v>
+        <v>100109</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
+      <c r="K28" t="inlineStr"/>
+      <c r="L28" t="inlineStr"/>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
           <t>Selsknösen, Vb</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>741958</v>
+        <v>742171</v>
       </c>
       <c r="R28" t="n">
-        <v>7111915</v>
+        <v>7112018</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3375,13 +3371,17 @@
           <t>2025-08-27</t>
         </is>
       </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>Ringhacksliknande på gran.</t>
+        </is>
+      </c>
       <c r="AD28" t="b">
         <v>0</v>
       </c>
       <c r="AE28" t="b">
         <v>0</v>
       </c>
-      <c r="AF28" t="inlineStr"/>
       <c r="AG28" t="b">
         <v>0</v>
       </c>
@@ -3400,53 +3400,45 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>128120482</v>
+        <v>128120464</v>
       </c>
       <c r="B29" t="n">
-        <v>57686</v>
+        <v>91431</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>100049</v>
+        <v>5447</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
-      <c r="K29" t="inlineStr"/>
-      <c r="L29" t="inlineStr"/>
-      <c r="M29" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
           <t>Selsknösen, Vb</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>742472</v>
+        <v>742344</v>
       </c>
       <c r="R29" t="n">
-        <v>7112117</v>
+        <v>7112196</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3508,7 +3500,7 @@
         <v>128120512</v>
       </c>
       <c r="B30" t="n">
-        <v>91482</v>
+        <v>91484</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3602,45 +3594,53 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>128120464</v>
+        <v>128120482</v>
       </c>
       <c r="B31" t="n">
-        <v>91429</v>
+        <v>57686</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>5447</v>
+        <v>100049</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
+      <c r="K31" t="inlineStr"/>
+      <c r="L31" t="inlineStr"/>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
           <t>Selsknösen, Vb</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>742344</v>
+        <v>742472</v>
       </c>
       <c r="R31" t="n">
-        <v>7112196</v>
+        <v>7112117</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3699,10 +3699,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>128120489</v>
+        <v>128120494</v>
       </c>
       <c r="B32" t="n">
-        <v>57686</v>
+        <v>80194</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3710,42 +3710,34 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>100049</v>
+        <v>6458</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
-      <c r="K32" t="inlineStr"/>
-      <c r="L32" t="inlineStr"/>
-      <c r="M32" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
           <t>Selsknösen, Vb</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>742176</v>
+        <v>741962</v>
       </c>
       <c r="R32" t="n">
-        <v>7112009</v>
+        <v>7111966</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3804,10 +3796,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>128120494</v>
+        <v>128120489</v>
       </c>
       <c r="B33" t="n">
-        <v>80192</v>
+        <v>57686</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3815,34 +3807,42 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6458</v>
+        <v>100049</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
+      <c r="K33" t="inlineStr"/>
+      <c r="L33" t="inlineStr"/>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
           <t>Selsknösen, Vb</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>741962</v>
+        <v>742176</v>
       </c>
       <c r="R33" t="n">
-        <v>7111966</v>
+        <v>7112009</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3901,32 +3901,32 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>128120497</v>
+        <v>128120515</v>
       </c>
       <c r="B34" t="n">
-        <v>58059</v>
+        <v>91484</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>103015</v>
+        <v>5432</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -3936,10 +3936,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>741902</v>
+        <v>741977</v>
       </c>
       <c r="R34" t="n">
-        <v>7111998</v>
+        <v>7111967</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -3966,12 +3966,12 @@
       </c>
       <c r="Y34" t="inlineStr">
         <is>
-          <t>2025-08-27</t>
+          <t>2025-08-23</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
         <is>
-          <t>2025-08-27</t>
+          <t>2025-08-23</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -3998,32 +3998,32 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>128120498</v>
+        <v>128120497</v>
       </c>
       <c r="B35" t="n">
-        <v>98585</v>
+        <v>58059</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>220787</v>
+        <v>103015</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4033,10 +4033,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>742472</v>
+        <v>741902</v>
       </c>
       <c r="R35" t="n">
-        <v>7112142</v>
+        <v>7111998</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4071,18 +4071,12 @@
           <t>2025-08-27</t>
         </is>
       </c>
-      <c r="AC35" t="inlineStr">
-        <is>
-          <t>Rikligt</t>
-        </is>
-      </c>
       <c r="AD35" t="b">
         <v>0</v>
       </c>
       <c r="AE35" t="b">
         <v>0</v>
       </c>
-      <c r="AF35" t="inlineStr"/>
       <c r="AG35" t="b">
         <v>0</v>
       </c>
@@ -4101,32 +4095,32 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>128120515</v>
+        <v>128120498</v>
       </c>
       <c r="B36" t="n">
-        <v>91482</v>
+        <v>98588</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>5432</v>
+        <v>220787</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4136,10 +4130,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>741977</v>
+        <v>742472</v>
       </c>
       <c r="R36" t="n">
-        <v>7111967</v>
+        <v>7112142</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4166,12 +4160,17 @@
       </c>
       <c r="Y36" t="inlineStr">
         <is>
-          <t>2025-08-23</t>
+          <t>2025-08-27</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
         <is>
-          <t>2025-08-23</t>
+          <t>2025-08-27</t>
+        </is>
+      </c>
+      <c r="AC36" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4180,6 +4179,7 @@
       <c r="AE36" t="b">
         <v>0</v>
       </c>
+      <c r="AF36" t="inlineStr"/>
       <c r="AG36" t="b">
         <v>0</v>
       </c>
@@ -4201,7 +4201,7 @@
         <v>128120463</v>
       </c>
       <c r="B37" t="n">
-        <v>91429</v>
+        <v>91431</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4295,10 +4295,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>128120484</v>
+        <v>128120517</v>
       </c>
       <c r="B38" t="n">
-        <v>57686</v>
+        <v>91484</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4306,42 +4306,34 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>100049</v>
+        <v>5432</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
-      <c r="K38" t="inlineStr"/>
-      <c r="L38" t="inlineStr"/>
-      <c r="M38" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
           <t>Selsknösen, Vb</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>741951</v>
+        <v>741968</v>
       </c>
       <c r="R38" t="n">
-        <v>7111949</v>
+        <v>7111957</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4400,10 +4392,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>128120517</v>
+        <v>128120469</v>
       </c>
       <c r="B39" t="n">
-        <v>91482</v>
+        <v>91466</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4411,21 +4403,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>5432</v>
+        <v>1202</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4435,10 +4427,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>741968</v>
+        <v>742088</v>
       </c>
       <c r="R39" t="n">
-        <v>7111957</v>
+        <v>7111972</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4497,49 +4489,53 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>128120504</v>
+        <v>128120484</v>
       </c>
       <c r="B40" t="n">
-        <v>98585</v>
+        <v>57686</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I40" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr"/>
+      <c r="K40" t="inlineStr"/>
+      <c r="L40" t="inlineStr"/>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
           <t>Selsknösen, Vb</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>741998</v>
+        <v>741951</v>
       </c>
       <c r="R40" t="n">
-        <v>7111958</v>
+        <v>7111949</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4580,7 +4576,6 @@
       <c r="AE40" t="b">
         <v>0</v>
       </c>
-      <c r="AF40" t="inlineStr"/>
       <c r="AG40" t="b">
         <v>0</v>
       </c>
@@ -4599,10 +4594,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>128120509</v>
+        <v>128120504</v>
       </c>
       <c r="B41" t="n">
-        <v>98585</v>
+        <v>98588</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4627,17 +4622,21 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I41" t="inlineStr"/>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
       <c r="P41" t="inlineStr">
         <is>
           <t>Selsknösen, Vb</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>742189</v>
+        <v>741998</v>
       </c>
       <c r="R41" t="n">
-        <v>7112063</v>
+        <v>7111958</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4678,6 +4677,7 @@
       <c r="AE41" t="b">
         <v>0</v>
       </c>
+      <c r="AF41" t="inlineStr"/>
       <c r="AG41" t="b">
         <v>0</v>
       </c>
@@ -4696,32 +4696,32 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>128120469</v>
+        <v>128120509</v>
       </c>
       <c r="B42" t="n">
-        <v>91464</v>
+        <v>98588</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4731,10 +4731,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>742088</v>
+        <v>742189</v>
       </c>
       <c r="R42" t="n">
-        <v>7111972</v>
+        <v>7112063</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4796,7 +4796,7 @@
         <v>128120467</v>
       </c>
       <c r="B43" t="n">
-        <v>91464</v>
+        <v>91466</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4998,7 +4998,7 @@
         <v>128120507</v>
       </c>
       <c r="B45" t="n">
-        <v>98585</v>
+        <v>98588</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5095,7 +5095,7 @@
         <v>128120513</v>
       </c>
       <c r="B46" t="n">
-        <v>91482</v>
+        <v>91484</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5189,10 +5189,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>128120524</v>
+        <v>128120514</v>
       </c>
       <c r="B47" t="n">
-        <v>79087</v>
+        <v>91484</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5200,21 +5200,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5224,10 +5224,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>742089</v>
+        <v>742136</v>
       </c>
       <c r="R47" t="n">
-        <v>7112176</v>
+        <v>7112081</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5286,10 +5286,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>128120514</v>
+        <v>128120524</v>
       </c>
       <c r="B48" t="n">
-        <v>91482</v>
+        <v>79089</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5297,21 +5297,21 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5321,10 +5321,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>742136</v>
+        <v>742089</v>
       </c>
       <c r="R48" t="n">
-        <v>7112081</v>
+        <v>7112176</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5386,7 +5386,7 @@
         <v>128120531</v>
       </c>
       <c r="B49" t="n">
-        <v>80227</v>
+        <v>80229</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5483,7 +5483,7 @@
         <v>128120527</v>
       </c>
       <c r="B50" t="n">
-        <v>82946</v>
+        <v>82948</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5577,10 +5577,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>128120488</v>
+        <v>128120521</v>
       </c>
       <c r="B51" t="n">
-        <v>57686</v>
+        <v>79089</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5588,42 +5588,34 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
-      <c r="K51" t="inlineStr"/>
-      <c r="L51" t="inlineStr"/>
-      <c r="M51" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
           <t>Selsknösen, Vb</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>742135</v>
+        <v>741973</v>
       </c>
       <c r="R51" t="n">
-        <v>7112060</v>
+        <v>7112070</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5682,7 +5674,7 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>128120480</v>
+        <v>128120488</v>
       </c>
       <c r="B52" t="n">
         <v>57686</v>
@@ -5715,7 +5707,7 @@
       <c r="L52" t="inlineStr"/>
       <c r="M52" t="inlineStr">
         <is>
-          <t>gammalt bo</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N52" t="inlineStr"/>
@@ -5725,10 +5717,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>742020</v>
+        <v>742135</v>
       </c>
       <c r="R52" t="n">
-        <v>7111987</v>
+        <v>7112060</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5787,10 +5779,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>128120521</v>
+        <v>128120480</v>
       </c>
       <c r="B53" t="n">
-        <v>79087</v>
+        <v>57686</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5798,34 +5790,42 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
+      <c r="K53" t="inlineStr"/>
+      <c r="L53" t="inlineStr"/>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>gammalt bo</t>
+        </is>
+      </c>
+      <c r="N53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
           <t>Selsknösen, Vb</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>741973</v>
+        <v>742020</v>
       </c>
       <c r="R53" t="n">
-        <v>7112070</v>
+        <v>7111987</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -5887,7 +5887,7 @@
         <v>128120468</v>
       </c>
       <c r="B54" t="n">
-        <v>91464</v>
+        <v>91466</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -5984,7 +5984,7 @@
         <v>128120522</v>
       </c>
       <c r="B55" t="n">
-        <v>79087</v>
+        <v>79089</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6178,7 +6178,7 @@
         <v>128120508</v>
       </c>
       <c r="B57" t="n">
-        <v>98585</v>
+        <v>98588</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6275,7 +6275,7 @@
         <v>128120523</v>
       </c>
       <c r="B58" t="n">
-        <v>79087</v>
+        <v>79089</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6372,7 +6372,7 @@
         <v>128120506</v>
       </c>
       <c r="B59" t="n">
-        <v>98585</v>
+        <v>98588</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6469,7 +6469,7 @@
         <v>128120492</v>
       </c>
       <c r="B60" t="n">
-        <v>80096</v>
+        <v>80098</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6671,7 +6671,7 @@
         <v>128120502</v>
       </c>
       <c r="B62" t="n">
-        <v>98585</v>
+        <v>98588</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6773,7 +6773,7 @@
         <v>128120516</v>
       </c>
       <c r="B63" t="n">
-        <v>91482</v>
+        <v>91484</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -6975,7 +6975,7 @@
         <v>128120510</v>
       </c>
       <c r="B65" t="n">
-        <v>98585</v>
+        <v>98588</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7072,7 +7072,7 @@
         <v>128120511</v>
       </c>
       <c r="B66" t="n">
-        <v>98585</v>
+        <v>98588</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7169,7 +7169,7 @@
         <v>128120499</v>
       </c>
       <c r="B67" t="n">
-        <v>98585</v>
+        <v>98588</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7383,10 +7383,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>128120490</v>
+        <v>128120526</v>
       </c>
       <c r="B69" t="n">
-        <v>57686</v>
+        <v>82948</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7394,42 +7394,34 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>100049</v>
+        <v>1312</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
-      <c r="K69" t="inlineStr"/>
-      <c r="L69" t="inlineStr"/>
-      <c r="M69" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N69" t="inlineStr"/>
       <c r="P69" t="inlineStr">
         <is>
           <t>Selsknösen, Vb</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>741943</v>
+        <v>742268</v>
       </c>
       <c r="R69" t="n">
-        <v>7111915</v>
+        <v>7112227</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7456,12 +7448,12 @@
       </c>
       <c r="Y69" t="inlineStr">
         <is>
-          <t>2025-08-27</t>
+          <t>2025-08-23</t>
         </is>
       </c>
       <c r="AA69" t="inlineStr">
         <is>
-          <t>2025-08-27</t>
+          <t>2025-08-23</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -7491,7 +7483,7 @@
         <v>128120491</v>
       </c>
       <c r="B70" t="n">
-        <v>80096</v>
+        <v>80098</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7585,10 +7577,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>128120526</v>
+        <v>128120490</v>
       </c>
       <c r="B71" t="n">
-        <v>82946</v>
+        <v>57686</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -7596,34 +7588,42 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>1312</v>
+        <v>100049</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
+      <c r="K71" t="inlineStr"/>
+      <c r="L71" t="inlineStr"/>
+      <c r="M71" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N71" t="inlineStr"/>
       <c r="P71" t="inlineStr">
         <is>
           <t>Selsknösen, Vb</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>742268</v>
+        <v>741943</v>
       </c>
       <c r="R71" t="n">
-        <v>7112227</v>
+        <v>7111915</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -7650,12 +7650,12 @@
       </c>
       <c r="Y71" t="inlineStr">
         <is>
-          <t>2025-08-23</t>
+          <t>2025-08-27</t>
         </is>
       </c>
       <c r="AA71" t="inlineStr">
         <is>
-          <t>2025-08-23</t>
+          <t>2025-08-27</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -7790,7 +7790,7 @@
         <v>128120501</v>
       </c>
       <c r="B73" t="n">
-        <v>98585</v>
+        <v>98588</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -7999,10 +7999,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>128120520</v>
+        <v>128120470</v>
       </c>
       <c r="B75" t="n">
-        <v>79087</v>
+        <v>91466</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8010,21 +8010,21 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -8034,10 +8034,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>741965</v>
+        <v>741946</v>
       </c>
       <c r="R75" t="n">
-        <v>7112091</v>
+        <v>7111928</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8096,10 +8096,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>128120472</v>
+        <v>128120466</v>
       </c>
       <c r="B76" t="n">
-        <v>57689</v>
+        <v>91466</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8107,42 +8107,34 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
-      <c r="K76" t="inlineStr"/>
-      <c r="L76" t="inlineStr"/>
-      <c r="M76" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N76" t="inlineStr"/>
       <c r="P76" t="inlineStr">
         <is>
           <t>Selsknösen, Vb</t>
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>741931</v>
+        <v>741977</v>
       </c>
       <c r="R76" t="n">
-        <v>7111932</v>
+        <v>7111936</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8175,11 +8167,6 @@
       <c r="AA76" t="inlineStr">
         <is>
           <t>2025-08-27</t>
-        </is>
-      </c>
-      <c r="AC76" t="inlineStr">
-        <is>
-          <t>Äldre ringhack på tall.</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -8206,10 +8193,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>128120466</v>
+        <v>128120520</v>
       </c>
       <c r="B77" t="n">
-        <v>91464</v>
+        <v>79089</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8217,21 +8204,21 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
@@ -8241,10 +8228,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>741977</v>
+        <v>741965</v>
       </c>
       <c r="R77" t="n">
-        <v>7111936</v>
+        <v>7112091</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8303,10 +8290,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>128120470</v>
+        <v>128120472</v>
       </c>
       <c r="B78" t="n">
-        <v>91464</v>
+        <v>57689</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -8314,34 +8301,42 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
+      <c r="K78" t="inlineStr"/>
+      <c r="L78" t="inlineStr"/>
+      <c r="M78" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N78" t="inlineStr"/>
       <c r="P78" t="inlineStr">
         <is>
           <t>Selsknösen, Vb</t>
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>741946</v>
+        <v>741931</v>
       </c>
       <c r="R78" t="n">
-        <v>7111928</v>
+        <v>7111932</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -8374,6 +8369,11 @@
       <c r="AA78" t="inlineStr">
         <is>
           <t>2025-08-27</t>
+        </is>
+      </c>
+      <c r="AC78" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på tall.</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -8400,49 +8400,45 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>128120503</v>
+        <v>128120477</v>
       </c>
       <c r="B79" t="n">
-        <v>98585</v>
+        <v>57849</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I79" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I79" t="inlineStr"/>
       <c r="P79" t="inlineStr">
         <is>
           <t>Selsknösen, Vb</t>
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>742010</v>
+        <v>742054</v>
       </c>
       <c r="R79" t="n">
-        <v>7111949</v>
+        <v>7112013</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -8483,7 +8479,6 @@
       <c r="AE79" t="b">
         <v>0</v>
       </c>
-      <c r="AF79" t="inlineStr"/>
       <c r="AG79" t="b">
         <v>0</v>
       </c>
@@ -8502,45 +8497,49 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>128120477</v>
+        <v>128120503</v>
       </c>
       <c r="B80" t="n">
-        <v>57849</v>
+        <v>98588</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>103021</v>
+        <v>220787</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I80" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I80" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
       <c r="P80" t="inlineStr">
         <is>
           <t>Selsknösen, Vb</t>
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>742054</v>
+        <v>742010</v>
       </c>
       <c r="R80" t="n">
-        <v>7112013</v>
+        <v>7111949</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -8581,6 +8580,7 @@
       <c r="AE80" t="b">
         <v>0</v>
       </c>
+      <c r="AF80" t="inlineStr"/>
       <c r="AG80" t="b">
         <v>0</v>
       </c>
@@ -8602,7 +8602,7 @@
         <v>128314983</v>
       </c>
       <c r="B81" t="n">
-        <v>91822</v>
+        <v>91824</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -8700,7 +8700,7 @@
         <v>128314982</v>
       </c>
       <c r="B82" t="n">
-        <v>91836</v>
+        <v>91838</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>

--- a/artfynd/A 38519-2025 artfynd.xlsx
+++ b/artfynd/A 38519-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128115307</v>
       </c>
       <c r="B2" t="n">
-        <v>91482</v>
+        <v>91484</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>128115310</v>
       </c>
       <c r="B3" t="n">
-        <v>79087</v>
+        <v>79089</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -869,49 +869,45 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>128115305</v>
+        <v>128115311</v>
       </c>
       <c r="B4" t="n">
-        <v>98585</v>
+        <v>79089</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
-      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Selsknösen, Vb</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>741970</v>
+        <v>742052</v>
       </c>
       <c r="R4" t="n">
-        <v>7111969</v>
+        <v>7112024</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -952,7 +948,6 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
-      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
@@ -974,7 +969,7 @@
         <v>128115303</v>
       </c>
       <c r="B5" t="n">
-        <v>98585</v>
+        <v>98591</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1073,45 +1068,49 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128115311</v>
+        <v>128115305</v>
       </c>
       <c r="B6" t="n">
-        <v>79087</v>
+        <v>98591</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Selsknösen, Vb</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>742052</v>
+        <v>741970</v>
       </c>
       <c r="R6" t="n">
-        <v>7112024</v>
+        <v>7111969</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1152,6 +1151,7 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
+      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -1173,7 +1173,7 @@
         <v>128115285</v>
       </c>
       <c r="B7" t="n">
-        <v>91429</v>
+        <v>91431</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1267,32 +1267,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>128115289</v>
+        <v>128115299</v>
       </c>
       <c r="B8" t="n">
-        <v>91464</v>
+        <v>80230</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1202</v>
+        <v>6464</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1302,10 +1302,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>742020</v>
+        <v>742269</v>
       </c>
       <c r="R8" t="n">
-        <v>7111950</v>
+        <v>7112162</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1346,7 +1346,6 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
-      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
@@ -1365,10 +1364,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>128115299</v>
+        <v>128115290</v>
       </c>
       <c r="B9" t="n">
-        <v>80228</v>
+        <v>56880</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1376,34 +1375,38 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6464</v>
+        <v>100138</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr"/>
+      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Selsknösen, Vb</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>742269</v>
+        <v>742080</v>
       </c>
       <c r="R9" t="n">
-        <v>7112162</v>
+        <v>7112234</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1436,6 +1439,11 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-08-27</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Fjäder funnen</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1462,49 +1470,45 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>128115290</v>
+        <v>128115289</v>
       </c>
       <c r="B10" t="n">
-        <v>56880</v>
+        <v>91466</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100138</v>
+        <v>1202</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr"/>
-      <c r="M10" t="inlineStr"/>
-      <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Selsknösen, Vb</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>742080</v>
+        <v>742020</v>
       </c>
       <c r="R10" t="n">
-        <v>7112234</v>
+        <v>7111950</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1539,17 +1543,13 @@
           <t>2025-08-27</t>
         </is>
       </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Fjäder funnen</t>
-        </is>
-      </c>
       <c r="AD10" t="b">
         <v>0</v>
       </c>
       <c r="AE10" t="b">
         <v>0</v>
       </c>
+      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
@@ -1782,7 +1782,7 @@
         <v>128115294</v>
       </c>
       <c r="B13" t="n">
-        <v>80096</v>
+        <v>80098</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1879,7 +1879,7 @@
         <v>128115302</v>
       </c>
       <c r="B14" t="n">
-        <v>98585</v>
+        <v>98591</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1978,42 +1978,38 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>128115367</v>
+        <v>128115304</v>
       </c>
       <c r="B15" t="n">
-        <v>57689</v>
+        <v>98591</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr"/>
       <c r="K15" t="inlineStr"/>
       <c r="L15" t="inlineStr"/>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
       <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
@@ -2021,10 +2017,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>742063</v>
+        <v>741996</v>
       </c>
       <c r="R15" t="n">
-        <v>7111956</v>
+        <v>7111968</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2059,17 +2055,13 @@
           <t>2025-08-27</t>
         </is>
       </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
-        </is>
-      </c>
       <c r="AD15" t="b">
         <v>0</v>
       </c>
       <c r="AE15" t="b">
         <v>0</v>
       </c>
+      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
       </c>
@@ -2088,38 +2080,42 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>128115304</v>
+        <v>128115367</v>
       </c>
       <c r="B16" t="n">
-        <v>98585</v>
+        <v>57689</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="J16" t="inlineStr"/>
       <c r="K16" t="inlineStr"/>
       <c r="L16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
@@ -2127,10 +2123,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>741996</v>
+        <v>742063</v>
       </c>
       <c r="R16" t="n">
-        <v>7111968</v>
+        <v>7111956</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2165,13 +2161,17 @@
           <t>2025-08-27</t>
         </is>
       </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
+        </is>
+      </c>
       <c r="AD16" t="b">
         <v>0</v>
       </c>
       <c r="AE16" t="b">
         <v>0</v>
       </c>
-      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
@@ -2193,7 +2193,7 @@
         <v>128115314</v>
       </c>
       <c r="B17" t="n">
-        <v>98502</v>
+        <v>98508</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2290,7 +2290,7 @@
         <v>128115287</v>
       </c>
       <c r="B18" t="n">
-        <v>91429</v>
+        <v>91431</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2384,32 +2384,32 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>128115288</v>
+        <v>128115298</v>
       </c>
       <c r="B19" t="n">
-        <v>96930</v>
+        <v>95817</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>1841</v>
+        <v>2809</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Vedflikmossa</t>
+          <t>Mörk husmossa</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Lophozia guttulata</t>
+          <t>Hylocomiastrum umbratum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Lindb. &amp; Arnell) A.Evans</t>
+          <t>(Hedw.) M.Fleisch.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2419,10 +2419,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>742438</v>
+        <v>742124</v>
       </c>
       <c r="R19" t="n">
-        <v>7112145</v>
+        <v>7112073</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2463,7 +2463,6 @@
       <c r="AE19" t="b">
         <v>0</v>
       </c>
-      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
       </c>
@@ -2482,32 +2481,32 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>128115298</v>
+        <v>128115288</v>
       </c>
       <c r="B20" t="n">
-        <v>95815</v>
+        <v>96932</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>2809</v>
+        <v>1841</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Mörk husmossa</t>
+          <t>Vedflikmossa</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Hylocomiastrum umbratum</t>
+          <t>Lophozia guttulata</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Hedw.) M.Fleisch.</t>
+          <t>(Lindb. &amp; Arnell) A.Evans</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2517,10 +2516,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>742124</v>
+        <v>742438</v>
       </c>
       <c r="R20" t="n">
-        <v>7112073</v>
+        <v>7112145</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2561,6 +2560,7 @@
       <c r="AE20" t="b">
         <v>0</v>
       </c>
+      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
       </c>
@@ -2582,7 +2582,7 @@
         <v>128115286</v>
       </c>
       <c r="B21" t="n">
-        <v>91429</v>
+        <v>91431</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2679,7 +2679,7 @@
         <v>128115309</v>
       </c>
       <c r="B22" t="n">
-        <v>79087</v>
+        <v>79089</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2776,7 +2776,7 @@
         <v>128115313</v>
       </c>
       <c r="B23" t="n">
-        <v>82946</v>
+        <v>82948</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2870,49 +2870,45 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>128120500</v>
+        <v>128120479</v>
       </c>
       <c r="B24" t="n">
-        <v>98588</v>
+        <v>80223</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>220787</v>
+        <v>6462</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
-      <c r="J24" t="inlineStr"/>
-      <c r="K24" t="inlineStr"/>
-      <c r="L24" t="inlineStr"/>
-      <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
           <t>Selsknösen, Vb</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>741939</v>
+        <v>741958</v>
       </c>
       <c r="R24" t="n">
-        <v>7111973</v>
+        <v>7111915</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -2939,17 +2935,12 @@
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>2025-08-23</t>
+          <t>2025-08-27</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>2025-08-23</t>
-        </is>
-      </c>
-      <c r="AC24" t="inlineStr">
-        <is>
-          <t>Rikligt</t>
+          <t>2025-08-27</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -2977,45 +2968,53 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>128120479</v>
+        <v>128120481</v>
       </c>
       <c r="B25" t="n">
-        <v>80223</v>
+        <v>57686</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6462</v>
+        <v>100049</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
+      <c r="K25" t="inlineStr"/>
+      <c r="L25" t="inlineStr"/>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
           <t>Selsknösen, Vb</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>741958</v>
+        <v>742368</v>
       </c>
       <c r="R25" t="n">
-        <v>7111915</v>
+        <v>7112244</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3056,7 +3055,6 @@
       <c r="AE25" t="b">
         <v>0</v>
       </c>
-      <c r="AF25" t="inlineStr"/>
       <c r="AG25" t="b">
         <v>0</v>
       </c>
@@ -3075,10 +3073,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>128120481</v>
+        <v>128120473</v>
       </c>
       <c r="B26" t="n">
-        <v>57686</v>
+        <v>57689</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3086,16 +3084,16 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
@@ -3118,10 +3116,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>742368</v>
+        <v>742178</v>
       </c>
       <c r="R26" t="n">
-        <v>7112244</v>
+        <v>7112150</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3148,12 +3146,17 @@
       </c>
       <c r="Y26" t="inlineStr">
         <is>
-          <t>2025-08-27</t>
+          <t>2025-08-23</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>2025-08-27</t>
+          <t>2025-08-23</t>
+        </is>
+      </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3180,7 +3183,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>128120473</v>
+        <v>128120471</v>
       </c>
       <c r="B27" t="n">
         <v>57689</v>
@@ -3213,7 +3216,7 @@
       <c r="L27" t="inlineStr"/>
       <c r="M27" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N27" t="inlineStr"/>
@@ -3223,10 +3226,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>742178</v>
+        <v>742171</v>
       </c>
       <c r="R27" t="n">
-        <v>7112150</v>
+        <v>7112018</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3253,17 +3256,17 @@
       </c>
       <c r="Y27" t="inlineStr">
         <is>
-          <t>2025-08-23</t>
+          <t>2025-08-27</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
         <is>
-          <t>2025-08-23</t>
+          <t>2025-08-27</t>
         </is>
       </c>
       <c r="AC27" t="inlineStr">
         <is>
-          <t>Äldre ringhack</t>
+          <t>Ringhacksliknande på gran.</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3290,42 +3293,38 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>128120471</v>
+        <v>128120500</v>
       </c>
       <c r="B28" t="n">
-        <v>57689</v>
+        <v>98591</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
+      <c r="J28" t="inlineStr"/>
       <c r="K28" t="inlineStr"/>
       <c r="L28" t="inlineStr"/>
-      <c r="M28" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
@@ -3333,10 +3332,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>742171</v>
+        <v>741939</v>
       </c>
       <c r="R28" t="n">
-        <v>7112018</v>
+        <v>7111973</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3363,17 +3362,17 @@
       </c>
       <c r="Y28" t="inlineStr">
         <is>
-          <t>2025-08-27</t>
+          <t>2025-08-23</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
         <is>
-          <t>2025-08-27</t>
+          <t>2025-08-23</t>
         </is>
       </c>
       <c r="AC28" t="inlineStr">
         <is>
-          <t>Ringhacksliknande på gran.</t>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3382,6 +3381,7 @@
       <c r="AE28" t="b">
         <v>0</v>
       </c>
+      <c r="AF28" t="inlineStr"/>
       <c r="AG28" t="b">
         <v>0</v>
       </c>
@@ -3400,45 +3400,53 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>128120464</v>
+        <v>128120482</v>
       </c>
       <c r="B29" t="n">
-        <v>91431</v>
+        <v>57686</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>5447</v>
+        <v>100049</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
+      <c r="K29" t="inlineStr"/>
+      <c r="L29" t="inlineStr"/>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
           <t>Selsknösen, Vb</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>742344</v>
+        <v>742472</v>
       </c>
       <c r="R29" t="n">
-        <v>7112196</v>
+        <v>7112117</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3497,32 +3505,32 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>128120512</v>
+        <v>128120464</v>
       </c>
       <c r="B30" t="n">
-        <v>91484</v>
+        <v>91431</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>5432</v>
+        <v>5447</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3532,10 +3540,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>742457</v>
+        <v>742344</v>
       </c>
       <c r="R30" t="n">
-        <v>7112145</v>
+        <v>7112196</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3594,10 +3602,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>128120482</v>
+        <v>128120512</v>
       </c>
       <c r="B31" t="n">
-        <v>57686</v>
+        <v>91484</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3605,42 +3613,34 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>100049</v>
+        <v>5432</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
-      <c r="K31" t="inlineStr"/>
-      <c r="L31" t="inlineStr"/>
-      <c r="M31" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
           <t>Selsknösen, Vb</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>742472</v>
+        <v>742457</v>
       </c>
       <c r="R31" t="n">
-        <v>7112117</v>
+        <v>7112145</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4098,7 +4098,7 @@
         <v>128120498</v>
       </c>
       <c r="B36" t="n">
-        <v>98588</v>
+        <v>98591</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4295,10 +4295,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>128120517</v>
+        <v>128120484</v>
       </c>
       <c r="B38" t="n">
-        <v>91484</v>
+        <v>57686</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4306,34 +4306,42 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>5432</v>
+        <v>100049</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
+      <c r="K38" t="inlineStr"/>
+      <c r="L38" t="inlineStr"/>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
           <t>Selsknösen, Vb</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>741968</v>
+        <v>741951</v>
       </c>
       <c r="R38" t="n">
-        <v>7111957</v>
+        <v>7111949</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4489,10 +4497,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>128120484</v>
+        <v>128120517</v>
       </c>
       <c r="B40" t="n">
-        <v>57686</v>
+        <v>91484</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4500,42 +4508,34 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>100049</v>
+        <v>5432</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
-      <c r="K40" t="inlineStr"/>
-      <c r="L40" t="inlineStr"/>
-      <c r="M40" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
           <t>Selsknösen, Vb</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>741951</v>
+        <v>741968</v>
       </c>
       <c r="R40" t="n">
-        <v>7111949</v>
+        <v>7111957</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4594,10 +4594,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>128120504</v>
+        <v>128120509</v>
       </c>
       <c r="B41" t="n">
-        <v>98588</v>
+        <v>98591</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4622,21 +4622,17 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I41" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
+      <c r="I41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
           <t>Selsknösen, Vb</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>741998</v>
+        <v>742189</v>
       </c>
       <c r="R41" t="n">
-        <v>7111958</v>
+        <v>7112063</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4677,7 +4673,6 @@
       <c r="AE41" t="b">
         <v>0</v>
       </c>
-      <c r="AF41" t="inlineStr"/>
       <c r="AG41" t="b">
         <v>0</v>
       </c>
@@ -4696,10 +4691,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>128120509</v>
+        <v>128120504</v>
       </c>
       <c r="B42" t="n">
-        <v>98588</v>
+        <v>98591</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4724,17 +4719,21 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I42" t="inlineStr"/>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
       <c r="P42" t="inlineStr">
         <is>
           <t>Selsknösen, Vb</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>742189</v>
+        <v>741998</v>
       </c>
       <c r="R42" t="n">
-        <v>7112063</v>
+        <v>7111958</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4775,6 +4774,7 @@
       <c r="AE42" t="b">
         <v>0</v>
       </c>
+      <c r="AF42" t="inlineStr"/>
       <c r="AG42" t="b">
         <v>0</v>
       </c>
@@ -4793,32 +4793,32 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>128120467</v>
+        <v>128120507</v>
       </c>
       <c r="B43" t="n">
-        <v>91466</v>
+        <v>98591</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -4828,10 +4828,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>742208</v>
+        <v>742163</v>
       </c>
       <c r="R43" t="n">
-        <v>7112210</v>
+        <v>7112200</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4858,12 +4858,12 @@
       </c>
       <c r="Y43" t="inlineStr">
         <is>
-          <t>2025-08-23</t>
+          <t>2025-08-27</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
         <is>
-          <t>2025-08-23</t>
+          <t>2025-08-27</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -4890,10 +4890,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>128120483</v>
+        <v>128120467</v>
       </c>
       <c r="B44" t="n">
-        <v>57686</v>
+        <v>91466</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4901,42 +4901,34 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>100049</v>
+        <v>1202</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
-      <c r="K44" t="inlineStr"/>
-      <c r="L44" t="inlineStr"/>
-      <c r="M44" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
           <t>Selsknösen, Vb</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>742340</v>
+        <v>742208</v>
       </c>
       <c r="R44" t="n">
-        <v>7112183</v>
+        <v>7112210</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -4963,12 +4955,12 @@
       </c>
       <c r="Y44" t="inlineStr">
         <is>
-          <t>2025-08-27</t>
+          <t>2025-08-23</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
         <is>
-          <t>2025-08-27</t>
+          <t>2025-08-23</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -4995,45 +4987,53 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>128120507</v>
+        <v>128120483</v>
       </c>
       <c r="B45" t="n">
-        <v>98588</v>
+        <v>57686</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
+      <c r="K45" t="inlineStr"/>
+      <c r="L45" t="inlineStr"/>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
           <t>Selsknösen, Vb</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>742163</v>
+        <v>742340</v>
       </c>
       <c r="R45" t="n">
-        <v>7112200</v>
+        <v>7112183</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5981,10 +5981,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>128120522</v>
+        <v>128120478</v>
       </c>
       <c r="B55" t="n">
-        <v>79089</v>
+        <v>57849</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -5992,21 +5992,21 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6016,10 +6016,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>741909</v>
+        <v>741940</v>
       </c>
       <c r="R55" t="n">
-        <v>7111957</v>
+        <v>7111944</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6078,32 +6078,32 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>128120478</v>
+        <v>128120508</v>
       </c>
       <c r="B56" t="n">
-        <v>57849</v>
+        <v>98591</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>103021</v>
+        <v>220787</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6113,10 +6113,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>741940</v>
+        <v>742177</v>
       </c>
       <c r="R56" t="n">
-        <v>7111944</v>
+        <v>7112084</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6175,32 +6175,32 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>128120508</v>
+        <v>128120522</v>
       </c>
       <c r="B57" t="n">
-        <v>98588</v>
+        <v>79089</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6210,10 +6210,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>742177</v>
+        <v>741909</v>
       </c>
       <c r="R57" t="n">
-        <v>7112084</v>
+        <v>7111957</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6272,32 +6272,32 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>128120523</v>
+        <v>128120506</v>
       </c>
       <c r="B58" t="n">
-        <v>79089</v>
+        <v>98591</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6307,10 +6307,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>742019</v>
+        <v>741991</v>
       </c>
       <c r="R58" t="n">
-        <v>7112056</v>
+        <v>7111978</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6337,12 +6337,12 @@
       </c>
       <c r="Y58" t="inlineStr">
         <is>
-          <t>2025-08-23</t>
+          <t>2025-08-27</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
         <is>
-          <t>2025-08-23</t>
+          <t>2025-08-27</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -6369,32 +6369,32 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>128120506</v>
+        <v>128120523</v>
       </c>
       <c r="B59" t="n">
-        <v>98588</v>
+        <v>79089</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -6404,10 +6404,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>741991</v>
+        <v>742019</v>
       </c>
       <c r="R59" t="n">
-        <v>7111978</v>
+        <v>7112056</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6434,12 +6434,12 @@
       </c>
       <c r="Y59" t="inlineStr">
         <is>
-          <t>2025-08-27</t>
+          <t>2025-08-23</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
         <is>
-          <t>2025-08-27</t>
+          <t>2025-08-23</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -6671,7 +6671,7 @@
         <v>128120502</v>
       </c>
       <c r="B62" t="n">
-        <v>98588</v>
+        <v>98591</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6867,10 +6867,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>128120475</v>
+        <v>128120487</v>
       </c>
       <c r="B64" t="n">
-        <v>57689</v>
+        <v>57686</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -6878,16 +6878,16 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
@@ -6900,7 +6900,7 @@
       <c r="L64" t="inlineStr"/>
       <c r="M64" t="inlineStr">
         <is>
-          <t>gammalt bo</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N64" t="inlineStr"/>
@@ -6910,10 +6910,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>742203</v>
+        <v>741971</v>
       </c>
       <c r="R64" t="n">
-        <v>7112188</v>
+        <v>7111953</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -6946,6 +6946,11 @@
       <c r="AA64" t="inlineStr">
         <is>
           <t>2025-08-27</t>
+        </is>
+      </c>
+      <c r="AC64" t="inlineStr">
+        <is>
+          <t>Mycket färska spår, se bild.</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -6975,7 +6980,7 @@
         <v>128120510</v>
       </c>
       <c r="B65" t="n">
-        <v>98588</v>
+        <v>98591</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7072,7 +7077,7 @@
         <v>128120511</v>
       </c>
       <c r="B66" t="n">
-        <v>98588</v>
+        <v>98591</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7169,7 +7174,7 @@
         <v>128120499</v>
       </c>
       <c r="B67" t="n">
-        <v>98588</v>
+        <v>98591</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7273,10 +7278,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>128120487</v>
+        <v>128120475</v>
       </c>
       <c r="B68" t="n">
-        <v>57686</v>
+        <v>57689</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7284,16 +7289,16 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
@@ -7306,7 +7311,7 @@
       <c r="L68" t="inlineStr"/>
       <c r="M68" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>gammalt bo</t>
         </is>
       </c>
       <c r="N68" t="inlineStr"/>
@@ -7316,10 +7321,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>741971</v>
+        <v>742203</v>
       </c>
       <c r="R68" t="n">
-        <v>7111953</v>
+        <v>7112188</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7352,11 +7357,6 @@
       <c r="AA68" t="inlineStr">
         <is>
           <t>2025-08-27</t>
-        </is>
-      </c>
-      <c r="AC68" t="inlineStr">
-        <is>
-          <t>Mycket färska spår, se bild.</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -7790,7 +7790,7 @@
         <v>128120501</v>
       </c>
       <c r="B73" t="n">
-        <v>98588</v>
+        <v>98591</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8193,10 +8193,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>128120520</v>
+        <v>128120472</v>
       </c>
       <c r="B77" t="n">
-        <v>79089</v>
+        <v>57689</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8204,34 +8204,42 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
+      <c r="K77" t="inlineStr"/>
+      <c r="L77" t="inlineStr"/>
+      <c r="M77" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N77" t="inlineStr"/>
       <c r="P77" t="inlineStr">
         <is>
           <t>Selsknösen, Vb</t>
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>741965</v>
+        <v>741931</v>
       </c>
       <c r="R77" t="n">
-        <v>7112091</v>
+        <v>7111932</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8264,6 +8272,11 @@
       <c r="AA77" t="inlineStr">
         <is>
           <t>2025-08-27</t>
+        </is>
+      </c>
+      <c r="AC77" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på tall.</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -8290,10 +8303,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>128120472</v>
+        <v>128120520</v>
       </c>
       <c r="B78" t="n">
-        <v>57689</v>
+        <v>79089</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -8301,42 +8314,34 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
-      <c r="K78" t="inlineStr"/>
-      <c r="L78" t="inlineStr"/>
-      <c r="M78" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N78" t="inlineStr"/>
       <c r="P78" t="inlineStr">
         <is>
           <t>Selsknösen, Vb</t>
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>741931</v>
+        <v>741965</v>
       </c>
       <c r="R78" t="n">
-        <v>7111932</v>
+        <v>7112091</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -8369,11 +8374,6 @@
       <c r="AA78" t="inlineStr">
         <is>
           <t>2025-08-27</t>
-        </is>
-      </c>
-      <c r="AC78" t="inlineStr">
-        <is>
-          <t>Äldre ringhack på tall.</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -8500,7 +8500,7 @@
         <v>128120503</v>
       </c>
       <c r="B80" t="n">
-        <v>98588</v>
+        <v>98591</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>

--- a/artfynd/A 38519-2025 artfynd.xlsx
+++ b/artfynd/A 38519-2025 artfynd.xlsx
@@ -1678,49 +1678,45 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>128115293</v>
+        <v>128115294</v>
       </c>
       <c r="B12" t="n">
-        <v>57686</v>
+        <v>80098</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100049</v>
+        <v>6456</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="K12" t="inlineStr"/>
-      <c r="L12" t="inlineStr"/>
-      <c r="M12" t="inlineStr"/>
-      <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
           <t>Selsknösen, Vb</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>742018</v>
+        <v>742181</v>
       </c>
       <c r="R12" t="n">
-        <v>7112166</v>
+        <v>7112082</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1779,45 +1775,49 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>128115294</v>
+        <v>128115293</v>
       </c>
       <c r="B13" t="n">
-        <v>80098</v>
+        <v>57686</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6456</v>
+        <v>100049</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr"/>
+      <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>Selsknösen, Vb</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>742181</v>
+        <v>742018</v>
       </c>
       <c r="R13" t="n">
-        <v>7112082</v>
+        <v>7112166</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2968,10 +2968,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>128120481</v>
+        <v>128120473</v>
       </c>
       <c r="B25" t="n">
-        <v>57686</v>
+        <v>57689</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2979,16 +2979,16 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
@@ -3011,10 +3011,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>742368</v>
+        <v>742178</v>
       </c>
       <c r="R25" t="n">
-        <v>7112244</v>
+        <v>7112150</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3041,12 +3041,17 @@
       </c>
       <c r="Y25" t="inlineStr">
         <is>
-          <t>2025-08-27</t>
+          <t>2025-08-23</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>2025-08-27</t>
+          <t>2025-08-23</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3073,7 +3078,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>128120473</v>
+        <v>128120471</v>
       </c>
       <c r="B26" t="n">
         <v>57689</v>
@@ -3106,7 +3111,7 @@
       <c r="L26" t="inlineStr"/>
       <c r="M26" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N26" t="inlineStr"/>
@@ -3116,10 +3121,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>742178</v>
+        <v>742171</v>
       </c>
       <c r="R26" t="n">
-        <v>7112150</v>
+        <v>7112018</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3146,17 +3151,17 @@
       </c>
       <c r="Y26" t="inlineStr">
         <is>
-          <t>2025-08-23</t>
+          <t>2025-08-27</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>2025-08-23</t>
+          <t>2025-08-27</t>
         </is>
       </c>
       <c r="AC26" t="inlineStr">
         <is>
-          <t>Äldre ringhack</t>
+          <t>Ringhacksliknande på gran.</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3183,42 +3188,38 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>128120471</v>
+        <v>128120500</v>
       </c>
       <c r="B27" t="n">
-        <v>57689</v>
+        <v>98591</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
+      <c r="J27" t="inlineStr"/>
       <c r="K27" t="inlineStr"/>
       <c r="L27" t="inlineStr"/>
-      <c r="M27" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
@@ -3226,10 +3227,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>742171</v>
+        <v>741939</v>
       </c>
       <c r="R27" t="n">
-        <v>7112018</v>
+        <v>7111973</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3256,17 +3257,17 @@
       </c>
       <c r="Y27" t="inlineStr">
         <is>
-          <t>2025-08-27</t>
+          <t>2025-08-23</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
         <is>
-          <t>2025-08-27</t>
+          <t>2025-08-23</t>
         </is>
       </c>
       <c r="AC27" t="inlineStr">
         <is>
-          <t>Ringhacksliknande på gran.</t>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3275,6 +3276,7 @@
       <c r="AE27" t="b">
         <v>0</v>
       </c>
+      <c r="AF27" t="inlineStr"/>
       <c r="AG27" t="b">
         <v>0</v>
       </c>
@@ -3293,38 +3295,42 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>128120500</v>
+        <v>128120481</v>
       </c>
       <c r="B28" t="n">
-        <v>98591</v>
+        <v>57686</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
-      <c r="J28" t="inlineStr"/>
       <c r="K28" t="inlineStr"/>
       <c r="L28" t="inlineStr"/>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
@@ -3332,10 +3338,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>741939</v>
+        <v>742368</v>
       </c>
       <c r="R28" t="n">
-        <v>7111973</v>
+        <v>7112244</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3362,17 +3368,12 @@
       </c>
       <c r="Y28" t="inlineStr">
         <is>
-          <t>2025-08-23</t>
+          <t>2025-08-27</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
         <is>
-          <t>2025-08-23</t>
-        </is>
-      </c>
-      <c r="AC28" t="inlineStr">
-        <is>
-          <t>Rikligt</t>
+          <t>2025-08-27</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3381,7 +3382,6 @@
       <c r="AE28" t="b">
         <v>0</v>
       </c>
-      <c r="AF28" t="inlineStr"/>
       <c r="AG28" t="b">
         <v>0</v>
       </c>
@@ -3400,53 +3400,45 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>128120482</v>
+        <v>128120464</v>
       </c>
       <c r="B29" t="n">
-        <v>57686</v>
+        <v>91431</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>100049</v>
+        <v>5447</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
-      <c r="K29" t="inlineStr"/>
-      <c r="L29" t="inlineStr"/>
-      <c r="M29" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
           <t>Selsknösen, Vb</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>742472</v>
+        <v>742344</v>
       </c>
       <c r="R29" t="n">
-        <v>7112117</v>
+        <v>7112196</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3505,45 +3497,53 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>128120464</v>
+        <v>128120482</v>
       </c>
       <c r="B30" t="n">
-        <v>91431</v>
+        <v>57686</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>5447</v>
+        <v>100049</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
+      <c r="K30" t="inlineStr"/>
+      <c r="L30" t="inlineStr"/>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
           <t>Selsknösen, Vb</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>742344</v>
+        <v>742472</v>
       </c>
       <c r="R30" t="n">
-        <v>7112196</v>
+        <v>7112117</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3901,32 +3901,32 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>128120515</v>
+        <v>128120497</v>
       </c>
       <c r="B34" t="n">
-        <v>91484</v>
+        <v>58059</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>5432</v>
+        <v>103015</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -3936,10 +3936,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>741977</v>
+        <v>741902</v>
       </c>
       <c r="R34" t="n">
-        <v>7111967</v>
+        <v>7111998</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -3966,12 +3966,12 @@
       </c>
       <c r="Y34" t="inlineStr">
         <is>
-          <t>2025-08-23</t>
+          <t>2025-08-27</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
         <is>
-          <t>2025-08-23</t>
+          <t>2025-08-27</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -3998,32 +3998,32 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>128120497</v>
+        <v>128120498</v>
       </c>
       <c r="B35" t="n">
-        <v>58059</v>
+        <v>98591</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>103015</v>
+        <v>220787</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4033,10 +4033,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>741902</v>
+        <v>742472</v>
       </c>
       <c r="R35" t="n">
-        <v>7111998</v>
+        <v>7112142</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4071,12 +4071,18 @@
           <t>2025-08-27</t>
         </is>
       </c>
+      <c r="AC35" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
+        </is>
+      </c>
       <c r="AD35" t="b">
         <v>0</v>
       </c>
       <c r="AE35" t="b">
         <v>0</v>
       </c>
+      <c r="AF35" t="inlineStr"/>
       <c r="AG35" t="b">
         <v>0</v>
       </c>
@@ -4095,32 +4101,32 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>128120498</v>
+        <v>128120515</v>
       </c>
       <c r="B36" t="n">
-        <v>98591</v>
+        <v>91484</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>220787</v>
+        <v>5432</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4130,10 +4136,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>742472</v>
+        <v>741977</v>
       </c>
       <c r="R36" t="n">
-        <v>7112142</v>
+        <v>7111967</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4160,17 +4166,12 @@
       </c>
       <c r="Y36" t="inlineStr">
         <is>
-          <t>2025-08-27</t>
+          <t>2025-08-23</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
         <is>
-          <t>2025-08-27</t>
-        </is>
-      </c>
-      <c r="AC36" t="inlineStr">
-        <is>
-          <t>Rikligt</t>
+          <t>2025-08-23</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4179,7 +4180,6 @@
       <c r="AE36" t="b">
         <v>0</v>
       </c>
-      <c r="AF36" t="inlineStr"/>
       <c r="AG36" t="b">
         <v>0</v>
       </c>
@@ -4793,45 +4793,53 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>128120507</v>
+        <v>128120483</v>
       </c>
       <c r="B43" t="n">
-        <v>98591</v>
+        <v>57686</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
+      <c r="K43" t="inlineStr"/>
+      <c r="L43" t="inlineStr"/>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
           <t>Selsknösen, Vb</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>742163</v>
+        <v>742340</v>
       </c>
       <c r="R43" t="n">
-        <v>7112200</v>
+        <v>7112183</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4987,53 +4995,45 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>128120483</v>
+        <v>128120507</v>
       </c>
       <c r="B45" t="n">
-        <v>57686</v>
+        <v>98591</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
-      <c r="K45" t="inlineStr"/>
-      <c r="L45" t="inlineStr"/>
-      <c r="M45" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
           <t>Selsknösen, Vb</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>742340</v>
+        <v>742163</v>
       </c>
       <c r="R45" t="n">
-        <v>7112183</v>
+        <v>7112200</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5577,10 +5577,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>128120521</v>
+        <v>128120488</v>
       </c>
       <c r="B51" t="n">
-        <v>79089</v>
+        <v>57686</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5588,34 +5588,42 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
+      <c r="K51" t="inlineStr"/>
+      <c r="L51" t="inlineStr"/>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
           <t>Selsknösen, Vb</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>741973</v>
+        <v>742135</v>
       </c>
       <c r="R51" t="n">
-        <v>7112070</v>
+        <v>7112060</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5674,7 +5682,7 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>128120488</v>
+        <v>128120480</v>
       </c>
       <c r="B52" t="n">
         <v>57686</v>
@@ -5707,7 +5715,7 @@
       <c r="L52" t="inlineStr"/>
       <c r="M52" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>gammalt bo</t>
         </is>
       </c>
       <c r="N52" t="inlineStr"/>
@@ -5717,10 +5725,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>742135</v>
+        <v>742020</v>
       </c>
       <c r="R52" t="n">
-        <v>7112060</v>
+        <v>7111987</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5779,10 +5787,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>128120480</v>
+        <v>128120521</v>
       </c>
       <c r="B53" t="n">
-        <v>57686</v>
+        <v>79089</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5790,42 +5798,34 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
-      <c r="K53" t="inlineStr"/>
-      <c r="L53" t="inlineStr"/>
-      <c r="M53" t="inlineStr">
-        <is>
-          <t>gammalt bo</t>
-        </is>
-      </c>
-      <c r="N53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
           <t>Selsknösen, Vb</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>742020</v>
+        <v>741973</v>
       </c>
       <c r="R53" t="n">
-        <v>7111987</v>
+        <v>7112070</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -5981,10 +5981,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>128120478</v>
+        <v>128120522</v>
       </c>
       <c r="B55" t="n">
-        <v>57849</v>
+        <v>79089</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -5992,21 +5992,21 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6016,10 +6016,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>741940</v>
+        <v>741909</v>
       </c>
       <c r="R55" t="n">
-        <v>7111944</v>
+        <v>7111957</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6175,10 +6175,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>128120522</v>
+        <v>128120478</v>
       </c>
       <c r="B57" t="n">
-        <v>79089</v>
+        <v>57849</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6186,21 +6186,21 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6210,10 +6210,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>741909</v>
+        <v>741940</v>
       </c>
       <c r="R57" t="n">
-        <v>7111957</v>
+        <v>7111944</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -7480,45 +7480,53 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>128120491</v>
+        <v>128120490</v>
       </c>
       <c r="B70" t="n">
-        <v>80098</v>
+        <v>57686</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>6456</v>
+        <v>100049</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
+      <c r="K70" t="inlineStr"/>
+      <c r="L70" t="inlineStr"/>
+      <c r="M70" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N70" t="inlineStr"/>
       <c r="P70" t="inlineStr">
         <is>
           <t>Selsknösen, Vb</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>742255</v>
+        <v>741943</v>
       </c>
       <c r="R70" t="n">
-        <v>7112289</v>
+        <v>7111915</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7577,53 +7585,45 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>128120490</v>
+        <v>128120491</v>
       </c>
       <c r="B71" t="n">
-        <v>57686</v>
+        <v>80098</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>100049</v>
+        <v>6456</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
-      <c r="K71" t="inlineStr"/>
-      <c r="L71" t="inlineStr"/>
-      <c r="M71" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N71" t="inlineStr"/>
       <c r="P71" t="inlineStr">
         <is>
           <t>Selsknösen, Vb</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>741943</v>
+        <v>742255</v>
       </c>
       <c r="R71" t="n">
-        <v>7111915</v>
+        <v>7112289</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -8193,10 +8193,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>128120472</v>
+        <v>128120520</v>
       </c>
       <c r="B77" t="n">
-        <v>57689</v>
+        <v>79089</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8204,42 +8204,34 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
-      <c r="K77" t="inlineStr"/>
-      <c r="L77" t="inlineStr"/>
-      <c r="M77" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N77" t="inlineStr"/>
       <c r="P77" t="inlineStr">
         <is>
           <t>Selsknösen, Vb</t>
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>741931</v>
+        <v>741965</v>
       </c>
       <c r="R77" t="n">
-        <v>7111932</v>
+        <v>7112091</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8272,11 +8264,6 @@
       <c r="AA77" t="inlineStr">
         <is>
           <t>2025-08-27</t>
-        </is>
-      </c>
-      <c r="AC77" t="inlineStr">
-        <is>
-          <t>Äldre ringhack på tall.</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -8303,10 +8290,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>128120520</v>
+        <v>128120472</v>
       </c>
       <c r="B78" t="n">
-        <v>79089</v>
+        <v>57689</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -8314,34 +8301,42 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
+      <c r="K78" t="inlineStr"/>
+      <c r="L78" t="inlineStr"/>
+      <c r="M78" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N78" t="inlineStr"/>
       <c r="P78" t="inlineStr">
         <is>
           <t>Selsknösen, Vb</t>
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>741965</v>
+        <v>741931</v>
       </c>
       <c r="R78" t="n">
-        <v>7112091</v>
+        <v>7111932</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -8374,6 +8369,11 @@
       <c r="AA78" t="inlineStr">
         <is>
           <t>2025-08-27</t>
+        </is>
+      </c>
+      <c r="AC78" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på tall.</t>
         </is>
       </c>
       <c r="AD78" t="b">

--- a/artfynd/A 38519-2025 artfynd.xlsx
+++ b/artfynd/A 38519-2025 artfynd.xlsx
@@ -2870,45 +2870,53 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>128120479</v>
+        <v>128120481</v>
       </c>
       <c r="B24" t="n">
-        <v>80223</v>
+        <v>57686</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6462</v>
+        <v>100049</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
+      <c r="K24" t="inlineStr"/>
+      <c r="L24" t="inlineStr"/>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
           <t>Selsknösen, Vb</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>741958</v>
+        <v>742368</v>
       </c>
       <c r="R24" t="n">
-        <v>7111915</v>
+        <v>7112244</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -2949,7 +2957,6 @@
       <c r="AE24" t="b">
         <v>0</v>
       </c>
-      <c r="AF24" t="inlineStr"/>
       <c r="AG24" t="b">
         <v>0</v>
       </c>
@@ -3188,49 +3195,45 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>128120500</v>
+        <v>128120479</v>
       </c>
       <c r="B27" t="n">
-        <v>98591</v>
+        <v>80223</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>220787</v>
+        <v>6462</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
-      <c r="J27" t="inlineStr"/>
-      <c r="K27" t="inlineStr"/>
-      <c r="L27" t="inlineStr"/>
-      <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
           <t>Selsknösen, Vb</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>741939</v>
+        <v>741958</v>
       </c>
       <c r="R27" t="n">
-        <v>7111973</v>
+        <v>7111915</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3257,17 +3260,12 @@
       </c>
       <c r="Y27" t="inlineStr">
         <is>
-          <t>2025-08-23</t>
+          <t>2025-08-27</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
         <is>
-          <t>2025-08-23</t>
-        </is>
-      </c>
-      <c r="AC27" t="inlineStr">
-        <is>
-          <t>Rikligt</t>
+          <t>2025-08-27</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3295,42 +3293,38 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>128120481</v>
+        <v>128120500</v>
       </c>
       <c r="B28" t="n">
-        <v>57686</v>
+        <v>98592</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
+      <c r="J28" t="inlineStr"/>
       <c r="K28" t="inlineStr"/>
       <c r="L28" t="inlineStr"/>
-      <c r="M28" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
@@ -3338,10 +3332,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>742368</v>
+        <v>741939</v>
       </c>
       <c r="R28" t="n">
-        <v>7112244</v>
+        <v>7111973</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3368,12 +3362,17 @@
       </c>
       <c r="Y28" t="inlineStr">
         <is>
-          <t>2025-08-27</t>
+          <t>2025-08-23</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
         <is>
-          <t>2025-08-27</t>
+          <t>2025-08-23</t>
+        </is>
+      </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3382,6 +3381,7 @@
       <c r="AE28" t="b">
         <v>0</v>
       </c>
+      <c r="AF28" t="inlineStr"/>
       <c r="AG28" t="b">
         <v>0</v>
       </c>
@@ -3403,7 +3403,7 @@
         <v>128120464</v>
       </c>
       <c r="B29" t="n">
-        <v>91431</v>
+        <v>91432</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3497,10 +3497,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>128120482</v>
+        <v>128120512</v>
       </c>
       <c r="B30" t="n">
-        <v>57686</v>
+        <v>91485</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3508,42 +3508,34 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>100049</v>
+        <v>5432</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
-      <c r="K30" t="inlineStr"/>
-      <c r="L30" t="inlineStr"/>
-      <c r="M30" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
           <t>Selsknösen, Vb</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>742472</v>
+        <v>742457</v>
       </c>
       <c r="R30" t="n">
-        <v>7112117</v>
+        <v>7112145</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3602,10 +3594,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>128120512</v>
+        <v>128120482</v>
       </c>
       <c r="B31" t="n">
-        <v>91484</v>
+        <v>57686</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3613,34 +3605,42 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>5432</v>
+        <v>100049</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
+      <c r="K31" t="inlineStr"/>
+      <c r="L31" t="inlineStr"/>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
           <t>Selsknösen, Vb</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>742457</v>
+        <v>742472</v>
       </c>
       <c r="R31" t="n">
-        <v>7112145</v>
+        <v>7112117</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3998,32 +3998,32 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>128120498</v>
+        <v>128120515</v>
       </c>
       <c r="B35" t="n">
-        <v>98591</v>
+        <v>91485</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>220787</v>
+        <v>5432</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4033,10 +4033,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>742472</v>
+        <v>741977</v>
       </c>
       <c r="R35" t="n">
-        <v>7112142</v>
+        <v>7111967</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4063,17 +4063,12 @@
       </c>
       <c r="Y35" t="inlineStr">
         <is>
-          <t>2025-08-27</t>
+          <t>2025-08-23</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
         <is>
-          <t>2025-08-27</t>
-        </is>
-      </c>
-      <c r="AC35" t="inlineStr">
-        <is>
-          <t>Rikligt</t>
+          <t>2025-08-23</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4082,7 +4077,6 @@
       <c r="AE35" t="b">
         <v>0</v>
       </c>
-      <c r="AF35" t="inlineStr"/>
       <c r="AG35" t="b">
         <v>0</v>
       </c>
@@ -4101,32 +4095,32 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>128120515</v>
+        <v>128120498</v>
       </c>
       <c r="B36" t="n">
-        <v>91484</v>
+        <v>98592</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>5432</v>
+        <v>220787</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4136,10 +4130,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>741977</v>
+        <v>742472</v>
       </c>
       <c r="R36" t="n">
-        <v>7111967</v>
+        <v>7112142</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4166,12 +4160,17 @@
       </c>
       <c r="Y36" t="inlineStr">
         <is>
-          <t>2025-08-23</t>
+          <t>2025-08-27</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
         <is>
-          <t>2025-08-23</t>
+          <t>2025-08-27</t>
+        </is>
+      </c>
+      <c r="AC36" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4180,6 +4179,7 @@
       <c r="AE36" t="b">
         <v>0</v>
       </c>
+      <c r="AF36" t="inlineStr"/>
       <c r="AG36" t="b">
         <v>0</v>
       </c>
@@ -4201,7 +4201,7 @@
         <v>128120463</v>
       </c>
       <c r="B37" t="n">
-        <v>91431</v>
+        <v>91432</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4295,10 +4295,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>128120484</v>
+        <v>128120517</v>
       </c>
       <c r="B38" t="n">
-        <v>57686</v>
+        <v>91485</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4306,42 +4306,34 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>100049</v>
+        <v>5432</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
-      <c r="K38" t="inlineStr"/>
-      <c r="L38" t="inlineStr"/>
-      <c r="M38" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
           <t>Selsknösen, Vb</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>741951</v>
+        <v>741968</v>
       </c>
       <c r="R38" t="n">
-        <v>7111949</v>
+        <v>7111957</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4400,45 +4392,49 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>128120469</v>
+        <v>128120504</v>
       </c>
       <c r="B39" t="n">
-        <v>91466</v>
+        <v>98592</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I39" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
       <c r="P39" t="inlineStr">
         <is>
           <t>Selsknösen, Vb</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>742088</v>
+        <v>741998</v>
       </c>
       <c r="R39" t="n">
-        <v>7111972</v>
+        <v>7111958</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4479,6 +4475,7 @@
       <c r="AE39" t="b">
         <v>0</v>
       </c>
+      <c r="AF39" t="inlineStr"/>
       <c r="AG39" t="b">
         <v>0</v>
       </c>
@@ -4497,32 +4494,32 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>128120517</v>
+        <v>128120509</v>
       </c>
       <c r="B40" t="n">
-        <v>91484</v>
+        <v>98592</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>5432</v>
+        <v>220787</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4532,10 +4529,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>741968</v>
+        <v>742189</v>
       </c>
       <c r="R40" t="n">
-        <v>7111957</v>
+        <v>7112063</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4594,32 +4591,32 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>128120509</v>
+        <v>128120469</v>
       </c>
       <c r="B41" t="n">
-        <v>98591</v>
+        <v>91467</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4629,10 +4626,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>742189</v>
+        <v>742088</v>
       </c>
       <c r="R41" t="n">
-        <v>7112063</v>
+        <v>7111972</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4691,49 +4688,53 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>128120504</v>
+        <v>128120484</v>
       </c>
       <c r="B42" t="n">
-        <v>98591</v>
+        <v>57686</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I42" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr"/>
+      <c r="K42" t="inlineStr"/>
+      <c r="L42" t="inlineStr"/>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
           <t>Selsknösen, Vb</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>741998</v>
+        <v>741951</v>
       </c>
       <c r="R42" t="n">
-        <v>7111958</v>
+        <v>7111949</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4774,7 +4775,6 @@
       <c r="AE42" t="b">
         <v>0</v>
       </c>
-      <c r="AF42" t="inlineStr"/>
       <c r="AG42" t="b">
         <v>0</v>
       </c>
@@ -4793,10 +4793,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>128120483</v>
+        <v>128120467</v>
       </c>
       <c r="B43" t="n">
-        <v>57686</v>
+        <v>91467</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4804,42 +4804,34 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>100049</v>
+        <v>1202</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
-      <c r="K43" t="inlineStr"/>
-      <c r="L43" t="inlineStr"/>
-      <c r="M43" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
           <t>Selsknösen, Vb</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>742340</v>
+        <v>742208</v>
       </c>
       <c r="R43" t="n">
-        <v>7112183</v>
+        <v>7112210</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4866,12 +4858,12 @@
       </c>
       <c r="Y43" t="inlineStr">
         <is>
-          <t>2025-08-27</t>
+          <t>2025-08-23</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
         <is>
-          <t>2025-08-27</t>
+          <t>2025-08-23</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -4898,10 +4890,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>128120467</v>
+        <v>128120483</v>
       </c>
       <c r="B44" t="n">
-        <v>91466</v>
+        <v>57686</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4909,34 +4901,42 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>1202</v>
+        <v>100049</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
+      <c r="K44" t="inlineStr"/>
+      <c r="L44" t="inlineStr"/>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
           <t>Selsknösen, Vb</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>742208</v>
+        <v>742340</v>
       </c>
       <c r="R44" t="n">
-        <v>7112210</v>
+        <v>7112183</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -4963,12 +4963,12 @@
       </c>
       <c r="Y44" t="inlineStr">
         <is>
-          <t>2025-08-23</t>
+          <t>2025-08-27</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
         <is>
-          <t>2025-08-23</t>
+          <t>2025-08-27</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -4998,7 +4998,7 @@
         <v>128120507</v>
       </c>
       <c r="B45" t="n">
-        <v>98591</v>
+        <v>98592</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5095,7 +5095,7 @@
         <v>128120513</v>
       </c>
       <c r="B46" t="n">
-        <v>91484</v>
+        <v>91485</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5192,7 +5192,7 @@
         <v>128120514</v>
       </c>
       <c r="B47" t="n">
-        <v>91484</v>
+        <v>91485</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5480,10 +5480,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>128120527</v>
+        <v>128120521</v>
       </c>
       <c r="B50" t="n">
-        <v>82948</v>
+        <v>79089</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5491,21 +5491,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>1312</v>
+        <v>6425</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5515,10 +5515,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>742229</v>
+        <v>741973</v>
       </c>
       <c r="R50" t="n">
-        <v>7112259</v>
+        <v>7112070</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5545,12 +5545,12 @@
       </c>
       <c r="Y50" t="inlineStr">
         <is>
-          <t>2025-08-23</t>
+          <t>2025-08-27</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
         <is>
-          <t>2025-08-23</t>
+          <t>2025-08-27</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -5577,10 +5577,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>128120488</v>
+        <v>128120527</v>
       </c>
       <c r="B51" t="n">
-        <v>57686</v>
+        <v>82948</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5588,42 +5588,34 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>100049</v>
+        <v>1312</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
-      <c r="K51" t="inlineStr"/>
-      <c r="L51" t="inlineStr"/>
-      <c r="M51" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
           <t>Selsknösen, Vb</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>742135</v>
+        <v>742229</v>
       </c>
       <c r="R51" t="n">
-        <v>7112060</v>
+        <v>7112259</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5650,12 +5642,12 @@
       </c>
       <c r="Y51" t="inlineStr">
         <is>
-          <t>2025-08-27</t>
+          <t>2025-08-23</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
         <is>
-          <t>2025-08-27</t>
+          <t>2025-08-23</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -5682,7 +5674,7 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>128120480</v>
+        <v>128120488</v>
       </c>
       <c r="B52" t="n">
         <v>57686</v>
@@ -5715,7 +5707,7 @@
       <c r="L52" t="inlineStr"/>
       <c r="M52" t="inlineStr">
         <is>
-          <t>gammalt bo</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N52" t="inlineStr"/>
@@ -5725,10 +5717,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>742020</v>
+        <v>742135</v>
       </c>
       <c r="R52" t="n">
-        <v>7111987</v>
+        <v>7112060</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5787,10 +5779,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>128120521</v>
+        <v>128120480</v>
       </c>
       <c r="B53" t="n">
-        <v>79089</v>
+        <v>57686</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5798,34 +5790,42 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
+      <c r="K53" t="inlineStr"/>
+      <c r="L53" t="inlineStr"/>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>gammalt bo</t>
+        </is>
+      </c>
+      <c r="N53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
           <t>Selsknösen, Vb</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>741973</v>
+        <v>742020</v>
       </c>
       <c r="R53" t="n">
-        <v>7112070</v>
+        <v>7111987</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -5884,10 +5884,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>128120468</v>
+        <v>128120478</v>
       </c>
       <c r="B54" t="n">
-        <v>91466</v>
+        <v>57849</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -5895,21 +5895,21 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>1202</v>
+        <v>103021</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -5919,10 +5919,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>742464</v>
+        <v>741940</v>
       </c>
       <c r="R54" t="n">
-        <v>7112167</v>
+        <v>7111944</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -5981,32 +5981,32 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>128120522</v>
+        <v>128120508</v>
       </c>
       <c r="B55" t="n">
-        <v>79089</v>
+        <v>98592</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6016,10 +6016,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>741909</v>
+        <v>742177</v>
       </c>
       <c r="R55" t="n">
-        <v>7111957</v>
+        <v>7112084</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6078,32 +6078,32 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>128120508</v>
+        <v>128120522</v>
       </c>
       <c r="B56" t="n">
-        <v>98591</v>
+        <v>79089</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6113,10 +6113,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>742177</v>
+        <v>741909</v>
       </c>
       <c r="R56" t="n">
-        <v>7112084</v>
+        <v>7111957</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6175,10 +6175,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>128120478</v>
+        <v>128120468</v>
       </c>
       <c r="B57" t="n">
-        <v>57849</v>
+        <v>91467</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6186,21 +6186,21 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>103021</v>
+        <v>1202</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6210,10 +6210,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>741940</v>
+        <v>742464</v>
       </c>
       <c r="R57" t="n">
-        <v>7111944</v>
+        <v>7112167</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6275,7 +6275,7 @@
         <v>128120506</v>
       </c>
       <c r="B58" t="n">
-        <v>98591</v>
+        <v>98592</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6671,7 +6671,7 @@
         <v>128120502</v>
       </c>
       <c r="B62" t="n">
-        <v>98591</v>
+        <v>98592</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6770,32 +6770,32 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>128120516</v>
+        <v>128120511</v>
       </c>
       <c r="B63" t="n">
-        <v>91484</v>
+        <v>98592</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>5432</v>
+        <v>220787</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -6805,10 +6805,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>742047</v>
+        <v>742032</v>
       </c>
       <c r="R63" t="n">
-        <v>7111978</v>
+        <v>7111965</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -6867,42 +6867,38 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>128120487</v>
+        <v>128120499</v>
       </c>
       <c r="B64" t="n">
-        <v>57686</v>
+        <v>98592</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
+      <c r="J64" t="inlineStr"/>
       <c r="K64" t="inlineStr"/>
       <c r="L64" t="inlineStr"/>
-      <c r="M64" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N64" t="inlineStr"/>
       <c r="P64" t="inlineStr">
         <is>
@@ -6910,10 +6906,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>741971</v>
+        <v>741963</v>
       </c>
       <c r="R64" t="n">
-        <v>7111953</v>
+        <v>7111964</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -6950,7 +6946,7 @@
       </c>
       <c r="AC64" t="inlineStr">
         <is>
-          <t>Mycket färska spår, se bild.</t>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -6959,6 +6955,7 @@
       <c r="AE64" t="b">
         <v>0</v>
       </c>
+      <c r="AF64" t="inlineStr"/>
       <c r="AG64" t="b">
         <v>0</v>
       </c>
@@ -6977,32 +6974,32 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>128120510</v>
+        <v>128120516</v>
       </c>
       <c r="B65" t="n">
-        <v>98591</v>
+        <v>91485</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>220787</v>
+        <v>5432</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -7012,10 +7009,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>742050</v>
+        <v>742047</v>
       </c>
       <c r="R65" t="n">
-        <v>7111983</v>
+        <v>7111978</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7074,45 +7071,53 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>128120511</v>
+        <v>128120487</v>
       </c>
       <c r="B66" t="n">
-        <v>98591</v>
+        <v>57686</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
+      <c r="K66" t="inlineStr"/>
+      <c r="L66" t="inlineStr"/>
+      <c r="M66" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N66" t="inlineStr"/>
       <c r="P66" t="inlineStr">
         <is>
           <t>Selsknösen, Vb</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>742032</v>
+        <v>741971</v>
       </c>
       <c r="R66" t="n">
-        <v>7111965</v>
+        <v>7111953</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7145,6 +7150,11 @@
       <c r="AA66" t="inlineStr">
         <is>
           <t>2025-08-27</t>
+        </is>
+      </c>
+      <c r="AC66" t="inlineStr">
+        <is>
+          <t>Mycket färska spår, se bild.</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7171,38 +7181,42 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>128120499</v>
+        <v>128120475</v>
       </c>
       <c r="B67" t="n">
-        <v>98591</v>
+        <v>57689</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
-      <c r="J67" t="inlineStr"/>
       <c r="K67" t="inlineStr"/>
       <c r="L67" t="inlineStr"/>
+      <c r="M67" t="inlineStr">
+        <is>
+          <t>gammalt bo</t>
+        </is>
+      </c>
       <c r="N67" t="inlineStr"/>
       <c r="P67" t="inlineStr">
         <is>
@@ -7210,10 +7224,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>741963</v>
+        <v>742203</v>
       </c>
       <c r="R67" t="n">
-        <v>7111964</v>
+        <v>7112188</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7248,18 +7262,12 @@
           <t>2025-08-27</t>
         </is>
       </c>
-      <c r="AC67" t="inlineStr">
-        <is>
-          <t>Rikligt</t>
-        </is>
-      </c>
       <c r="AD67" t="b">
         <v>0</v>
       </c>
       <c r="AE67" t="b">
         <v>0</v>
       </c>
-      <c r="AF67" t="inlineStr"/>
       <c r="AG67" t="b">
         <v>0</v>
       </c>
@@ -7278,53 +7286,45 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>128120475</v>
+        <v>128120510</v>
       </c>
       <c r="B68" t="n">
-        <v>57689</v>
+        <v>98592</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
-      <c r="K68" t="inlineStr"/>
-      <c r="L68" t="inlineStr"/>
-      <c r="M68" t="inlineStr">
-        <is>
-          <t>gammalt bo</t>
-        </is>
-      </c>
-      <c r="N68" t="inlineStr"/>
       <c r="P68" t="inlineStr">
         <is>
           <t>Selsknösen, Vb</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>742203</v>
+        <v>742050</v>
       </c>
       <c r="R68" t="n">
-        <v>7112188</v>
+        <v>7111983</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7383,10 +7383,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>128120526</v>
+        <v>128120490</v>
       </c>
       <c r="B69" t="n">
-        <v>82948</v>
+        <v>57686</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7394,34 +7394,42 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>1312</v>
+        <v>100049</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
+      <c r="K69" t="inlineStr"/>
+      <c r="L69" t="inlineStr"/>
+      <c r="M69" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N69" t="inlineStr"/>
       <c r="P69" t="inlineStr">
         <is>
           <t>Selsknösen, Vb</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>742268</v>
+        <v>741943</v>
       </c>
       <c r="R69" t="n">
-        <v>7112227</v>
+        <v>7111915</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7448,12 +7456,12 @@
       </c>
       <c r="Y69" t="inlineStr">
         <is>
-          <t>2025-08-23</t>
+          <t>2025-08-27</t>
         </is>
       </c>
       <c r="AA69" t="inlineStr">
         <is>
-          <t>2025-08-23</t>
+          <t>2025-08-27</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -7480,10 +7488,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>128120490</v>
+        <v>128120526</v>
       </c>
       <c r="B70" t="n">
-        <v>57686</v>
+        <v>82948</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7491,42 +7499,34 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>100049</v>
+        <v>1312</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
-      <c r="K70" t="inlineStr"/>
-      <c r="L70" t="inlineStr"/>
-      <c r="M70" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N70" t="inlineStr"/>
       <c r="P70" t="inlineStr">
         <is>
           <t>Selsknösen, Vb</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>741943</v>
+        <v>742268</v>
       </c>
       <c r="R70" t="n">
-        <v>7111915</v>
+        <v>7112227</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7553,12 +7553,12 @@
       </c>
       <c r="Y70" t="inlineStr">
         <is>
-          <t>2025-08-27</t>
+          <t>2025-08-23</t>
         </is>
       </c>
       <c r="AA70" t="inlineStr">
         <is>
-          <t>2025-08-27</t>
+          <t>2025-08-23</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -7790,7 +7790,7 @@
         <v>128120501</v>
       </c>
       <c r="B73" t="n">
-        <v>98591</v>
+        <v>98592</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -7999,10 +7999,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>128120470</v>
+        <v>128120520</v>
       </c>
       <c r="B75" t="n">
-        <v>91466</v>
+        <v>79089</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8010,21 +8010,21 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -8034,10 +8034,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>741946</v>
+        <v>741965</v>
       </c>
       <c r="R75" t="n">
-        <v>7111928</v>
+        <v>7112091</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8096,10 +8096,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>128120466</v>
+        <v>128120470</v>
       </c>
       <c r="B76" t="n">
-        <v>91466</v>
+        <v>91467</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8131,10 +8131,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>741977</v>
+        <v>741946</v>
       </c>
       <c r="R76" t="n">
-        <v>7111936</v>
+        <v>7111928</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8193,10 +8193,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>128120520</v>
+        <v>128120466</v>
       </c>
       <c r="B77" t="n">
-        <v>79089</v>
+        <v>91467</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8204,21 +8204,21 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
@@ -8228,10 +8228,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>741965</v>
+        <v>741977</v>
       </c>
       <c r="R77" t="n">
-        <v>7112091</v>
+        <v>7111936</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8500,7 +8500,7 @@
         <v>128120503</v>
       </c>
       <c r="B80" t="n">
-        <v>98591</v>
+        <v>98592</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -8602,7 +8602,7 @@
         <v>128314983</v>
       </c>
       <c r="B81" t="n">
-        <v>91824</v>
+        <v>91825</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -8700,7 +8700,7 @@
         <v>128314982</v>
       </c>
       <c r="B82" t="n">
-        <v>91838</v>
+        <v>91839</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>

--- a/artfynd/A 38519-2025 artfynd.xlsx
+++ b/artfynd/A 38519-2025 artfynd.xlsx
@@ -8602,7 +8602,7 @@
         <v>128314983</v>
       </c>
       <c r="B81" t="n">
-        <v>91825</v>
+        <v>91852</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -8700,7 +8700,7 @@
         <v>128314982</v>
       </c>
       <c r="B82" t="n">
-        <v>91839</v>
+        <v>91866</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>

--- a/artfynd/A 38519-2025 artfynd.xlsx
+++ b/artfynd/A 38519-2025 artfynd.xlsx
@@ -8602,7 +8602,7 @@
         <v>128314983</v>
       </c>
       <c r="B81" t="n">
-        <v>91852</v>
+        <v>91862</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -8700,7 +8700,7 @@
         <v>128314982</v>
       </c>
       <c r="B82" t="n">
-        <v>91866</v>
+        <v>91876</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>

--- a/artfynd/A 38519-2025 artfynd.xlsx
+++ b/artfynd/A 38519-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128115307</v>
       </c>
       <c r="B2" t="n">
-        <v>91484</v>
+        <v>91522</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -765,7 +765,7 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Elin Kannerby, Isac Enetjärn</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
@@ -775,7 +775,7 @@
         <v>128115310</v>
       </c>
       <c r="B3" t="n">
-        <v>79089</v>
+        <v>79120</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -862,7 +862,7 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Elin Kannerby, Isac Enetjärn</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
@@ -872,7 +872,7 @@
         <v>128115311</v>
       </c>
       <c r="B4" t="n">
-        <v>79089</v>
+        <v>79120</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -959,7 +959,7 @@
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Elin Kannerby, Isac Enetjärn</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
@@ -969,7 +969,7 @@
         <v>128115303</v>
       </c>
       <c r="B5" t="n">
-        <v>98591</v>
+        <v>98632</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1061,7 +1061,7 @@
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Elin Kannerby, Isac Enetjärn</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
@@ -1071,7 +1071,7 @@
         <v>128115305</v>
       </c>
       <c r="B6" t="n">
-        <v>98591</v>
+        <v>98632</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1163,7 +1163,7 @@
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Elin Kannerby, Isac Enetjärn</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
@@ -1173,7 +1173,7 @@
         <v>128115285</v>
       </c>
       <c r="B7" t="n">
-        <v>91431</v>
+        <v>91469</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1260,7 +1260,7 @@
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Elin Kannerby, Isac Enetjärn</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
@@ -1270,7 +1270,7 @@
         <v>128115299</v>
       </c>
       <c r="B8" t="n">
-        <v>80230</v>
+        <v>80261</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1357,7 +1357,7 @@
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Elin Kannerby, Isac Enetjärn</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
@@ -1367,7 +1367,7 @@
         <v>128115290</v>
       </c>
       <c r="B9" t="n">
-        <v>56880</v>
+        <v>56907</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1463,7 +1463,7 @@
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Elin Kannerby, Isac Enetjärn</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
@@ -1473,7 +1473,7 @@
         <v>128115289</v>
       </c>
       <c r="B10" t="n">
-        <v>91466</v>
+        <v>91504</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1561,7 +1561,7 @@
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Elin Kannerby, Isac Enetjärn</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
@@ -1571,7 +1571,7 @@
         <v>128115295</v>
       </c>
       <c r="B11" t="n">
-        <v>57689</v>
+        <v>57716</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1671,7 +1671,7 @@
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Elin Kannerby, Isac Enetjärn</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
@@ -1681,7 +1681,7 @@
         <v>128115294</v>
       </c>
       <c r="B12" t="n">
-        <v>80098</v>
+        <v>80129</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1768,7 +1768,7 @@
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Elin Kannerby, Isac Enetjärn</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
@@ -1778,7 +1778,7 @@
         <v>128115293</v>
       </c>
       <c r="B13" t="n">
-        <v>57686</v>
+        <v>57713</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1869,7 +1869,7 @@
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Elin Kannerby, Isac Enetjärn</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
@@ -1879,7 +1879,7 @@
         <v>128115302</v>
       </c>
       <c r="B14" t="n">
-        <v>98591</v>
+        <v>98632</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1971,7 +1971,7 @@
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Elin Kannerby, Isac Enetjärn</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
@@ -1981,7 +1981,7 @@
         <v>128115304</v>
       </c>
       <c r="B15" t="n">
-        <v>98591</v>
+        <v>98632</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2073,7 +2073,7 @@
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Elin Kannerby, Isac Enetjärn</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
@@ -2083,7 +2083,7 @@
         <v>128115367</v>
       </c>
       <c r="B16" t="n">
-        <v>57689</v>
+        <v>57716</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2183,7 +2183,7 @@
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Elin Kannerby, Isac Enetjärn</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
@@ -2193,7 +2193,7 @@
         <v>128115314</v>
       </c>
       <c r="B17" t="n">
-        <v>98508</v>
+        <v>98549</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2280,7 +2280,7 @@
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Elin Kannerby, Isac Enetjärn</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
@@ -2290,7 +2290,7 @@
         <v>128115287</v>
       </c>
       <c r="B18" t="n">
-        <v>91431</v>
+        <v>91469</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2377,7 +2377,7 @@
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Elin Kannerby, Isac Enetjärn</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
@@ -2387,7 +2387,7 @@
         <v>128115298</v>
       </c>
       <c r="B19" t="n">
-        <v>95817</v>
+        <v>95858</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2474,7 +2474,7 @@
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Elin Kannerby, Isac Enetjärn</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
@@ -2484,7 +2484,7 @@
         <v>128115288</v>
       </c>
       <c r="B20" t="n">
-        <v>96932</v>
+        <v>96973</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2572,7 +2572,7 @@
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Elin Kannerby, Isac Enetjärn</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
@@ -2582,7 +2582,7 @@
         <v>128115286</v>
       </c>
       <c r="B21" t="n">
-        <v>91431</v>
+        <v>91469</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2669,7 +2669,7 @@
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Elin Kannerby, Isac Enetjärn</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
@@ -2679,7 +2679,7 @@
         <v>128115309</v>
       </c>
       <c r="B22" t="n">
-        <v>79089</v>
+        <v>79120</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2766,7 +2766,7 @@
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Elin Kannerby, Isac Enetjärn</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
@@ -2776,7 +2776,7 @@
         <v>128115313</v>
       </c>
       <c r="B23" t="n">
-        <v>82948</v>
+        <v>82979</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2863,7 +2863,7 @@
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Elin Kannerby, Isac Enetjärn</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
@@ -8690,7 +8690,7 @@
       </c>
       <c r="AX81" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Elin Kannerby, Isac Enetjärn</t>
         </is>
       </c>
       <c r="AY81" t="inlineStr"/>
@@ -8787,7 +8787,7 @@
       </c>
       <c r="AX82" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Elin Kannerby, Isac Enetjärn</t>
         </is>
       </c>
       <c r="AY82" t="inlineStr"/>

--- a/artfynd/A 38519-2025 artfynd.xlsx
+++ b/artfynd/A 38519-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128115307</v>
       </c>
       <c r="B2" t="n">
-        <v>91522</v>
+        <v>91526</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>128115310</v>
       </c>
       <c r="B3" t="n">
-        <v>79120</v>
+        <v>79124</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
         <v>128115311</v>
       </c>
       <c r="B4" t="n">
-        <v>79120</v>
+        <v>79124</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -969,7 +969,7 @@
         <v>128115303</v>
       </c>
       <c r="B5" t="n">
-        <v>98632</v>
+        <v>98636</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1071,7 +1071,7 @@
         <v>128115305</v>
       </c>
       <c r="B6" t="n">
-        <v>98632</v>
+        <v>98636</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1173,7 +1173,7 @@
         <v>128115285</v>
       </c>
       <c r="B7" t="n">
-        <v>91469</v>
+        <v>91473</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1270,7 +1270,7 @@
         <v>128115299</v>
       </c>
       <c r="B8" t="n">
-        <v>80261</v>
+        <v>80265</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1367,7 +1367,7 @@
         <v>128115290</v>
       </c>
       <c r="B9" t="n">
-        <v>56907</v>
+        <v>56910</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1473,7 +1473,7 @@
         <v>128115289</v>
       </c>
       <c r="B10" t="n">
-        <v>91504</v>
+        <v>91508</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1571,7 +1571,7 @@
         <v>128115295</v>
       </c>
       <c r="B11" t="n">
-        <v>57716</v>
+        <v>57720</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1681,7 +1681,7 @@
         <v>128115294</v>
       </c>
       <c r="B12" t="n">
-        <v>80129</v>
+        <v>80133</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1778,7 +1778,7 @@
         <v>128115293</v>
       </c>
       <c r="B13" t="n">
-        <v>57713</v>
+        <v>57717</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1879,7 +1879,7 @@
         <v>128115302</v>
       </c>
       <c r="B14" t="n">
-        <v>98632</v>
+        <v>98636</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1981,7 +1981,7 @@
         <v>128115304</v>
       </c>
       <c r="B15" t="n">
-        <v>98632</v>
+        <v>98636</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2083,7 +2083,7 @@
         <v>128115367</v>
       </c>
       <c r="B16" t="n">
-        <v>57716</v>
+        <v>57720</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2193,7 +2193,7 @@
         <v>128115314</v>
       </c>
       <c r="B17" t="n">
-        <v>98549</v>
+        <v>98553</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2290,7 +2290,7 @@
         <v>128115287</v>
       </c>
       <c r="B18" t="n">
-        <v>91469</v>
+        <v>91473</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2387,7 +2387,7 @@
         <v>128115298</v>
       </c>
       <c r="B19" t="n">
-        <v>95858</v>
+        <v>95862</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2484,7 +2484,7 @@
         <v>128115288</v>
       </c>
       <c r="B20" t="n">
-        <v>96973</v>
+        <v>96977</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2582,7 +2582,7 @@
         <v>128115286</v>
       </c>
       <c r="B21" t="n">
-        <v>91469</v>
+        <v>91473</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2679,7 +2679,7 @@
         <v>128115309</v>
       </c>
       <c r="B22" t="n">
-        <v>79120</v>
+        <v>79124</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2776,7 +2776,7 @@
         <v>128115313</v>
       </c>
       <c r="B23" t="n">
-        <v>82979</v>
+        <v>82983</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -8602,7 +8602,7 @@
         <v>128314983</v>
       </c>
       <c r="B81" t="n">
-        <v>91862</v>
+        <v>91866</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -8700,7 +8700,7 @@
         <v>128314982</v>
       </c>
       <c r="B82" t="n">
-        <v>91876</v>
+        <v>91880</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>

--- a/artfynd/A 38519-2025 artfynd.xlsx
+++ b/artfynd/A 38519-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128115307</v>
       </c>
       <c r="B2" t="n">
-        <v>91526</v>
+        <v>91531</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>128115310</v>
       </c>
       <c r="B3" t="n">
-        <v>79124</v>
+        <v>79029</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
         <v>128115311</v>
       </c>
       <c r="B4" t="n">
-        <v>79124</v>
+        <v>79029</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -969,7 +969,7 @@
         <v>128115303</v>
       </c>
       <c r="B5" t="n">
-        <v>98636</v>
+        <v>98643</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1071,7 +1071,7 @@
         <v>128115305</v>
       </c>
       <c r="B6" t="n">
-        <v>98636</v>
+        <v>98643</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1173,7 +1173,7 @@
         <v>128115285</v>
       </c>
       <c r="B7" t="n">
-        <v>91473</v>
+        <v>91478</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1270,7 +1270,7 @@
         <v>128115299</v>
       </c>
       <c r="B8" t="n">
-        <v>80265</v>
+        <v>80170</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1367,7 +1367,7 @@
         <v>128115290</v>
       </c>
       <c r="B9" t="n">
-        <v>56910</v>
+        <v>56913</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1473,7 +1473,7 @@
         <v>128115289</v>
       </c>
       <c r="B10" t="n">
-        <v>91508</v>
+        <v>91513</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1571,7 +1571,7 @@
         <v>128115295</v>
       </c>
       <c r="B11" t="n">
-        <v>57720</v>
+        <v>57723</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1681,7 +1681,7 @@
         <v>128115294</v>
       </c>
       <c r="B12" t="n">
-        <v>80133</v>
+        <v>80038</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1778,7 +1778,7 @@
         <v>128115293</v>
       </c>
       <c r="B13" t="n">
-        <v>57717</v>
+        <v>57720</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1879,7 +1879,7 @@
         <v>128115302</v>
       </c>
       <c r="B14" t="n">
-        <v>98636</v>
+        <v>98643</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1981,7 +1981,7 @@
         <v>128115304</v>
       </c>
       <c r="B15" t="n">
-        <v>98636</v>
+        <v>98643</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2083,7 +2083,7 @@
         <v>128115367</v>
       </c>
       <c r="B16" t="n">
-        <v>57720</v>
+        <v>57723</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2193,7 +2193,7 @@
         <v>128115314</v>
       </c>
       <c r="B17" t="n">
-        <v>98553</v>
+        <v>98560</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2290,7 +2290,7 @@
         <v>128115287</v>
       </c>
       <c r="B18" t="n">
-        <v>91473</v>
+        <v>91478</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2387,7 +2387,7 @@
         <v>128115298</v>
       </c>
       <c r="B19" t="n">
-        <v>95862</v>
+        <v>95869</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2484,7 +2484,7 @@
         <v>128115288</v>
       </c>
       <c r="B20" t="n">
-        <v>96977</v>
+        <v>96984</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2582,7 +2582,7 @@
         <v>128115286</v>
       </c>
       <c r="B21" t="n">
-        <v>91473</v>
+        <v>91478</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2679,7 +2679,7 @@
         <v>128115309</v>
       </c>
       <c r="B22" t="n">
-        <v>79124</v>
+        <v>79029</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2776,7 +2776,7 @@
         <v>128115313</v>
       </c>
       <c r="B23" t="n">
-        <v>82983</v>
+        <v>82892</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -8602,7 +8602,7 @@
         <v>128314983</v>
       </c>
       <c r="B81" t="n">
-        <v>91866</v>
+        <v>91871</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -8700,7 +8700,7 @@
         <v>128314982</v>
       </c>
       <c r="B82" t="n">
-        <v>91880</v>
+        <v>91885</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>

--- a/artfynd/A 38519-2025 artfynd.xlsx
+++ b/artfynd/A 38519-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128115307</v>
       </c>
       <c r="B2" t="n">
-        <v>91538</v>
+        <v>91541</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -969,7 +969,7 @@
         <v>128115303</v>
       </c>
       <c r="B5" t="n">
-        <v>98651</v>
+        <v>98656</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1071,7 +1071,7 @@
         <v>128115305</v>
       </c>
       <c r="B6" t="n">
-        <v>98651</v>
+        <v>98656</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1173,7 +1173,7 @@
         <v>128115285</v>
       </c>
       <c r="B7" t="n">
-        <v>91485</v>
+        <v>91488</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1473,7 +1473,7 @@
         <v>128115289</v>
       </c>
       <c r="B10" t="n">
-        <v>91520</v>
+        <v>91523</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1879,7 +1879,7 @@
         <v>128115302</v>
       </c>
       <c r="B14" t="n">
-        <v>98651</v>
+        <v>98656</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1981,7 +1981,7 @@
         <v>128115304</v>
       </c>
       <c r="B15" t="n">
-        <v>98651</v>
+        <v>98656</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2193,7 +2193,7 @@
         <v>128115314</v>
       </c>
       <c r="B17" t="n">
-        <v>98568</v>
+        <v>98573</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2290,7 +2290,7 @@
         <v>128115287</v>
       </c>
       <c r="B18" t="n">
-        <v>91485</v>
+        <v>91488</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2387,7 +2387,7 @@
         <v>128115298</v>
       </c>
       <c r="B19" t="n">
-        <v>95877</v>
+        <v>95882</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2484,7 +2484,7 @@
         <v>128115288</v>
       </c>
       <c r="B20" t="n">
-        <v>96992</v>
+        <v>96997</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2582,7 +2582,7 @@
         <v>128115286</v>
       </c>
       <c r="B21" t="n">
-        <v>91485</v>
+        <v>91488</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -8602,7 +8602,7 @@
         <v>128314983</v>
       </c>
       <c r="B81" t="n">
-        <v>91879</v>
+        <v>91882</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -8700,7 +8700,7 @@
         <v>128314982</v>
       </c>
       <c r="B82" t="n">
-        <v>91893</v>
+        <v>91896</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>

--- a/artfynd/A 38519-2025 artfynd.xlsx
+++ b/artfynd/A 38519-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128115307</v>
       </c>
       <c r="B2" t="n">
-        <v>91541</v>
+        <v>91544</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>128115310</v>
       </c>
       <c r="B3" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
         <v>128115311</v>
       </c>
       <c r="B4" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -969,7 +969,7 @@
         <v>128115303</v>
       </c>
       <c r="B5" t="n">
-        <v>98656</v>
+        <v>98659</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1071,7 +1071,7 @@
         <v>128115305</v>
       </c>
       <c r="B6" t="n">
-        <v>98656</v>
+        <v>98659</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1173,7 +1173,7 @@
         <v>128115285</v>
       </c>
       <c r="B7" t="n">
-        <v>91488</v>
+        <v>91491</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1270,7 +1270,7 @@
         <v>128115299</v>
       </c>
       <c r="B8" t="n">
-        <v>80175</v>
+        <v>80176</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1473,7 +1473,7 @@
         <v>128115289</v>
       </c>
       <c r="B10" t="n">
-        <v>91523</v>
+        <v>91526</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1681,7 +1681,7 @@
         <v>128115294</v>
       </c>
       <c r="B12" t="n">
-        <v>80043</v>
+        <v>80044</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1879,7 +1879,7 @@
         <v>128115302</v>
       </c>
       <c r="B14" t="n">
-        <v>98656</v>
+        <v>98659</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1981,7 +1981,7 @@
         <v>128115304</v>
       </c>
       <c r="B15" t="n">
-        <v>98656</v>
+        <v>98659</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2193,7 +2193,7 @@
         <v>128115314</v>
       </c>
       <c r="B17" t="n">
-        <v>98573</v>
+        <v>98576</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2290,7 +2290,7 @@
         <v>128115287</v>
       </c>
       <c r="B18" t="n">
-        <v>91488</v>
+        <v>91491</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2387,7 +2387,7 @@
         <v>128115298</v>
       </c>
       <c r="B19" t="n">
-        <v>95882</v>
+        <v>95885</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2484,7 +2484,7 @@
         <v>128115288</v>
       </c>
       <c r="B20" t="n">
-        <v>96997</v>
+        <v>97000</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2582,7 +2582,7 @@
         <v>128115286</v>
       </c>
       <c r="B21" t="n">
-        <v>91488</v>
+        <v>91491</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2679,7 +2679,7 @@
         <v>128115309</v>
       </c>
       <c r="B22" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2776,7 +2776,7 @@
         <v>128115313</v>
       </c>
       <c r="B23" t="n">
-        <v>82897</v>
+        <v>82898</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -8602,7 +8602,7 @@
         <v>128314983</v>
       </c>
       <c r="B81" t="n">
-        <v>91882</v>
+        <v>91885</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -8700,7 +8700,7 @@
         <v>128314982</v>
       </c>
       <c r="B82" t="n">
-        <v>91896</v>
+        <v>91899</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>

--- a/artfynd/A 38519-2025 artfynd.xlsx
+++ b/artfynd/A 38519-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128115307</v>
       </c>
       <c r="B2" t="n">
-        <v>91544</v>
+        <v>91551</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>128115310</v>
       </c>
       <c r="B3" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
         <v>128115311</v>
       </c>
       <c r="B4" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -969,7 +969,7 @@
         <v>128115303</v>
       </c>
       <c r="B5" t="n">
-        <v>98659</v>
+        <v>98669</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1071,7 +1071,7 @@
         <v>128115305</v>
       </c>
       <c r="B6" t="n">
-        <v>98659</v>
+        <v>98669</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1173,7 +1173,7 @@
         <v>128115285</v>
       </c>
       <c r="B7" t="n">
-        <v>91491</v>
+        <v>91497</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1270,7 +1270,7 @@
         <v>128115299</v>
       </c>
       <c r="B8" t="n">
-        <v>80176</v>
+        <v>80180</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1367,7 +1367,7 @@
         <v>128115290</v>
       </c>
       <c r="B9" t="n">
-        <v>56913</v>
+        <v>56915</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1473,7 +1473,7 @@
         <v>128115289</v>
       </c>
       <c r="B10" t="n">
-        <v>91526</v>
+        <v>91533</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1571,7 +1571,7 @@
         <v>128115295</v>
       </c>
       <c r="B11" t="n">
-        <v>57723</v>
+        <v>57725</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1681,7 +1681,7 @@
         <v>128115294</v>
       </c>
       <c r="B12" t="n">
-        <v>80044</v>
+        <v>80048</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1778,7 +1778,7 @@
         <v>128115293</v>
       </c>
       <c r="B13" t="n">
-        <v>57720</v>
+        <v>57722</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1879,7 +1879,7 @@
         <v>128115302</v>
       </c>
       <c r="B14" t="n">
-        <v>98659</v>
+        <v>98669</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1981,7 +1981,7 @@
         <v>128115304</v>
       </c>
       <c r="B15" t="n">
-        <v>98659</v>
+        <v>98669</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2083,7 +2083,7 @@
         <v>128115367</v>
       </c>
       <c r="B16" t="n">
-        <v>57723</v>
+        <v>57725</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2193,7 +2193,7 @@
         <v>128115314</v>
       </c>
       <c r="B17" t="n">
-        <v>98576</v>
+        <v>98586</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2290,7 +2290,7 @@
         <v>128115287</v>
       </c>
       <c r="B18" t="n">
-        <v>91491</v>
+        <v>91497</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2387,7 +2387,7 @@
         <v>128115298</v>
       </c>
       <c r="B19" t="n">
-        <v>95885</v>
+        <v>95895</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2484,7 +2484,7 @@
         <v>128115288</v>
       </c>
       <c r="B20" t="n">
-        <v>97000</v>
+        <v>97010</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2582,7 +2582,7 @@
         <v>128115286</v>
       </c>
       <c r="B21" t="n">
-        <v>91491</v>
+        <v>91497</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2679,7 +2679,7 @@
         <v>128115309</v>
       </c>
       <c r="B22" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2776,7 +2776,7 @@
         <v>128115313</v>
       </c>
       <c r="B23" t="n">
-        <v>82898</v>
+        <v>82902</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -8602,7 +8602,7 @@
         <v>128314983</v>
       </c>
       <c r="B81" t="n">
-        <v>91885</v>
+        <v>91892</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -8700,7 +8700,7 @@
         <v>128314982</v>
       </c>
       <c r="B82" t="n">
-        <v>91899</v>
+        <v>91906</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>

--- a/artfynd/A 38519-2025 artfynd.xlsx
+++ b/artfynd/A 38519-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128115307</v>
       </c>
       <c r="B2" t="n">
-        <v>91551</v>
+        <v>91558</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -969,7 +969,7 @@
         <v>128115303</v>
       </c>
       <c r="B5" t="n">
-        <v>98669</v>
+        <v>98676</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1071,7 +1071,7 @@
         <v>128115305</v>
       </c>
       <c r="B6" t="n">
-        <v>98669</v>
+        <v>98676</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1173,7 +1173,7 @@
         <v>128115285</v>
       </c>
       <c r="B7" t="n">
-        <v>91497</v>
+        <v>91504</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1473,7 +1473,7 @@
         <v>128115289</v>
       </c>
       <c r="B10" t="n">
-        <v>91533</v>
+        <v>91540</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1879,7 +1879,7 @@
         <v>128115302</v>
       </c>
       <c r="B14" t="n">
-        <v>98669</v>
+        <v>98676</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1981,7 +1981,7 @@
         <v>128115304</v>
       </c>
       <c r="B15" t="n">
-        <v>98669</v>
+        <v>98676</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2193,7 +2193,7 @@
         <v>128115314</v>
       </c>
       <c r="B17" t="n">
-        <v>98586</v>
+        <v>98593</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2290,7 +2290,7 @@
         <v>128115287</v>
       </c>
       <c r="B18" t="n">
-        <v>91497</v>
+        <v>91504</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2387,7 +2387,7 @@
         <v>128115298</v>
       </c>
       <c r="B19" t="n">
-        <v>95895</v>
+        <v>95902</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2484,7 +2484,7 @@
         <v>128115288</v>
       </c>
       <c r="B20" t="n">
-        <v>97010</v>
+        <v>97017</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2582,7 +2582,7 @@
         <v>128115286</v>
       </c>
       <c r="B21" t="n">
-        <v>91497</v>
+        <v>91504</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2776,7 +2776,7 @@
         <v>128115313</v>
       </c>
       <c r="B23" t="n">
-        <v>82902</v>
+        <v>82871</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -8602,7 +8602,7 @@
         <v>128314983</v>
       </c>
       <c r="B81" t="n">
-        <v>91892</v>
+        <v>91899</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -8700,7 +8700,7 @@
         <v>128314982</v>
       </c>
       <c r="B82" t="n">
-        <v>91906</v>
+        <v>91913</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>

--- a/artfynd/A 38519-2025 artfynd.xlsx
+++ b/artfynd/A 38519-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128115307</v>
       </c>
       <c r="B2" t="n">
-        <v>91558</v>
+        <v>91560</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>128115310</v>
       </c>
       <c r="B3" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
         <v>128115311</v>
       </c>
       <c r="B4" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -969,7 +969,7 @@
         <v>128115303</v>
       </c>
       <c r="B5" t="n">
-        <v>98676</v>
+        <v>98678</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1071,7 +1071,7 @@
         <v>128115305</v>
       </c>
       <c r="B6" t="n">
-        <v>98676</v>
+        <v>98678</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1173,7 +1173,7 @@
         <v>128115285</v>
       </c>
       <c r="B7" t="n">
-        <v>91504</v>
+        <v>91506</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1270,7 +1270,7 @@
         <v>128115299</v>
       </c>
       <c r="B8" t="n">
-        <v>80180</v>
+        <v>80182</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1367,7 +1367,7 @@
         <v>128115290</v>
       </c>
       <c r="B9" t="n">
-        <v>56915</v>
+        <v>56917</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1473,7 +1473,7 @@
         <v>128115289</v>
       </c>
       <c r="B10" t="n">
-        <v>91540</v>
+        <v>91542</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1571,7 +1571,7 @@
         <v>128115295</v>
       </c>
       <c r="B11" t="n">
-        <v>57725</v>
+        <v>57727</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1681,7 +1681,7 @@
         <v>128115294</v>
       </c>
       <c r="B12" t="n">
-        <v>80048</v>
+        <v>80050</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1778,7 +1778,7 @@
         <v>128115293</v>
       </c>
       <c r="B13" t="n">
-        <v>57722</v>
+        <v>57724</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1879,7 +1879,7 @@
         <v>128115302</v>
       </c>
       <c r="B14" t="n">
-        <v>98676</v>
+        <v>98678</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1981,7 +1981,7 @@
         <v>128115304</v>
       </c>
       <c r="B15" t="n">
-        <v>98676</v>
+        <v>98678</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2083,7 +2083,7 @@
         <v>128115367</v>
       </c>
       <c r="B16" t="n">
-        <v>57725</v>
+        <v>57727</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2193,7 +2193,7 @@
         <v>128115314</v>
       </c>
       <c r="B17" t="n">
-        <v>98593</v>
+        <v>98595</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2290,7 +2290,7 @@
         <v>128115287</v>
       </c>
       <c r="B18" t="n">
-        <v>91504</v>
+        <v>91506</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2387,7 +2387,7 @@
         <v>128115298</v>
       </c>
       <c r="B19" t="n">
-        <v>95902</v>
+        <v>95904</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2484,7 +2484,7 @@
         <v>128115288</v>
       </c>
       <c r="B20" t="n">
-        <v>97017</v>
+        <v>97019</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2582,7 +2582,7 @@
         <v>128115286</v>
       </c>
       <c r="B21" t="n">
-        <v>91504</v>
+        <v>91506</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2679,7 +2679,7 @@
         <v>128115309</v>
       </c>
       <c r="B22" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2776,7 +2776,7 @@
         <v>128115313</v>
       </c>
       <c r="B23" t="n">
-        <v>82871</v>
+        <v>82873</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -8602,7 +8602,7 @@
         <v>128314983</v>
       </c>
       <c r="B81" t="n">
-        <v>91899</v>
+        <v>91901</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -8700,7 +8700,7 @@
         <v>128314982</v>
       </c>
       <c r="B82" t="n">
-        <v>91913</v>
+        <v>91915</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>

--- a/artfynd/A 38519-2025 artfynd.xlsx
+++ b/artfynd/A 38519-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128115307</v>
       </c>
       <c r="B2" t="n">
-        <v>91560</v>
+        <v>91558</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -969,7 +969,7 @@
         <v>128115303</v>
       </c>
       <c r="B5" t="n">
-        <v>98678</v>
+        <v>98704</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1071,7 +1071,7 @@
         <v>128115305</v>
       </c>
       <c r="B6" t="n">
-        <v>98678</v>
+        <v>98704</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1173,7 +1173,7 @@
         <v>128115285</v>
       </c>
       <c r="B7" t="n">
-        <v>91506</v>
+        <v>91504</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1473,7 +1473,7 @@
         <v>128115289</v>
       </c>
       <c r="B10" t="n">
-        <v>91542</v>
+        <v>91540</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1879,7 +1879,7 @@
         <v>128115302</v>
       </c>
       <c r="B14" t="n">
-        <v>98678</v>
+        <v>98704</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1981,7 +1981,7 @@
         <v>128115304</v>
       </c>
       <c r="B15" t="n">
-        <v>98678</v>
+        <v>98704</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2193,7 +2193,7 @@
         <v>128115314</v>
       </c>
       <c r="B17" t="n">
-        <v>98595</v>
+        <v>98621</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2290,7 +2290,7 @@
         <v>128115287</v>
       </c>
       <c r="B18" t="n">
-        <v>91506</v>
+        <v>91504</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2387,7 +2387,7 @@
         <v>128115298</v>
       </c>
       <c r="B19" t="n">
-        <v>95904</v>
+        <v>95930</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2484,7 +2484,7 @@
         <v>128115288</v>
       </c>
       <c r="B20" t="n">
-        <v>97019</v>
+        <v>97045</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2582,7 +2582,7 @@
         <v>128115286</v>
       </c>
       <c r="B21" t="n">
-        <v>91506</v>
+        <v>91504</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -8602,7 +8602,7 @@
         <v>128314983</v>
       </c>
       <c r="B81" t="n">
-        <v>91901</v>
+        <v>91910</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -8700,7 +8700,7 @@
         <v>128314982</v>
       </c>
       <c r="B82" t="n">
-        <v>91915</v>
+        <v>91924</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>

--- a/artfynd/A 38519-2025 artfynd.xlsx
+++ b/artfynd/A 38519-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128115307</v>
       </c>
       <c r="B2" t="n">
-        <v>91558</v>
+        <v>91560</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -695,14 +695,10 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr"/>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -969,7 +965,7 @@
         <v>128115303</v>
       </c>
       <c r="B5" t="n">
-        <v>98704</v>
+        <v>98705</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1071,7 +1067,7 @@
         <v>128115305</v>
       </c>
       <c r="B6" t="n">
-        <v>98704</v>
+        <v>98705</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1879,7 +1875,7 @@
         <v>128115302</v>
       </c>
       <c r="B14" t="n">
-        <v>98704</v>
+        <v>98705</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1981,7 +1977,7 @@
         <v>128115304</v>
       </c>
       <c r="B15" t="n">
-        <v>98704</v>
+        <v>98705</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2193,7 +2189,7 @@
         <v>128115314</v>
       </c>
       <c r="B17" t="n">
-        <v>98621</v>
+        <v>98622</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2387,7 +2383,7 @@
         <v>128115298</v>
       </c>
       <c r="B19" t="n">
-        <v>95930</v>
+        <v>95931</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2484,7 +2480,7 @@
         <v>128115288</v>
       </c>
       <c r="B20" t="n">
-        <v>97045</v>
+        <v>97046</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -8602,7 +8598,7 @@
         <v>128314983</v>
       </c>
       <c r="B81" t="n">
-        <v>91910</v>
+        <v>91911</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -8700,7 +8696,7 @@
         <v>128314982</v>
       </c>
       <c r="B82" t="n">
-        <v>91924</v>
+        <v>91925</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>

--- a/artfynd/A 38519-2025 artfynd.xlsx
+++ b/artfynd/A 38519-2025 artfynd.xlsx
@@ -965,7 +965,7 @@
         <v>128115303</v>
       </c>
       <c r="B5" t="n">
-        <v>98705</v>
+        <v>98706</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1067,7 +1067,7 @@
         <v>128115305</v>
       </c>
       <c r="B6" t="n">
-        <v>98705</v>
+        <v>98706</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1875,7 +1875,7 @@
         <v>128115302</v>
       </c>
       <c r="B14" t="n">
-        <v>98705</v>
+        <v>98706</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1977,7 +1977,7 @@
         <v>128115304</v>
       </c>
       <c r="B15" t="n">
-        <v>98705</v>
+        <v>98706</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2189,7 +2189,7 @@
         <v>128115314</v>
       </c>
       <c r="B17" t="n">
-        <v>98622</v>
+        <v>98623</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2383,7 +2383,7 @@
         <v>128115298</v>
       </c>
       <c r="B19" t="n">
-        <v>95931</v>
+        <v>95932</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2480,7 +2480,7 @@
         <v>128115288</v>
       </c>
       <c r="B20" t="n">
-        <v>97046</v>
+        <v>97047</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>

--- a/artfynd/A 38519-2025 artfynd.xlsx
+++ b/artfynd/A 38519-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128115307</v>
       </c>
       <c r="B2" t="n">
-        <v>91560</v>
+        <v>91563</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -771,7 +771,7 @@
         <v>128115310</v>
       </c>
       <c r="B3" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -868,7 +868,7 @@
         <v>128115311</v>
       </c>
       <c r="B4" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -965,7 +965,7 @@
         <v>128115303</v>
       </c>
       <c r="B5" t="n">
-        <v>98706</v>
+        <v>98710</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1067,7 +1067,7 @@
         <v>128115305</v>
       </c>
       <c r="B6" t="n">
-        <v>98706</v>
+        <v>98710</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1169,7 +1169,7 @@
         <v>128115285</v>
       </c>
       <c r="B7" t="n">
-        <v>91504</v>
+        <v>91507</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1266,7 +1266,7 @@
         <v>128115299</v>
       </c>
       <c r="B8" t="n">
-        <v>80182</v>
+        <v>80184</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1469,7 +1469,7 @@
         <v>128115289</v>
       </c>
       <c r="B10" t="n">
-        <v>91540</v>
+        <v>91543</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1677,7 +1677,7 @@
         <v>128115294</v>
       </c>
       <c r="B12" t="n">
-        <v>80050</v>
+        <v>80052</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1875,7 +1875,7 @@
         <v>128115302</v>
       </c>
       <c r="B14" t="n">
-        <v>98706</v>
+        <v>98710</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1977,7 +1977,7 @@
         <v>128115304</v>
       </c>
       <c r="B15" t="n">
-        <v>98706</v>
+        <v>98710</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2189,7 +2189,7 @@
         <v>128115314</v>
       </c>
       <c r="B17" t="n">
-        <v>98623</v>
+        <v>98627</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2286,7 +2286,7 @@
         <v>128115287</v>
       </c>
       <c r="B18" t="n">
-        <v>91504</v>
+        <v>91507</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2383,7 +2383,7 @@
         <v>128115298</v>
       </c>
       <c r="B19" t="n">
-        <v>95932</v>
+        <v>95936</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2480,7 +2480,7 @@
         <v>128115288</v>
       </c>
       <c r="B20" t="n">
-        <v>97047</v>
+        <v>97051</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2578,7 +2578,7 @@
         <v>128115286</v>
       </c>
       <c r="B21" t="n">
-        <v>91504</v>
+        <v>91507</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2675,7 +2675,7 @@
         <v>128115309</v>
       </c>
       <c r="B22" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2772,7 +2772,7 @@
         <v>128115313</v>
       </c>
       <c r="B23" t="n">
-        <v>82873</v>
+        <v>82877</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -8598,7 +8598,7 @@
         <v>128314983</v>
       </c>
       <c r="B81" t="n">
-        <v>91911</v>
+        <v>91914</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -8696,7 +8696,7 @@
         <v>128314982</v>
       </c>
       <c r="B82" t="n">
-        <v>91925</v>
+        <v>91928</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>

--- a/artfynd/A 38519-2025 artfynd.xlsx
+++ b/artfynd/A 38519-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY82"/>
+  <dimension ref="A1:AY79"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>128115307</v>
+        <v>128115289</v>
       </c>
       <c r="B2" t="n">
-        <v>91570</v>
+        <v>91909</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,19 +686,23 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5432</v>
+        <v>1202</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr"/>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -706,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>742140</v>
+        <v>742020</v>
       </c>
       <c r="R2" t="n">
-        <v>7112068</v>
+        <v>7111950</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -750,6 +754,7 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -768,10 +773,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>128115310</v>
+        <v>128120465</v>
       </c>
       <c r="B3" t="n">
-        <v>79044</v>
+        <v>91909</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -779,21 +784,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -803,10 +808,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>742019</v>
+        <v>741940</v>
       </c>
       <c r="R3" t="n">
-        <v>7112138</v>
+        <v>7112070</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -853,22 +858,22 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Maria Wikdahl</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Elin Kannerby, Isac Enetjärn</t>
+          <t>Maria Wikdahl</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>128115311</v>
+        <v>128120466</v>
       </c>
       <c r="B4" t="n">
-        <v>79044</v>
+        <v>91909</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -876,21 +881,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -900,10 +905,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>742052</v>
+        <v>741977</v>
       </c>
       <c r="R4" t="n">
-        <v>7112024</v>
+        <v>7111936</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -950,61 +955,57 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Maria Wikdahl</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Elin Kannerby, Isac Enetjärn</t>
+          <t>Maria Wikdahl</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128115303</v>
+        <v>128120467</v>
       </c>
       <c r="B5" t="n">
-        <v>98724</v>
+        <v>91909</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
-      <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
-      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Selsknösen, Vb</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>742050</v>
+        <v>742208</v>
       </c>
       <c r="R5" t="n">
-        <v>7111963</v>
+        <v>7112210</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1031,12 +1032,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-08-27</t>
+          <t>2025-08-23</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2025-08-27</t>
+          <t>2025-08-23</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1045,68 +1046,63 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
-      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Maria Wikdahl</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Elin Kannerby, Isac Enetjärn</t>
+          <t>Maria Wikdahl</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128115305</v>
+        <v>128120468</v>
       </c>
       <c r="B6" t="n">
-        <v>98724</v>
+        <v>91909</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
-      <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
-      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Selsknösen, Vb</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>741970</v>
+        <v>742464</v>
       </c>
       <c r="R6" t="n">
-        <v>7111969</v>
+        <v>7112167</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1147,51 +1143,50 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
-      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Maria Wikdahl</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Elin Kannerby, Isac Enetjärn</t>
+          <t>Maria Wikdahl</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>128115285</v>
+        <v>128120469</v>
       </c>
       <c r="B7" t="n">
-        <v>91514</v>
+        <v>91909</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>5447</v>
+        <v>1202</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1201,10 +1196,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>742407</v>
+        <v>742088</v>
       </c>
       <c r="R7" t="n">
-        <v>7112222</v>
+        <v>7111972</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1251,44 +1246,44 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Maria Wikdahl</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Elin Kannerby, Isac Enetjärn</t>
+          <t>Maria Wikdahl</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>128115299</v>
+        <v>128120470</v>
       </c>
       <c r="B8" t="n">
-        <v>80185</v>
+        <v>91909</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6464</v>
+        <v>1202</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1298,10 +1293,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>742269</v>
+        <v>741946</v>
       </c>
       <c r="R8" t="n">
-        <v>7112162</v>
+        <v>7111928</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1348,61 +1343,57 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Maria Wikdahl</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Elin Kannerby, Isac Enetjärn</t>
+          <t>Maria Wikdahl</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>128115290</v>
+        <v>128115313</v>
       </c>
       <c r="B9" t="n">
-        <v>56917</v>
+        <v>83173</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100138</v>
+        <v>1312</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr"/>
-      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Selsknösen, Vb</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>742080</v>
+        <v>742199</v>
       </c>
       <c r="R9" t="n">
-        <v>7112234</v>
+        <v>7112142</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1435,11 +1426,6 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-08-27</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Fjäder funnen</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1466,10 +1452,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>128115289</v>
+        <v>128120526</v>
       </c>
       <c r="B10" t="n">
-        <v>91550</v>
+        <v>83173</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1477,21 +1463,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1202</v>
+        <v>1312</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1501,10 +1487,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>742020</v>
+        <v>742268</v>
       </c>
       <c r="R10" t="n">
-        <v>7111950</v>
+        <v>7112227</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1531,12 +1517,12 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-08-27</t>
+          <t>2025-08-23</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2025-08-27</t>
+          <t>2025-08-23</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1545,29 +1531,28 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
-      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Maria Wikdahl</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Elin Kannerby, Isac Enetjärn</t>
+          <t>Maria Wikdahl</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>128115295</v>
+        <v>128120527</v>
       </c>
       <c r="B11" t="n">
-        <v>57727</v>
+        <v>83173</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1575,42 +1560,34 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100109</v>
+        <v>1312</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>Selsknösen, Vb</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>742086</v>
+        <v>742229</v>
       </c>
       <c r="R11" t="n">
-        <v>7112044</v>
+        <v>7112259</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1637,17 +1614,12 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-08-27</t>
+          <t>2025-08-23</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2025-08-27</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
+          <t>2025-08-23</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1662,44 +1634,44 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Maria Wikdahl</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Elin Kannerby, Isac Enetjärn</t>
+          <t>Maria Wikdahl</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>128115294</v>
+        <v>128314982</v>
       </c>
       <c r="B12" t="n">
-        <v>80053</v>
+        <v>92295</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6456</v>
+        <v>1505</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Kristallticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Skeletocutis stellae</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Pilát) Jean Keller</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1709,10 +1681,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>742181</v>
+        <v>742153</v>
       </c>
       <c r="R12" t="n">
-        <v>7112082</v>
+        <v>7112076</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1771,10 +1743,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>128115293</v>
+        <v>128115288</v>
       </c>
       <c r="B13" t="n">
-        <v>57724</v>
+        <v>97453</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1782,38 +1754,34 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100049</v>
+        <v>1841</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedflikmossa</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Lophozia guttulata</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Lindb. &amp; Arnell) A.Evans</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="K13" t="inlineStr"/>
-      <c r="L13" t="inlineStr"/>
-      <c r="M13" t="inlineStr"/>
-      <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>Selsknösen, Vb</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>742018</v>
+        <v>742438</v>
       </c>
       <c r="R13" t="n">
-        <v>7112166</v>
+        <v>7112145</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1854,6 +1822,7 @@
       <c r="AE13" t="b">
         <v>0</v>
       </c>
+      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
@@ -1872,10 +1841,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>128115302</v>
+        <v>128314983</v>
       </c>
       <c r="B14" t="n">
-        <v>98724</v>
+        <v>92281</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1883,38 +1852,34 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>220787</v>
+        <v>2062</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ulltickeporing</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Skeletocutis brevispora</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="J14" t="inlineStr"/>
-      <c r="K14" t="inlineStr"/>
-      <c r="L14" t="inlineStr"/>
-      <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
           <t>Selsknösen, Vb</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>742182</v>
+        <v>742315</v>
       </c>
       <c r="R14" t="n">
-        <v>7112089</v>
+        <v>7112279</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1974,49 +1939,45 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>128115304</v>
+        <v>128115298</v>
       </c>
       <c r="B15" t="n">
-        <v>98724</v>
+        <v>96338</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>220787</v>
+        <v>2809</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Mörk husmossa</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hylocomiastrum umbratum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Hedw.) M.Fleisch.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
-      <c r="J15" t="inlineStr"/>
-      <c r="K15" t="inlineStr"/>
-      <c r="L15" t="inlineStr"/>
-      <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
           <t>Selsknösen, Vb</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>741996</v>
+        <v>742124</v>
       </c>
       <c r="R15" t="n">
-        <v>7111968</v>
+        <v>7112073</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2057,7 +2018,6 @@
       <c r="AE15" t="b">
         <v>0</v>
       </c>
-      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
       </c>
@@ -2076,53 +2036,45 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>128115367</v>
+        <v>128115285</v>
       </c>
       <c r="B16" t="n">
-        <v>57727</v>
+        <v>91872</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100109</v>
+        <v>5447</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="K16" t="inlineStr"/>
-      <c r="L16" t="inlineStr"/>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
           <t>Selsknösen, Vb</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>742063</v>
+        <v>742407</v>
       </c>
       <c r="R16" t="n">
-        <v>7111956</v>
+        <v>7112222</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2155,11 +2107,6 @@
       <c r="AA16" t="inlineStr">
         <is>
           <t>2025-08-27</t>
-        </is>
-      </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2186,10 +2133,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>128115314</v>
+        <v>128115286</v>
       </c>
       <c r="B17" t="n">
-        <v>98641</v>
+        <v>91872</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2197,21 +2144,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>219790</v>
+        <v>5447</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2221,10 +2168,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>742445</v>
+        <v>742205</v>
       </c>
       <c r="R17" t="n">
-        <v>7112152</v>
+        <v>7112115</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2286,7 +2233,7 @@
         <v>128115287</v>
       </c>
       <c r="B18" t="n">
-        <v>91514</v>
+        <v>91872</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2380,10 +2327,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>128115298</v>
+        <v>128120463</v>
       </c>
       <c r="B19" t="n">
-        <v>95950</v>
+        <v>91872</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2391,21 +2338,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>2809</v>
+        <v>5447</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Mörk husmossa</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Hylocomiastrum umbratum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Hedw.) M.Fleisch.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2415,10 +2362,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>742124</v>
+        <v>742161</v>
       </c>
       <c r="R19" t="n">
-        <v>7112073</v>
+        <v>7112190</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2465,44 +2412,44 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Maria Wikdahl</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Elin Kannerby, Isac Enetjärn</t>
+          <t>Maria Wikdahl</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>128115288</v>
+        <v>128120464</v>
       </c>
       <c r="B20" t="n">
-        <v>97065</v>
+        <v>91872</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>1841</v>
+        <v>5447</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Vedflikmossa</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Lophozia guttulata</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Lindb. &amp; Arnell) A.Evans</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2512,10 +2459,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>742438</v>
+        <v>742344</v>
       </c>
       <c r="R20" t="n">
-        <v>7112145</v>
+        <v>7112196</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2556,51 +2503,50 @@
       <c r="AE20" t="b">
         <v>0</v>
       </c>
-      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
       </c>
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Maria Wikdahl</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Elin Kannerby, Isac Enetjärn</t>
+          <t>Maria Wikdahl</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>128115286</v>
+        <v>128115309</v>
       </c>
       <c r="B21" t="n">
-        <v>91514</v>
+        <v>79327</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2610,10 +2556,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>742205</v>
+        <v>741959</v>
       </c>
       <c r="R21" t="n">
-        <v>7112115</v>
+        <v>7112093</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2672,14 +2618,14 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>128115309</v>
+        <v>128115310</v>
       </c>
       <c r="B22" t="n">
-        <v>79044</v>
+        <v>79327</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E22" t="n">
@@ -2707,10 +2653,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>741959</v>
+        <v>742019</v>
       </c>
       <c r="R22" t="n">
-        <v>7112093</v>
+        <v>7112138</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2769,32 +2715,32 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>128115313</v>
+        <v>128115311</v>
       </c>
       <c r="B23" t="n">
-        <v>82878</v>
+        <v>79327</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>1312</v>
+        <v>6425</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2804,10 +2750,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>742199</v>
+        <v>742052</v>
       </c>
       <c r="R23" t="n">
-        <v>7112142</v>
+        <v>7112024</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2866,42 +2812,37 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>128120481</v>
+        <v>128120518</v>
       </c>
       <c r="B24" t="n">
-        <v>57686</v>
+        <v>79327</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
+      <c r="J24" t="inlineStr"/>
       <c r="K24" t="inlineStr"/>
-      <c r="L24" t="inlineStr"/>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
@@ -2909,10 +2850,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>742368</v>
+        <v>741896</v>
       </c>
       <c r="R24" t="n">
-        <v>7112244</v>
+        <v>7112025</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -2947,12 +2888,18 @@
           <t>2025-08-27</t>
         </is>
       </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
+        </is>
+      </c>
       <c r="AD24" t="b">
         <v>0</v>
       </c>
       <c r="AE24" t="b">
         <v>0</v>
       </c>
+      <c r="AF24" t="inlineStr"/>
       <c r="AG24" t="b">
         <v>0</v>
       </c>
@@ -2971,53 +2918,45 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>128120473</v>
+        <v>128120519</v>
       </c>
       <c r="B25" t="n">
-        <v>57689</v>
+        <v>79327</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
-      <c r="K25" t="inlineStr"/>
-      <c r="L25" t="inlineStr"/>
-      <c r="M25" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
           <t>Selsknösen, Vb</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>742178</v>
+        <v>741938</v>
       </c>
       <c r="R25" t="n">
-        <v>7112150</v>
+        <v>7112064</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3044,17 +2983,12 @@
       </c>
       <c r="Y25" t="inlineStr">
         <is>
-          <t>2025-08-23</t>
+          <t>2025-08-27</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>2025-08-23</t>
-        </is>
-      </c>
-      <c r="AC25" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
+          <t>2025-08-27</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3081,53 +3015,45 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>128120471</v>
+        <v>128120520</v>
       </c>
       <c r="B26" t="n">
-        <v>57689</v>
+        <v>79327</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
-      <c r="K26" t="inlineStr"/>
-      <c r="L26" t="inlineStr"/>
-      <c r="M26" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
           <t>Selsknösen, Vb</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>742171</v>
+        <v>741965</v>
       </c>
       <c r="R26" t="n">
-        <v>7112018</v>
+        <v>7112091</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3162,16 +3088,11 @@
           <t>2025-08-27</t>
         </is>
       </c>
-      <c r="AC26" t="inlineStr">
-        <is>
-          <t>Ringhacksliknande på gran.</t>
-        </is>
-      </c>
       <c r="AD26" t="b">
         <v>0</v>
       </c>
       <c r="AE26" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AG26" t="b">
         <v>0</v>
@@ -3191,32 +3112,32 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>128120479</v>
+        <v>128120521</v>
       </c>
       <c r="B27" t="n">
-        <v>80223</v>
+        <v>79327</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3226,10 +3147,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>741958</v>
+        <v>741973</v>
       </c>
       <c r="R27" t="n">
-        <v>7111915</v>
+        <v>7112070</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3268,9 +3189,8 @@
         <v>0</v>
       </c>
       <c r="AE27" t="b">
-        <v>1</v>
-      </c>
-      <c r="AF27" t="inlineStr"/>
+        <v>0</v>
+      </c>
       <c r="AG27" t="b">
         <v>0</v>
       </c>
@@ -3289,10 +3209,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>128120500</v>
+        <v>128120522</v>
       </c>
       <c r="B28" t="n">
-        <v>98592</v>
+        <v>79327</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3300,38 +3220,34 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
-      <c r="J28" t="inlineStr"/>
-      <c r="K28" t="inlineStr"/>
-      <c r="L28" t="inlineStr"/>
-      <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
           <t>Selsknösen, Vb</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>741939</v>
+        <v>741909</v>
       </c>
       <c r="R28" t="n">
-        <v>7111973</v>
+        <v>7111957</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3358,17 +3274,12 @@
       </c>
       <c r="Y28" t="inlineStr">
         <is>
-          <t>2025-08-23</t>
+          <t>2025-08-27</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
         <is>
-          <t>2025-08-23</t>
-        </is>
-      </c>
-      <c r="AC28" t="inlineStr">
-        <is>
-          <t>Rikligt</t>
+          <t>2025-08-27</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3377,7 +3288,6 @@
       <c r="AE28" t="b">
         <v>0</v>
       </c>
-      <c r="AF28" t="inlineStr"/>
       <c r="AG28" t="b">
         <v>0</v>
       </c>
@@ -3396,32 +3306,32 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>128120464</v>
+        <v>128120523</v>
       </c>
       <c r="B29" t="n">
-        <v>91432</v>
+        <v>79327</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3431,10 +3341,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>742344</v>
+        <v>742019</v>
       </c>
       <c r="R29" t="n">
-        <v>7112196</v>
+        <v>7112056</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3461,12 +3371,12 @@
       </c>
       <c r="Y29" t="inlineStr">
         <is>
-          <t>2025-08-27</t>
+          <t>2025-08-23</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>2025-08-27</t>
+          <t>2025-08-23</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3493,32 +3403,32 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>128120512</v>
+        <v>128120524</v>
       </c>
       <c r="B30" t="n">
-        <v>91485</v>
+        <v>79327</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3528,10 +3438,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>742457</v>
+        <v>742089</v>
       </c>
       <c r="R30" t="n">
-        <v>7112145</v>
+        <v>7112176</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3558,12 +3468,12 @@
       </c>
       <c r="Y30" t="inlineStr">
         <is>
-          <t>2025-08-27</t>
+          <t>2025-08-23</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
         <is>
-          <t>2025-08-27</t>
+          <t>2025-08-23</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3590,53 +3500,45 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>128120482</v>
+        <v>128120525</v>
       </c>
       <c r="B31" t="n">
-        <v>57686</v>
+        <v>79327</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
-      <c r="K31" t="inlineStr"/>
-      <c r="L31" t="inlineStr"/>
-      <c r="M31" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
           <t>Selsknösen, Vb</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>742472</v>
+        <v>741900</v>
       </c>
       <c r="R31" t="n">
-        <v>7112117</v>
+        <v>7112038</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3695,32 +3597,32 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>128120494</v>
+        <v>128115294</v>
       </c>
       <c r="B32" t="n">
-        <v>80194</v>
+        <v>80336</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6458</v>
+        <v>6456</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3730,10 +3632,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>741962</v>
+        <v>742181</v>
       </c>
       <c r="R32" t="n">
-        <v>7111966</v>
+        <v>7112082</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3780,65 +3682,57 @@
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Maria Wikdahl</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Maria Wikdahl</t>
+          <t>Elin Kannerby, Isac Enetjärn</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>128120489</v>
+        <v>128120491</v>
       </c>
       <c r="B33" t="n">
-        <v>57686</v>
+        <v>80336</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>100049</v>
+        <v>6456</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
-      <c r="K33" t="inlineStr"/>
-      <c r="L33" t="inlineStr"/>
-      <c r="M33" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
           <t>Selsknösen, Vb</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>742176</v>
+        <v>742255</v>
       </c>
       <c r="R33" t="n">
-        <v>7112009</v>
+        <v>7112289</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3897,10 +3791,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>128120497</v>
+        <v>128120492</v>
       </c>
       <c r="B34" t="n">
-        <v>58059</v>
+        <v>80336</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3908,21 +3802,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>103015</v>
+        <v>6456</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -3932,10 +3826,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>741902</v>
+        <v>741909</v>
       </c>
       <c r="R34" t="n">
-        <v>7111998</v>
+        <v>7111939</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -3994,10 +3888,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>128120515</v>
+        <v>128120494</v>
       </c>
       <c r="B35" t="n">
-        <v>91485</v>
+        <v>80432</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4005,21 +3899,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>5432</v>
+        <v>6458</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4029,10 +3923,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>741977</v>
+        <v>741962</v>
       </c>
       <c r="R35" t="n">
-        <v>7111967</v>
+        <v>7111966</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4059,12 +3953,12 @@
       </c>
       <c r="Y35" t="inlineStr">
         <is>
-          <t>2025-08-23</t>
+          <t>2025-08-27</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
         <is>
-          <t>2025-08-23</t>
+          <t>2025-08-27</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4091,32 +3985,32 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>128120498</v>
+        <v>128120479</v>
       </c>
       <c r="B36" t="n">
-        <v>98592</v>
+        <v>80461</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>220787</v>
+        <v>6462</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4126,10 +4020,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>742472</v>
+        <v>741958</v>
       </c>
       <c r="R36" t="n">
-        <v>7112142</v>
+        <v>7111915</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4164,16 +4058,11 @@
           <t>2025-08-27</t>
         </is>
       </c>
-      <c r="AC36" t="inlineStr">
-        <is>
-          <t>Rikligt</t>
-        </is>
-      </c>
       <c r="AD36" t="b">
         <v>0</v>
       </c>
       <c r="AE36" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AF36" t="inlineStr"/>
       <c r="AG36" t="b">
@@ -4194,10 +4083,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>128120463</v>
+        <v>128120531</v>
       </c>
       <c r="B37" t="n">
-        <v>91432</v>
+        <v>80467</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4205,21 +4094,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>5447</v>
+        <v>6463</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4229,10 +4118,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>742161</v>
+        <v>741963</v>
       </c>
       <c r="R37" t="n">
-        <v>7112190</v>
+        <v>7111967</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4291,32 +4180,32 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>128120517</v>
+        <v>128115299</v>
       </c>
       <c r="B38" t="n">
-        <v>91485</v>
+        <v>80468</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>5432</v>
+        <v>6464</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4326,10 +4215,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>741968</v>
+        <v>742269</v>
       </c>
       <c r="R38" t="n">
-        <v>7111957</v>
+        <v>7112162</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4376,61 +4265,61 @@
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Maria Wikdahl</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Maria Wikdahl</t>
+          <t>Elin Kannerby, Isac Enetjärn</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>128120504</v>
+        <v>128115293</v>
       </c>
       <c r="B39" t="n">
-        <v>98592</v>
+        <v>57950</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I39" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr"/>
+      <c r="K39" t="inlineStr"/>
+      <c r="L39" t="inlineStr"/>
+      <c r="M39" t="inlineStr"/>
+      <c r="N39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
           <t>Selsknösen, Vb</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>741998</v>
+        <v>742018</v>
       </c>
       <c r="R39" t="n">
-        <v>7111958</v>
+        <v>7112166</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4471,64 +4360,71 @@
       <c r="AE39" t="b">
         <v>0</v>
       </c>
-      <c r="AF39" t="inlineStr"/>
       <c r="AG39" t="b">
         <v>0</v>
       </c>
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Maria Wikdahl</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Maria Wikdahl</t>
+          <t>Elin Kannerby, Isac Enetjärn</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>128120509</v>
+        <v>128120480</v>
       </c>
       <c r="B40" t="n">
-        <v>98592</v>
+        <v>57950</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
+      <c r="K40" t="inlineStr"/>
+      <c r="L40" t="inlineStr"/>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>gammalt bo</t>
+        </is>
+      </c>
+      <c r="N40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
           <t>Selsknösen, Vb</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>742189</v>
+        <v>742020</v>
       </c>
       <c r="R40" t="n">
-        <v>7112063</v>
+        <v>7111987</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4567,7 +4463,7 @@
         <v>0</v>
       </c>
       <c r="AE40" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG40" t="b">
         <v>0</v>
@@ -4587,45 +4483,53 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>128120469</v>
+        <v>128120481</v>
       </c>
       <c r="B41" t="n">
-        <v>91467</v>
+        <v>57950</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>1202</v>
+        <v>100049</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
+      <c r="K41" t="inlineStr"/>
+      <c r="L41" t="inlineStr"/>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
           <t>Selsknösen, Vb</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>742088</v>
+        <v>742368</v>
       </c>
       <c r="R41" t="n">
-        <v>7111972</v>
+        <v>7112244</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4684,14 +4588,14 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>128120484</v>
+        <v>128120482</v>
       </c>
       <c r="B42" t="n">
-        <v>57686</v>
+        <v>57950</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E42" t="n">
@@ -4727,10 +4631,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>741951</v>
+        <v>742472</v>
       </c>
       <c r="R42" t="n">
-        <v>7111949</v>
+        <v>7112117</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4789,45 +4693,53 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>128120467</v>
+        <v>128120483</v>
       </c>
       <c r="B43" t="n">
-        <v>91467</v>
+        <v>57950</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>1202</v>
+        <v>100049</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
+      <c r="K43" t="inlineStr"/>
+      <c r="L43" t="inlineStr"/>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
           <t>Selsknösen, Vb</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>742208</v>
+        <v>742340</v>
       </c>
       <c r="R43" t="n">
-        <v>7112210</v>
+        <v>7112183</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4854,12 +4766,12 @@
       </c>
       <c r="Y43" t="inlineStr">
         <is>
-          <t>2025-08-23</t>
+          <t>2025-08-27</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
         <is>
-          <t>2025-08-23</t>
+          <t>2025-08-27</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -4886,14 +4798,14 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>128120483</v>
+        <v>128120484</v>
       </c>
       <c r="B44" t="n">
-        <v>57686</v>
+        <v>57950</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E44" t="n">
@@ -4929,10 +4841,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>742340</v>
+        <v>741951</v>
       </c>
       <c r="R44" t="n">
-        <v>7112183</v>
+        <v>7111949</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -4991,45 +4903,53 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>128120507</v>
+        <v>128120485</v>
       </c>
       <c r="B45" t="n">
-        <v>98592</v>
+        <v>57950</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
+      <c r="K45" t="inlineStr"/>
+      <c r="L45" t="inlineStr"/>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
           <t>Selsknösen, Vb</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>742163</v>
+        <v>742170</v>
       </c>
       <c r="R45" t="n">
-        <v>7112200</v>
+        <v>7112262</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5056,12 +4976,12 @@
       </c>
       <c r="Y45" t="inlineStr">
         <is>
-          <t>2025-08-27</t>
+          <t>2025-08-23</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
         <is>
-          <t>2025-08-27</t>
+          <t>2025-08-23</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5088,45 +5008,53 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>128120513</v>
+        <v>128120486</v>
       </c>
       <c r="B46" t="n">
-        <v>91485</v>
+        <v>57950</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>5432</v>
+        <v>100049</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
+      <c r="K46" t="inlineStr"/>
+      <c r="L46" t="inlineStr"/>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
           <t>Selsknösen, Vb</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>742161</v>
+        <v>742107</v>
       </c>
       <c r="R46" t="n">
-        <v>7112111</v>
+        <v>7112066</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5153,12 +5081,12 @@
       </c>
       <c r="Y46" t="inlineStr">
         <is>
-          <t>2025-08-27</t>
+          <t>2025-08-23</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
         <is>
-          <t>2025-08-27</t>
+          <t>2025-08-23</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5185,45 +5113,53 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>128120514</v>
+        <v>128120487</v>
       </c>
       <c r="B47" t="n">
-        <v>91485</v>
+        <v>57950</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>5432</v>
+        <v>100049</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
+      <c r="K47" t="inlineStr"/>
+      <c r="L47" t="inlineStr"/>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
           <t>Selsknösen, Vb</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>742136</v>
+        <v>741971</v>
       </c>
       <c r="R47" t="n">
-        <v>7112081</v>
+        <v>7111953</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5250,12 +5186,17 @@
       </c>
       <c r="Y47" t="inlineStr">
         <is>
-          <t>2025-08-23</t>
+          <t>2025-08-27</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
         <is>
-          <t>2025-08-23</t>
+          <t>2025-08-27</t>
+        </is>
+      </c>
+      <c r="AC47" t="inlineStr">
+        <is>
+          <t>Mycket färska spår, se bild.</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5282,45 +5223,53 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>128120524</v>
+        <v>128120488</v>
       </c>
       <c r="B48" t="n">
-        <v>79089</v>
+        <v>57950</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
+      <c r="K48" t="inlineStr"/>
+      <c r="L48" t="inlineStr"/>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
           <t>Selsknösen, Vb</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>742089</v>
+        <v>742135</v>
       </c>
       <c r="R48" t="n">
-        <v>7112176</v>
+        <v>7112060</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5347,12 +5296,12 @@
       </c>
       <c r="Y48" t="inlineStr">
         <is>
-          <t>2025-08-23</t>
+          <t>2025-08-27</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
         <is>
-          <t>2025-08-23</t>
+          <t>2025-08-27</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5379,10 +5328,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>128120531</v>
+        <v>128120489</v>
       </c>
       <c r="B49" t="n">
-        <v>80229</v>
+        <v>57950</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5390,34 +5339,42 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6463</v>
+        <v>100049</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
+      <c r="K49" t="inlineStr"/>
+      <c r="L49" t="inlineStr"/>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
           <t>Selsknösen, Vb</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>741963</v>
+        <v>742176</v>
       </c>
       <c r="R49" t="n">
-        <v>7111967</v>
+        <v>7112009</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5476,45 +5433,53 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>128120521</v>
+        <v>128120490</v>
       </c>
       <c r="B50" t="n">
-        <v>79089</v>
+        <v>57950</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
+      <c r="K50" t="inlineStr"/>
+      <c r="L50" t="inlineStr"/>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
           <t>Selsknösen, Vb</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>741973</v>
+        <v>741943</v>
       </c>
       <c r="R50" t="n">
-        <v>7112070</v>
+        <v>7111915</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5573,10 +5538,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>128120527</v>
+        <v>128115295</v>
       </c>
       <c r="B51" t="n">
-        <v>82948</v>
+        <v>57953</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5584,34 +5549,42 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>1312</v>
+        <v>100109</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
+      <c r="K51" t="inlineStr"/>
+      <c r="L51" t="inlineStr"/>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
           <t>Selsknösen, Vb</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>742229</v>
+        <v>742086</v>
       </c>
       <c r="R51" t="n">
-        <v>7112259</v>
+        <v>7112044</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5638,12 +5611,17 @@
       </c>
       <c r="Y51" t="inlineStr">
         <is>
-          <t>2025-08-23</t>
+          <t>2025-08-27</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
         <is>
-          <t>2025-08-23</t>
+          <t>2025-08-27</t>
+        </is>
+      </c>
+      <c r="AC51" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -5658,22 +5636,22 @@
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>Maria Wikdahl</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Maria Wikdahl</t>
+          <t>Elin Kannerby, Isac Enetjärn</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>128120488</v>
+        <v>128115367</v>
       </c>
       <c r="B52" t="n">
-        <v>57686</v>
+        <v>57953</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5681,16 +5659,16 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
@@ -5703,7 +5681,7 @@
       <c r="L52" t="inlineStr"/>
       <c r="M52" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="N52" t="inlineStr"/>
@@ -5713,10 +5691,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>742135</v>
+        <v>742063</v>
       </c>
       <c r="R52" t="n">
-        <v>7112060</v>
+        <v>7111956</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5751,6 +5729,11 @@
           <t>2025-08-27</t>
         </is>
       </c>
+      <c r="AC52" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
+        </is>
+      </c>
       <c r="AD52" t="b">
         <v>0</v>
       </c>
@@ -5763,22 +5746,22 @@
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>Maria Wikdahl</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>Maria Wikdahl</t>
+          <t>Elin Kannerby, Isac Enetjärn</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>128120480</v>
+        <v>128120471</v>
       </c>
       <c r="B53" t="n">
-        <v>57686</v>
+        <v>57953</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5786,16 +5769,16 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
@@ -5808,7 +5791,7 @@
       <c r="L53" t="inlineStr"/>
       <c r="M53" t="inlineStr">
         <is>
-          <t>gammalt bo</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N53" t="inlineStr"/>
@@ -5818,10 +5801,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>742020</v>
+        <v>742171</v>
       </c>
       <c r="R53" t="n">
-        <v>7111987</v>
+        <v>7112018</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -5854,6 +5837,11 @@
       <c r="AA53" t="inlineStr">
         <is>
           <t>2025-08-27</t>
+        </is>
+      </c>
+      <c r="AC53" t="inlineStr">
+        <is>
+          <t>Ringhacksliknande på gran.</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -5880,10 +5868,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>128120478</v>
+        <v>128120472</v>
       </c>
       <c r="B54" t="n">
-        <v>57849</v>
+        <v>57953</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -5891,34 +5879,42 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
+      <c r="K54" t="inlineStr"/>
+      <c r="L54" t="inlineStr"/>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
           <t>Selsknösen, Vb</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>741940</v>
+        <v>741931</v>
       </c>
       <c r="R54" t="n">
-        <v>7111944</v>
+        <v>7111932</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -5951,6 +5947,11 @@
       <c r="AA54" t="inlineStr">
         <is>
           <t>2025-08-27</t>
+        </is>
+      </c>
+      <c r="AC54" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på tall.</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -5977,45 +5978,53 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>128120508</v>
+        <v>128120473</v>
       </c>
       <c r="B55" t="n">
-        <v>98592</v>
+        <v>57953</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
+      <c r="K55" t="inlineStr"/>
+      <c r="L55" t="inlineStr"/>
+      <c r="M55" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
           <t>Selsknösen, Vb</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>742177</v>
+        <v>742178</v>
       </c>
       <c r="R55" t="n">
-        <v>7112084</v>
+        <v>7112150</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6042,12 +6051,17 @@
       </c>
       <c r="Y55" t="inlineStr">
         <is>
-          <t>2025-08-27</t>
+          <t>2025-08-23</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
         <is>
-          <t>2025-08-27</t>
+          <t>2025-08-23</t>
+        </is>
+      </c>
+      <c r="AC55" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6074,10 +6088,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>128120522</v>
+        <v>128120474</v>
       </c>
       <c r="B56" t="n">
-        <v>79089</v>
+        <v>57953</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6085,34 +6099,42 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
+      <c r="K56" t="inlineStr"/>
+      <c r="L56" t="inlineStr"/>
+      <c r="M56" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
           <t>Selsknösen, Vb</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>741909</v>
+        <v>742191</v>
       </c>
       <c r="R56" t="n">
-        <v>7111957</v>
+        <v>7112251</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6145,6 +6167,11 @@
       <c r="AA56" t="inlineStr">
         <is>
           <t>2025-08-27</t>
+        </is>
+      </c>
+      <c r="AC56" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6171,10 +6198,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>128120468</v>
+        <v>128120475</v>
       </c>
       <c r="B57" t="n">
-        <v>91467</v>
+        <v>57953</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6182,34 +6209,42 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
+      <c r="K57" t="inlineStr"/>
+      <c r="L57" t="inlineStr"/>
+      <c r="M57" t="inlineStr">
+        <is>
+          <t>gammalt bo</t>
+        </is>
+      </c>
+      <c r="N57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
           <t>Selsknösen, Vb</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>742464</v>
+        <v>742203</v>
       </c>
       <c r="R57" t="n">
-        <v>7112167</v>
+        <v>7112188</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6248,7 +6283,7 @@
         <v>0</v>
       </c>
       <c r="AE57" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG57" t="b">
         <v>0</v>
@@ -6268,45 +6303,49 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>128120506</v>
+        <v>128115290</v>
       </c>
       <c r="B58" t="n">
-        <v>98592</v>
+        <v>57141</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>220787</v>
+        <v>100138</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
+      <c r="K58" t="inlineStr"/>
+      <c r="L58" t="inlineStr"/>
+      <c r="M58" t="inlineStr"/>
+      <c r="N58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
           <t>Selsknösen, Vb</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>741991</v>
+        <v>742080</v>
       </c>
       <c r="R58" t="n">
-        <v>7111978</v>
+        <v>7112234</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6341,6 +6380,11 @@
           <t>2025-08-27</t>
         </is>
       </c>
+      <c r="AC58" t="inlineStr">
+        <is>
+          <t>Fjäder funnen</t>
+        </is>
+      </c>
       <c r="AD58" t="b">
         <v>0</v>
       </c>
@@ -6353,44 +6397,44 @@
       <c r="AT58" t="inlineStr"/>
       <c r="AW58" t="inlineStr">
         <is>
-          <t>Maria Wikdahl</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX58" t="inlineStr">
         <is>
-          <t>Maria Wikdahl</t>
+          <t>Elin Kannerby, Isac Enetjärn</t>
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>128120523</v>
+        <v>128120497</v>
       </c>
       <c r="B59" t="n">
-        <v>79089</v>
+        <v>58327</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>6425</v>
+        <v>103015</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -6400,10 +6444,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>742019</v>
+        <v>741902</v>
       </c>
       <c r="R59" t="n">
-        <v>7112056</v>
+        <v>7111998</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6430,12 +6474,12 @@
       </c>
       <c r="Y59" t="inlineStr">
         <is>
-          <t>2025-08-23</t>
+          <t>2025-08-27</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
         <is>
-          <t>2025-08-23</t>
+          <t>2025-08-27</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -6462,32 +6506,32 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>128120492</v>
+        <v>128120477</v>
       </c>
       <c r="B60" t="n">
-        <v>80098</v>
+        <v>58114</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>6456</v>
+        <v>103021</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -6497,10 +6541,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>741909</v>
+        <v>742054</v>
       </c>
       <c r="R60" t="n">
-        <v>7111939</v>
+        <v>7112013</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6559,10 +6603,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>128120485</v>
+        <v>128120478</v>
       </c>
       <c r="B61" t="n">
-        <v>57686</v>
+        <v>58114</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6570,42 +6614,34 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>100049</v>
+        <v>103021</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
-      <c r="K61" t="inlineStr"/>
-      <c r="L61" t="inlineStr"/>
-      <c r="M61" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
           <t>Selsknösen, Vb</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>742170</v>
+        <v>741940</v>
       </c>
       <c r="R61" t="n">
-        <v>7112262</v>
+        <v>7111944</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -6632,12 +6668,12 @@
       </c>
       <c r="Y61" t="inlineStr">
         <is>
-          <t>2025-08-23</t>
+          <t>2025-08-27</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
         <is>
-          <t>2025-08-23</t>
+          <t>2025-08-27</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -6664,49 +6700,45 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>128120502</v>
+        <v>128115314</v>
       </c>
       <c r="B62" t="n">
-        <v>98592</v>
+        <v>99035</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>220787</v>
+        <v>219790</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I62" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
         <is>
           <t>Selsknösen, Vb</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>741962</v>
+        <v>742445</v>
       </c>
       <c r="R62" t="n">
-        <v>7111971</v>
+        <v>7112152</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -6747,29 +6779,28 @@
       <c r="AE62" t="b">
         <v>0</v>
       </c>
-      <c r="AF62" t="inlineStr"/>
       <c r="AG62" t="b">
         <v>0</v>
       </c>
       <c r="AT62" t="inlineStr"/>
       <c r="AW62" t="inlineStr">
         <is>
-          <t>Maria Wikdahl</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX62" t="inlineStr">
         <is>
-          <t>Maria Wikdahl</t>
+          <t>Elin Kannerby, Isac Enetjärn</t>
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>128120511</v>
+        <v>128115302</v>
       </c>
       <c r="B63" t="n">
-        <v>98592</v>
+        <v>99118</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -6795,16 +6826,20 @@
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
+      <c r="J63" t="inlineStr"/>
+      <c r="K63" t="inlineStr"/>
+      <c r="L63" t="inlineStr"/>
+      <c r="N63" t="inlineStr"/>
       <c r="P63" t="inlineStr">
         <is>
           <t>Selsknösen, Vb</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>742032</v>
+        <v>742182</v>
       </c>
       <c r="R63" t="n">
-        <v>7111965</v>
+        <v>7112089</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -6845,28 +6880,29 @@
       <c r="AE63" t="b">
         <v>0</v>
       </c>
+      <c r="AF63" t="inlineStr"/>
       <c r="AG63" t="b">
         <v>0</v>
       </c>
       <c r="AT63" t="inlineStr"/>
       <c r="AW63" t="inlineStr">
         <is>
-          <t>Maria Wikdahl</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX63" t="inlineStr">
         <is>
-          <t>Maria Wikdahl</t>
+          <t>Elin Kannerby, Isac Enetjärn</t>
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>128120499</v>
+        <v>128115303</v>
       </c>
       <c r="B64" t="n">
-        <v>98592</v>
+        <v>99118</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -6902,10 +6938,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>741963</v>
+        <v>742050</v>
       </c>
       <c r="R64" t="n">
-        <v>7111964</v>
+        <v>7111963</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -6940,11 +6976,6 @@
           <t>2025-08-27</t>
         </is>
       </c>
-      <c r="AC64" t="inlineStr">
-        <is>
-          <t>Rikligt</t>
-        </is>
-      </c>
       <c r="AD64" t="b">
         <v>0</v>
       </c>
@@ -6958,57 +6989,61 @@
       <c r="AT64" t="inlineStr"/>
       <c r="AW64" t="inlineStr">
         <is>
-          <t>Maria Wikdahl</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX64" t="inlineStr">
         <is>
-          <t>Maria Wikdahl</t>
+          <t>Elin Kannerby, Isac Enetjärn</t>
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>128120516</v>
+        <v>128115304</v>
       </c>
       <c r="B65" t="n">
-        <v>91485</v>
+        <v>99118</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>5432</v>
+        <v>220787</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
+      <c r="J65" t="inlineStr"/>
+      <c r="K65" t="inlineStr"/>
+      <c r="L65" t="inlineStr"/>
+      <c r="N65" t="inlineStr"/>
       <c r="P65" t="inlineStr">
         <is>
           <t>Selsknösen, Vb</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>742047</v>
+        <v>741996</v>
       </c>
       <c r="R65" t="n">
-        <v>7111978</v>
+        <v>7111968</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7049,60 +7084,57 @@
       <c r="AE65" t="b">
         <v>0</v>
       </c>
+      <c r="AF65" t="inlineStr"/>
       <c r="AG65" t="b">
         <v>0</v>
       </c>
       <c r="AT65" t="inlineStr"/>
       <c r="AW65" t="inlineStr">
         <is>
-          <t>Maria Wikdahl</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX65" t="inlineStr">
         <is>
-          <t>Maria Wikdahl</t>
+          <t>Elin Kannerby, Isac Enetjärn</t>
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>128120487</v>
+        <v>128115305</v>
       </c>
       <c r="B66" t="n">
-        <v>57686</v>
+        <v>99118</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
+      <c r="J66" t="inlineStr"/>
       <c r="K66" t="inlineStr"/>
       <c r="L66" t="inlineStr"/>
-      <c r="M66" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N66" t="inlineStr"/>
       <c r="P66" t="inlineStr">
         <is>
@@ -7110,10 +7142,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>741971</v>
+        <v>741970</v>
       </c>
       <c r="R66" t="n">
-        <v>7111953</v>
+        <v>7111969</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7148,82 +7180,70 @@
           <t>2025-08-27</t>
         </is>
       </c>
-      <c r="AC66" t="inlineStr">
-        <is>
-          <t>Mycket färska spår, se bild.</t>
-        </is>
-      </c>
       <c r="AD66" t="b">
         <v>0</v>
       </c>
       <c r="AE66" t="b">
         <v>0</v>
       </c>
+      <c r="AF66" t="inlineStr"/>
       <c r="AG66" t="b">
         <v>0</v>
       </c>
       <c r="AT66" t="inlineStr"/>
       <c r="AW66" t="inlineStr">
         <is>
-          <t>Maria Wikdahl</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX66" t="inlineStr">
         <is>
-          <t>Maria Wikdahl</t>
+          <t>Elin Kannerby, Isac Enetjärn</t>
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>128120475</v>
+        <v>128120498</v>
       </c>
       <c r="B67" t="n">
-        <v>57689</v>
+        <v>99118</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
-      <c r="K67" t="inlineStr"/>
-      <c r="L67" t="inlineStr"/>
-      <c r="M67" t="inlineStr">
-        <is>
-          <t>gammalt bo</t>
-        </is>
-      </c>
-      <c r="N67" t="inlineStr"/>
       <c r="P67" t="inlineStr">
         <is>
           <t>Selsknösen, Vb</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>742203</v>
+        <v>742472</v>
       </c>
       <c r="R67" t="n">
-        <v>7112188</v>
+        <v>7112142</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7258,12 +7278,18 @@
           <t>2025-08-27</t>
         </is>
       </c>
+      <c r="AC67" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
+        </is>
+      </c>
       <c r="AD67" t="b">
         <v>0</v>
       </c>
       <c r="AE67" t="b">
-        <v>1</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="AF67" t="inlineStr"/>
       <c r="AG67" t="b">
         <v>0</v>
       </c>
@@ -7282,10 +7308,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>128120510</v>
+        <v>128120499</v>
       </c>
       <c r="B68" t="n">
-        <v>98592</v>
+        <v>99118</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7311,16 +7337,20 @@
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
+      <c r="J68" t="inlineStr"/>
+      <c r="K68" t="inlineStr"/>
+      <c r="L68" t="inlineStr"/>
+      <c r="N68" t="inlineStr"/>
       <c r="P68" t="inlineStr">
         <is>
           <t>Selsknösen, Vb</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>742050</v>
+        <v>741963</v>
       </c>
       <c r="R68" t="n">
-        <v>7111983</v>
+        <v>7111964</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7355,12 +7385,18 @@
           <t>2025-08-27</t>
         </is>
       </c>
+      <c r="AC68" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
+        </is>
+      </c>
       <c r="AD68" t="b">
         <v>0</v>
       </c>
       <c r="AE68" t="b">
         <v>0</v>
       </c>
+      <c r="AF68" t="inlineStr"/>
       <c r="AG68" t="b">
         <v>0</v>
       </c>
@@ -7379,42 +7415,38 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>128120490</v>
+        <v>128120500</v>
       </c>
       <c r="B69" t="n">
-        <v>57686</v>
+        <v>99118</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
+      <c r="J69" t="inlineStr"/>
       <c r="K69" t="inlineStr"/>
       <c r="L69" t="inlineStr"/>
-      <c r="M69" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N69" t="inlineStr"/>
       <c r="P69" t="inlineStr">
         <is>
@@ -7422,10 +7454,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>741943</v>
+        <v>741939</v>
       </c>
       <c r="R69" t="n">
-        <v>7111915</v>
+        <v>7111973</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7452,12 +7484,17 @@
       </c>
       <c r="Y69" t="inlineStr">
         <is>
-          <t>2025-08-27</t>
+          <t>2025-08-23</t>
         </is>
       </c>
       <c r="AA69" t="inlineStr">
         <is>
-          <t>2025-08-27</t>
+          <t>2025-08-23</t>
+        </is>
+      </c>
+      <c r="AC69" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -7466,6 +7503,7 @@
       <c r="AE69" t="b">
         <v>0</v>
       </c>
+      <c r="AF69" t="inlineStr"/>
       <c r="AG69" t="b">
         <v>0</v>
       </c>
@@ -7484,45 +7522,49 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>128120526</v>
+        <v>128120501</v>
       </c>
       <c r="B70" t="n">
-        <v>82948</v>
+        <v>99118</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>1312</v>
+        <v>220787</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
-        </is>
-      </c>
-      <c r="I70" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
       <c r="P70" t="inlineStr">
         <is>
           <t>Selsknösen, Vb</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>742268</v>
+        <v>742340</v>
       </c>
       <c r="R70" t="n">
-        <v>7112227</v>
+        <v>7112209</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7549,12 +7591,12 @@
       </c>
       <c r="Y70" t="inlineStr">
         <is>
-          <t>2025-08-23</t>
+          <t>2025-08-27</t>
         </is>
       </c>
       <c r="AA70" t="inlineStr">
         <is>
-          <t>2025-08-23</t>
+          <t>2025-08-27</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -7563,6 +7605,7 @@
       <c r="AE70" t="b">
         <v>0</v>
       </c>
+      <c r="AF70" t="inlineStr"/>
       <c r="AG70" t="b">
         <v>0</v>
       </c>
@@ -7581,45 +7624,49 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>128120491</v>
+        <v>128120502</v>
       </c>
       <c r="B71" t="n">
-        <v>80098</v>
+        <v>99118</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>6456</v>
+        <v>220787</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
-        </is>
-      </c>
-      <c r="I71" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
       <c r="P71" t="inlineStr">
         <is>
           <t>Selsknösen, Vb</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>742255</v>
+        <v>741962</v>
       </c>
       <c r="R71" t="n">
-        <v>7112289</v>
+        <v>7111971</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -7660,6 +7707,7 @@
       <c r="AE71" t="b">
         <v>0</v>
       </c>
+      <c r="AF71" t="inlineStr"/>
       <c r="AG71" t="b">
         <v>0</v>
       </c>
@@ -7678,53 +7726,49 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>128120486</v>
+        <v>128120503</v>
       </c>
       <c r="B72" t="n">
-        <v>57686</v>
+        <v>99118</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I72" t="inlineStr"/>
-      <c r="K72" t="inlineStr"/>
-      <c r="L72" t="inlineStr"/>
-      <c r="M72" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N72" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
       <c r="P72" t="inlineStr">
         <is>
           <t>Selsknösen, Vb</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>742107</v>
+        <v>742010</v>
       </c>
       <c r="R72" t="n">
-        <v>7112066</v>
+        <v>7111949</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -7751,12 +7795,12 @@
       </c>
       <c r="Y72" t="inlineStr">
         <is>
-          <t>2025-08-23</t>
+          <t>2025-08-27</t>
         </is>
       </c>
       <c r="AA72" t="inlineStr">
         <is>
-          <t>2025-08-23</t>
+          <t>2025-08-27</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -7765,6 +7809,7 @@
       <c r="AE72" t="b">
         <v>0</v>
       </c>
+      <c r="AF72" t="inlineStr"/>
       <c r="AG72" t="b">
         <v>0</v>
       </c>
@@ -7783,10 +7828,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>128120501</v>
+        <v>128120504</v>
       </c>
       <c r="B73" t="n">
-        <v>98592</v>
+        <v>99118</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -7813,7 +7858,7 @@
       </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>10</t>
         </is>
       </c>
       <c r="P73" t="inlineStr">
@@ -7822,10 +7867,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>742340</v>
+        <v>741998</v>
       </c>
       <c r="R73" t="n">
-        <v>7112209</v>
+        <v>7111958</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -7885,53 +7930,45 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>128120474</v>
+        <v>128120506</v>
       </c>
       <c r="B74" t="n">
-        <v>57689</v>
+        <v>99118</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
-      <c r="K74" t="inlineStr"/>
-      <c r="L74" t="inlineStr"/>
-      <c r="M74" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N74" t="inlineStr"/>
       <c r="P74" t="inlineStr">
         <is>
           <t>Selsknösen, Vb</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>742191</v>
+        <v>741991</v>
       </c>
       <c r="R74" t="n">
-        <v>7112251</v>
+        <v>7111978</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -7964,11 +8001,6 @@
       <c r="AA74" t="inlineStr">
         <is>
           <t>2025-08-27</t>
-        </is>
-      </c>
-      <c r="AC74" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -7995,32 +8027,32 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>128120520</v>
+        <v>128120507</v>
       </c>
       <c r="B75" t="n">
-        <v>79089</v>
+        <v>99118</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -8030,10 +8062,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>741965</v>
+        <v>742163</v>
       </c>
       <c r="R75" t="n">
-        <v>7112091</v>
+        <v>7112200</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8092,32 +8124,32 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>128120470</v>
+        <v>128120508</v>
       </c>
       <c r="B76" t="n">
-        <v>91467</v>
+        <v>99118</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
@@ -8127,10 +8159,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>741946</v>
+        <v>742177</v>
       </c>
       <c r="R76" t="n">
-        <v>7111928</v>
+        <v>7112084</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8189,32 +8221,32 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>128120466</v>
+        <v>128120509</v>
       </c>
       <c r="B77" t="n">
-        <v>91467</v>
+        <v>99118</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
@@ -8224,10 +8256,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>741977</v>
+        <v>742189</v>
       </c>
       <c r="R77" t="n">
-        <v>7111936</v>
+        <v>7112063</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8286,53 +8318,45 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>128120472</v>
+        <v>128120510</v>
       </c>
       <c r="B78" t="n">
-        <v>57689</v>
+        <v>99118</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
-      <c r="K78" t="inlineStr"/>
-      <c r="L78" t="inlineStr"/>
-      <c r="M78" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N78" t="inlineStr"/>
       <c r="P78" t="inlineStr">
         <is>
           <t>Selsknösen, Vb</t>
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>741931</v>
+        <v>742050</v>
       </c>
       <c r="R78" t="n">
-        <v>7111932</v>
+        <v>7111983</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -8365,11 +8389,6 @@
       <c r="AA78" t="inlineStr">
         <is>
           <t>2025-08-27</t>
-        </is>
-      </c>
-      <c r="AC78" t="inlineStr">
-        <is>
-          <t>Äldre ringhack på tall.</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -8396,32 +8415,32 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>128120477</v>
+        <v>128120511</v>
       </c>
       <c r="B79" t="n">
-        <v>57849</v>
+        <v>99118</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>103021</v>
+        <v>220787</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
@@ -8431,10 +8450,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>742054</v>
+        <v>742032</v>
       </c>
       <c r="R79" t="n">
-        <v>7112013</v>
+        <v>7111965</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -8490,303 +8509,6 @@
         </is>
       </c>
       <c r="AY79" t="inlineStr"/>
-    </row>
-    <row r="80">
-      <c r="A80" t="n">
-        <v>128120503</v>
-      </c>
-      <c r="B80" t="n">
-        <v>98592</v>
-      </c>
-      <c r="D80" t="inlineStr">
-        <is>
-          <t>VU</t>
-        </is>
-      </c>
-      <c r="E80" t="n">
-        <v>220787</v>
-      </c>
-      <c r="F80" t="inlineStr">
-        <is>
-          <t>Knärot</t>
-        </is>
-      </c>
-      <c r="G80" t="inlineStr">
-        <is>
-          <t>Goodyera repens</t>
-        </is>
-      </c>
-      <c r="H80" t="inlineStr">
-        <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I80" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="P80" t="inlineStr">
-        <is>
-          <t>Selsknösen, Vb</t>
-        </is>
-      </c>
-      <c r="Q80" t="n">
-        <v>742010</v>
-      </c>
-      <c r="R80" t="n">
-        <v>7111949</v>
-      </c>
-      <c r="S80" t="n">
-        <v>10</v>
-      </c>
-      <c r="T80" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="U80" t="inlineStr">
-        <is>
-          <t>Umeå</t>
-        </is>
-      </c>
-      <c r="V80" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="W80" t="inlineStr">
-        <is>
-          <t>Umeå socken</t>
-        </is>
-      </c>
-      <c r="Y80" t="inlineStr">
-        <is>
-          <t>2025-08-27</t>
-        </is>
-      </c>
-      <c r="AA80" t="inlineStr">
-        <is>
-          <t>2025-08-27</t>
-        </is>
-      </c>
-      <c r="AD80" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE80" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF80" t="inlineStr"/>
-      <c r="AG80" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT80" t="inlineStr"/>
-      <c r="AW80" t="inlineStr">
-        <is>
-          <t>Maria Wikdahl</t>
-        </is>
-      </c>
-      <c r="AX80" t="inlineStr">
-        <is>
-          <t>Maria Wikdahl</t>
-        </is>
-      </c>
-      <c r="AY80" t="inlineStr"/>
-    </row>
-    <row r="81">
-      <c r="A81" t="n">
-        <v>128314983</v>
-      </c>
-      <c r="B81" t="n">
-        <v>91921</v>
-      </c>
-      <c r="D81" t="inlineStr">
-        <is>
-          <t>VU</t>
-        </is>
-      </c>
-      <c r="E81" t="n">
-        <v>2062</v>
-      </c>
-      <c r="F81" t="inlineStr">
-        <is>
-          <t>Ulltickeporing</t>
-        </is>
-      </c>
-      <c r="G81" t="inlineStr">
-        <is>
-          <t>Skeletocutis brevispora</t>
-        </is>
-      </c>
-      <c r="H81" t="inlineStr">
-        <is>
-          <t>Niemelä</t>
-        </is>
-      </c>
-      <c r="I81" t="inlineStr"/>
-      <c r="P81" t="inlineStr">
-        <is>
-          <t>Selsknösen, Vb</t>
-        </is>
-      </c>
-      <c r="Q81" t="n">
-        <v>742315</v>
-      </c>
-      <c r="R81" t="n">
-        <v>7112279</v>
-      </c>
-      <c r="S81" t="n">
-        <v>10</v>
-      </c>
-      <c r="T81" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="U81" t="inlineStr">
-        <is>
-          <t>Umeå</t>
-        </is>
-      </c>
-      <c r="V81" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="W81" t="inlineStr">
-        <is>
-          <t>Umeå socken</t>
-        </is>
-      </c>
-      <c r="Y81" t="inlineStr">
-        <is>
-          <t>2025-08-27</t>
-        </is>
-      </c>
-      <c r="AA81" t="inlineStr">
-        <is>
-          <t>2025-08-27</t>
-        </is>
-      </c>
-      <c r="AD81" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE81" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF81" t="inlineStr"/>
-      <c r="AG81" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT81" t="inlineStr"/>
-      <c r="AW81" t="inlineStr">
-        <is>
-          <t>Elin Kannerby</t>
-        </is>
-      </c>
-      <c r="AX81" t="inlineStr">
-        <is>
-          <t>Elin Kannerby, Isac Enetjärn</t>
-        </is>
-      </c>
-      <c r="AY81" t="inlineStr"/>
-    </row>
-    <row r="82">
-      <c r="A82" t="n">
-        <v>128314982</v>
-      </c>
-      <c r="B82" t="n">
-        <v>91935</v>
-      </c>
-      <c r="D82" t="inlineStr">
-        <is>
-          <t>VU</t>
-        </is>
-      </c>
-      <c r="E82" t="n">
-        <v>1505</v>
-      </c>
-      <c r="F82" t="inlineStr">
-        <is>
-          <t>Kristallticka</t>
-        </is>
-      </c>
-      <c r="G82" t="inlineStr">
-        <is>
-          <t>Skeletocutis stellae</t>
-        </is>
-      </c>
-      <c r="H82" t="inlineStr">
-        <is>
-          <t>(Pilát) Jean Keller</t>
-        </is>
-      </c>
-      <c r="I82" t="inlineStr"/>
-      <c r="P82" t="inlineStr">
-        <is>
-          <t>Selsknösen, Vb</t>
-        </is>
-      </c>
-      <c r="Q82" t="n">
-        <v>742153</v>
-      </c>
-      <c r="R82" t="n">
-        <v>7112076</v>
-      </c>
-      <c r="S82" t="n">
-        <v>10</v>
-      </c>
-      <c r="T82" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="U82" t="inlineStr">
-        <is>
-          <t>Umeå</t>
-        </is>
-      </c>
-      <c r="V82" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="W82" t="inlineStr">
-        <is>
-          <t>Umeå socken</t>
-        </is>
-      </c>
-      <c r="Y82" t="inlineStr">
-        <is>
-          <t>2025-08-27</t>
-        </is>
-      </c>
-      <c r="AA82" t="inlineStr">
-        <is>
-          <t>2025-08-27</t>
-        </is>
-      </c>
-      <c r="AD82" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE82" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG82" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT82" t="inlineStr"/>
-      <c r="AW82" t="inlineStr">
-        <is>
-          <t>Elin Kannerby</t>
-        </is>
-      </c>
-      <c r="AX82" t="inlineStr">
-        <is>
-          <t>Elin Kannerby, Isac Enetjärn</t>
-        </is>
-      </c>
-      <c r="AY82" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 38519-2025 artfynd.xlsx
+++ b/artfynd/A 38519-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY79"/>
+  <dimension ref="A1:AZ79"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -770,6 +775,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128115289</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -867,6 +877,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128120465</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -964,6 +979,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128120466</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1061,6 +1081,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128120467</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1158,6 +1183,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128120468</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1255,6 +1285,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128120469</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1352,6 +1387,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128120470</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1449,6 +1489,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128115313</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1546,6 +1591,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128120526</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1643,6 +1693,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128120527</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1740,6 +1795,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128314982</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1838,6 +1898,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128115288</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -1936,6 +2001,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128314983</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2033,6 +2103,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128115298</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2130,6 +2205,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128115285</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2227,6 +2307,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128115286</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2324,6 +2409,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128115287</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2421,6 +2511,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128120463</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2518,6 +2613,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128120464</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2615,6 +2715,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128115309</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2712,6 +2817,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128115310</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -2809,6 +2919,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128115311</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -2915,6 +3030,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128120518</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3012,6 +3132,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128120519</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3109,6 +3234,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128120520</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3206,6 +3336,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128120521</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3303,6 +3438,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128120522</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3400,6 +3540,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128120523</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3497,6 +3642,11 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128120524</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -3594,6 +3744,11 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128120525</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -3691,6 +3846,11 @@
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128115294</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -3788,6 +3948,11 @@
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128120491</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -3885,6 +4050,11 @@
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128120492</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -3982,6 +4152,11 @@
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128120494</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -4080,6 +4255,11 @@
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128120479</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -4177,6 +4357,11 @@
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128120531</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -4274,6 +4459,11 @@
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128115299</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -4375,6 +4565,11 @@
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128115293</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -4480,6 +4675,11 @@
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128120480</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -4585,6 +4785,11 @@
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128120481</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -4690,6 +4895,11 @@
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128120482</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -4795,6 +5005,11 @@
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
+      <c r="AZ43" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128120483</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -4900,6 +5115,11 @@
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
+      <c r="AZ44" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128120484</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -5005,6 +5225,11 @@
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
+      <c r="AZ45" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128120485</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -5110,6 +5335,11 @@
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
+      <c r="AZ46" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128120486</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -5220,6 +5450,11 @@
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
+      <c r="AZ47" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128120487</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -5325,6 +5560,11 @@
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
+      <c r="AZ48" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128120488</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -5430,6 +5670,11 @@
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
+      <c r="AZ49" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128120489</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -5535,6 +5780,11 @@
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
+      <c r="AZ50" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128120490</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
@@ -5645,6 +5895,11 @@
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
+      <c r="AZ51" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128115295</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
@@ -5755,6 +6010,11 @@
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
+      <c r="AZ52" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128115367</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
@@ -5865,6 +6125,11 @@
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
+      <c r="AZ53" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128120471</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
@@ -5975,6 +6240,11 @@
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
+      <c r="AZ54" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128120472</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
@@ -6085,6 +6355,11 @@
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
+      <c r="AZ55" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128120473</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
@@ -6195,6 +6470,11 @@
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
+      <c r="AZ56" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128120474</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
@@ -6300,6 +6580,11 @@
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
+      <c r="AZ57" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128120475</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
@@ -6406,6 +6691,11 @@
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
+      <c r="AZ58" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128115290</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
@@ -6503,6 +6793,11 @@
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
+      <c r="AZ59" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128120497</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
@@ -6600,6 +6895,11 @@
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
+      <c r="AZ60" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128120477</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
@@ -6697,6 +6997,11 @@
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
+      <c r="AZ61" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128120478</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
@@ -6794,6 +7099,11 @@
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
+      <c r="AZ62" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128115314</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
@@ -6896,6 +7206,11 @@
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
+      <c r="AZ63" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128115302</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
@@ -6998,6 +7313,11 @@
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
+      <c r="AZ64" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128115303</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
@@ -7100,6 +7420,11 @@
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
+      <c r="AZ65" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128115304</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
@@ -7202,6 +7527,11 @@
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
+      <c r="AZ66" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128115305</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
@@ -7305,6 +7635,11 @@
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
+      <c r="AZ67" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128120498</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
@@ -7412,6 +7747,11 @@
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>
+      <c r="AZ68" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128120499</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
@@ -7519,6 +7859,11 @@
         </is>
       </c>
       <c r="AY69" t="inlineStr"/>
+      <c r="AZ69" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128120500</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
@@ -7621,6 +7966,11 @@
         </is>
       </c>
       <c r="AY70" t="inlineStr"/>
+      <c r="AZ70" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128120501</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
@@ -7723,6 +8073,11 @@
         </is>
       </c>
       <c r="AY71" t="inlineStr"/>
+      <c r="AZ71" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128120502</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
@@ -7825,6 +8180,11 @@
         </is>
       </c>
       <c r="AY72" t="inlineStr"/>
+      <c r="AZ72" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128120503</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
@@ -7927,6 +8287,11 @@
         </is>
       </c>
       <c r="AY73" t="inlineStr"/>
+      <c r="AZ73" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128120504</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="n">
@@ -8024,6 +8389,11 @@
         </is>
       </c>
       <c r="AY74" t="inlineStr"/>
+      <c r="AZ74" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128120506</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="n">
@@ -8121,6 +8491,11 @@
         </is>
       </c>
       <c r="AY75" t="inlineStr"/>
+      <c r="AZ75" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128120507</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="n">
@@ -8218,6 +8593,11 @@
         </is>
       </c>
       <c r="AY76" t="inlineStr"/>
+      <c r="AZ76" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128120508</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="n">
@@ -8315,6 +8695,11 @@
         </is>
       </c>
       <c r="AY77" t="inlineStr"/>
+      <c r="AZ77" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128120509</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="n">
@@ -8412,6 +8797,11 @@
         </is>
       </c>
       <c r="AY78" t="inlineStr"/>
+      <c r="AZ78" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128120510</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="n">
@@ -8509,8 +8899,93 @@
         </is>
       </c>
       <c r="AY79" t="inlineStr"/>
+      <c r="AZ79" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128120511</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ45" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ46" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ47" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ48" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ49" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ50" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ51" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ52" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ53" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ54" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ55" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ56" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ57" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ58" r:id="rId57"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ59" r:id="rId58"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ60" r:id="rId59"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ61" r:id="rId60"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ62" r:id="rId61"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ63" r:id="rId62"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ64" r:id="rId63"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ65" r:id="rId64"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ66" r:id="rId65"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ67" r:id="rId66"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ68" r:id="rId67"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ69" r:id="rId68"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ70" r:id="rId69"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ71" r:id="rId70"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ72" r:id="rId71"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ73" r:id="rId72"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ74" r:id="rId73"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ75" r:id="rId74"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ76" r:id="rId75"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ77" r:id="rId76"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ78" r:id="rId77"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ79" r:id="rId78"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>